--- a/c08/data/ohio_2019.xlsx
+++ b/c08/data/ohio_2019.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29231"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Teaching\431\2025-431\431-data\data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Teaching\431\2026-431\431-slides-2026\c08\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{D07BB70C-F453-4AFC-854A-72FF16D3AC7D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C8B1947A-6182-46B7-B171-4044B7265B14}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{8C286B1A-7D6E-4214-A5D8-8E314DB656C3}"/>
+    <workbookView xWindow="28680" yWindow="1140" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{8C286B1A-7D6E-4214-A5D8-8E314DB656C3}"/>
   </bookViews>
   <sheets>
     <sheet name="ohio_data" sheetId="1" r:id="rId1"/>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="522" uniqueCount="253">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="526" uniqueCount="255">
   <si>
     <t>39001</t>
   </si>
@@ -836,6 +836,12 @@
       </rPr>
       <t xml:space="preserve"> https://www.ohiosos.gov/elections/election-results-and-data/2024-official-election-results</t>
     </r>
+  </si>
+  <si>
+    <t>LBW_24</t>
+  </si>
+  <si>
+    <t>2016-2022</t>
   </si>
 </sst>
 </file>
@@ -970,7 +976,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="35">
+  <cellXfs count="33">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -1015,14 +1021,10 @@
     <xf numFmtId="0" fontId="3" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="164" fontId="5" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="2" fontId="5" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="164" fontId="2" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="2" fontId="2" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
@@ -1363,108 +1365,112 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7CE08F67-8BA6-4F4B-879B-B3108DD62E6F}">
-  <dimension ref="A1:X89"/>
+  <dimension ref="A1:Y89"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="9.140625" style="30"/>
+    <col min="1" max="1" width="9.140625" style="28"/>
     <col min="2" max="2" width="6.7109375" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="12.42578125" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="10.28515625" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="9.140625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="10.28515625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="10.28515625" style="17" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="10.28515625" style="15" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="9.140625" style="15" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="9.140625" style="17" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="10.28515625" style="17" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="9.140625" style="17" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="6.85546875" style="17" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="9.140625" style="17" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="8" style="17" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="9.140625" style="17" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="9" bestFit="1" customWidth="1"/>
-    <col min="20" max="21" width="11.28515625" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="13.7109375" style="13" customWidth="1"/>
-    <col min="23" max="23" width="13.7109375" style="13" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="10.140625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="9.140625" customWidth="1"/>
+    <col min="7" max="7" width="10.28515625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="10.28515625" style="17" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="10.28515625" style="15" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="9.140625" style="15" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="9.140625" style="17" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="10.28515625" style="17" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="9.140625" style="17" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="6.85546875" style="17" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="9.140625" style="17" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="8" style="17" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="9.140625" style="17" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="9" bestFit="1" customWidth="1"/>
+    <col min="21" max="22" width="11.28515625" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="13.7109375" style="13" customWidth="1"/>
+    <col min="24" max="24" width="13.7109375" style="13" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="10.140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:24" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="29" t="s">
+    <row r="1" spans="1:25" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="27" t="s">
         <v>201</v>
       </c>
-      <c r="B1" s="26" t="s">
+      <c r="B1" s="24" t="s">
         <v>202</v>
       </c>
-      <c r="C1" s="26" t="s">
+      <c r="C1" s="24" t="s">
         <v>203</v>
       </c>
-      <c r="D1" s="26" t="s">
+      <c r="D1" s="24" t="s">
         <v>218</v>
       </c>
-      <c r="E1" s="26" t="s">
+      <c r="E1" s="24" t="s">
         <v>219</v>
       </c>
-      <c r="F1" s="26" t="s">
+      <c r="F1" s="24" t="s">
+        <v>253</v>
+      </c>
+      <c r="G1" s="24" t="s">
         <v>204</v>
       </c>
-      <c r="G1" s="27" t="s">
+      <c r="H1" s="25" t="s">
         <v>205</v>
       </c>
-      <c r="H1" s="28" t="s">
+      <c r="I1" s="26" t="s">
         <v>206</v>
       </c>
-      <c r="I1" s="28" t="s">
+      <c r="J1" s="26" t="s">
         <v>207</v>
       </c>
-      <c r="J1" s="28" t="s">
+      <c r="K1" s="26" t="s">
         <v>208</v>
       </c>
-      <c r="K1" s="27" t="s">
+      <c r="L1" s="25" t="s">
         <v>209</v>
       </c>
-      <c r="L1" s="27" t="s">
+      <c r="M1" s="25" t="s">
         <v>210</v>
       </c>
-      <c r="M1" s="27" t="s">
+      <c r="N1" s="25" t="s">
         <v>211</v>
       </c>
-      <c r="N1" s="27" t="s">
+      <c r="O1" s="25" t="s">
         <v>212</v>
       </c>
-      <c r="O1" s="27" t="s">
+      <c r="P1" s="25" t="s">
         <v>213</v>
       </c>
-      <c r="P1" s="27" t="s">
+      <c r="Q1" s="25" t="s">
         <v>214</v>
       </c>
-      <c r="Q1" s="27" t="s">
+      <c r="R1" s="25" t="s">
         <v>215</v>
       </c>
-      <c r="R1" s="27" t="s">
+      <c r="S1" s="25" t="s">
         <v>216</v>
       </c>
-      <c r="S1" s="26" t="s">
+      <c r="T1" s="24" t="s">
         <v>217</v>
       </c>
-      <c r="T1" s="26" t="s">
+      <c r="U1" s="24" t="s">
         <v>220</v>
       </c>
-      <c r="U1" s="26" t="s">
+      <c r="V1" s="24" t="s">
         <v>221</v>
       </c>
-      <c r="V1" s="26" t="s">
+      <c r="W1" s="24" t="s">
         <v>244</v>
       </c>
-      <c r="W1" s="26" t="s">
+      <c r="X1" s="24" t="s">
         <v>245</v>
       </c>
-      <c r="X1" s="26" t="s">
+      <c r="Y1" s="24" t="s">
         <v>249</v>
       </c>
     </row>
-    <row r="2" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="A2" s="30" t="s">
+    <row r="2" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A2" s="28" t="s">
         <v>0</v>
       </c>
       <c r="B2" s="12" t="s">
@@ -1480,65 +1486,68 @@
         <v>-0.69</v>
       </c>
       <c r="F2" s="13">
+        <v>8</v>
+      </c>
+      <c r="G2" s="13">
         <v>11156</v>
       </c>
-      <c r="G2" s="16">
+      <c r="H2" s="16">
         <v>25.5</v>
       </c>
-      <c r="H2" s="14">
+      <c r="I2" s="14">
         <v>5.41</v>
       </c>
-      <c r="I2" s="14">
+      <c r="J2" s="14">
         <v>6.1</v>
       </c>
-      <c r="J2" s="14">
+      <c r="K2" s="14">
         <v>8.9600000000000009</v>
       </c>
-      <c r="K2" s="16">
+      <c r="L2" s="16">
         <v>30.2</v>
       </c>
-      <c r="L2" s="16">
+      <c r="M2" s="16">
         <v>40</v>
       </c>
-      <c r="M2" s="16">
+      <c r="N2" s="16">
         <v>36.299999999999997</v>
       </c>
-      <c r="N2" s="16">
+      <c r="O2" s="16">
         <v>80.2</v>
       </c>
-      <c r="O2" s="16">
+      <c r="P2" s="16">
         <v>6.8</v>
       </c>
-      <c r="P2" s="16">
+      <c r="Q2" s="16">
         <v>29.5</v>
       </c>
-      <c r="Q2" s="16">
+      <c r="R2" s="16">
         <v>7.2</v>
       </c>
-      <c r="R2" s="16">
+      <c r="S2" s="16">
         <v>8.4</v>
       </c>
-      <c r="S2" s="13">
+      <c r="T2" s="13">
         <v>27697</v>
-      </c>
-      <c r="T2" s="13">
-        <v>88</v>
       </c>
       <c r="U2" s="13">
         <v>88</v>
       </c>
-      <c r="V2" s="13" t="s">
+      <c r="V2" s="13">
+        <v>88</v>
+      </c>
+      <c r="W2" s="13" t="s">
         <v>226</v>
       </c>
-      <c r="W2" s="13" t="s">
+      <c r="X2" s="13" t="s">
         <v>227</v>
       </c>
-      <c r="X2" s="13">
+      <c r="Y2" s="13">
         <v>81.900000000000006</v>
       </c>
     </row>
-    <row r="3" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="A3" s="30" t="s">
+    <row r="3" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A3" s="28" t="s">
         <v>3</v>
       </c>
       <c r="B3" s="12" t="s">
@@ -1554,65 +1563,68 @@
         <v>-0.17</v>
       </c>
       <c r="F3" s="13">
+        <v>10</v>
+      </c>
+      <c r="G3" s="13">
         <v>8211</v>
       </c>
-      <c r="G3" s="16">
+      <c r="H3" s="16">
         <v>20.100000000000001</v>
       </c>
-      <c r="H3" s="14">
+      <c r="I3" s="14">
         <v>4.53</v>
       </c>
-      <c r="I3" s="14">
+      <c r="J3" s="14">
         <v>5.35</v>
       </c>
-      <c r="J3" s="14">
+      <c r="K3" s="14">
         <v>9.36</v>
       </c>
-      <c r="K3" s="16">
+      <c r="L3" s="16">
         <v>22.8</v>
       </c>
-      <c r="L3" s="16">
+      <c r="M3" s="16">
         <v>39.299999999999997</v>
       </c>
-      <c r="M3" s="16">
+      <c r="N3" s="16">
         <v>34</v>
       </c>
-      <c r="N3" s="16">
+      <c r="O3" s="16">
         <v>90.3</v>
       </c>
-      <c r="O3" s="16">
+      <c r="P3" s="16">
         <v>4</v>
       </c>
-      <c r="P3" s="16">
+      <c r="Q3" s="16">
         <v>19.600000000000001</v>
       </c>
-      <c r="Q3" s="16">
+      <c r="R3" s="16">
         <v>16.399999999999999</v>
       </c>
-      <c r="R3" s="16">
+      <c r="S3" s="16">
         <v>7.4</v>
       </c>
-      <c r="S3" s="13">
+      <c r="T3" s="13">
         <v>102351</v>
       </c>
-      <c r="T3" s="13">
+      <c r="U3" s="13">
         <v>60</v>
       </c>
-      <c r="U3" s="13">
+      <c r="V3" s="13">
         <v>58</v>
       </c>
-      <c r="V3" s="13" t="s">
+      <c r="W3" s="13" t="s">
         <v>228</v>
       </c>
-      <c r="W3" s="13" t="s">
+      <c r="X3" s="13" t="s">
         <v>229</v>
       </c>
-      <c r="X3" s="13">
+      <c r="Y3" s="13">
         <v>70.900000000000006</v>
       </c>
     </row>
-    <row r="4" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="A4" s="30" t="s">
+    <row r="4" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A4" s="28" t="s">
         <v>5</v>
       </c>
       <c r="B4" s="12" t="s">
@@ -1628,65 +1640,68 @@
         <v>0.17</v>
       </c>
       <c r="F4" s="13">
+        <v>6</v>
+      </c>
+      <c r="G4" s="13">
         <v>7410</v>
       </c>
-      <c r="G4" s="16">
+      <c r="H4" s="16">
         <v>19.899999999999999</v>
       </c>
-      <c r="H4" s="14">
+      <c r="I4" s="14">
         <v>4.49</v>
       </c>
-      <c r="I4" s="14">
+      <c r="J4" s="14">
         <v>5.44</v>
       </c>
-      <c r="J4" s="14">
+      <c r="K4" s="14">
         <v>6.11</v>
       </c>
-      <c r="K4" s="16">
+      <c r="L4" s="16">
         <v>23.6</v>
       </c>
-      <c r="L4" s="16">
+      <c r="M4" s="16">
         <v>34.1</v>
       </c>
-      <c r="M4" s="16">
+      <c r="N4" s="16">
         <v>30.8</v>
       </c>
-      <c r="N4" s="16">
+      <c r="O4" s="16">
         <v>88.5</v>
       </c>
-      <c r="O4" s="16">
+      <c r="P4" s="16">
         <v>4.2</v>
       </c>
-      <c r="P4" s="16">
+      <c r="Q4" s="16">
         <v>19.100000000000001</v>
       </c>
-      <c r="Q4" s="16">
+      <c r="R4" s="16">
         <v>18.7</v>
       </c>
-      <c r="R4" s="16">
+      <c r="S4" s="16">
         <v>9</v>
       </c>
-      <c r="S4" s="13">
+      <c r="T4" s="13">
         <v>53483</v>
-      </c>
-      <c r="T4" s="13">
-        <v>21</v>
       </c>
       <c r="U4" s="13">
         <v>21</v>
       </c>
-      <c r="V4" s="13" t="s">
+      <c r="V4" s="13">
+        <v>21</v>
+      </c>
+      <c r="W4" s="13" t="s">
         <v>230</v>
       </c>
-      <c r="W4" s="13" t="s">
+      <c r="X4" s="13" t="s">
         <v>231</v>
       </c>
-      <c r="X4" s="13">
+      <c r="Y4" s="13">
         <v>73.400000000000006</v>
       </c>
     </row>
-    <row r="5" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="A5" s="30" t="s">
+    <row r="5" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A5" s="28" t="s">
         <v>7</v>
       </c>
       <c r="B5" s="12" t="s">
@@ -1702,65 +1717,68 @@
         <v>-0.62</v>
       </c>
       <c r="F5" s="13">
+        <v>8</v>
+      </c>
+      <c r="G5" s="13">
         <v>10033</v>
       </c>
-      <c r="G5" s="16">
+      <c r="H5" s="16">
         <v>24.7</v>
       </c>
-      <c r="H5" s="14">
+      <c r="I5" s="14">
         <v>5.07</v>
       </c>
-      <c r="I5" s="14">
+      <c r="J5" s="14">
         <v>5.73</v>
       </c>
-      <c r="J5" s="14">
+      <c r="K5" s="14">
         <v>8.14</v>
       </c>
-      <c r="K5" s="16">
+      <c r="L5" s="16">
         <v>27</v>
       </c>
-      <c r="L5" s="16">
+      <c r="M5" s="16">
         <v>43</v>
       </c>
-      <c r="M5" s="16">
+      <c r="N5" s="16">
         <v>35.200000000000003</v>
       </c>
-      <c r="N5" s="16">
+      <c r="O5" s="16">
         <v>86</v>
       </c>
-      <c r="O5" s="16">
+      <c r="P5" s="16">
         <v>4.8</v>
       </c>
-      <c r="P5" s="16">
+      <c r="Q5" s="16">
         <v>26.5</v>
       </c>
-      <c r="Q5" s="16">
+      <c r="R5" s="16">
         <v>12.5</v>
       </c>
-      <c r="R5" s="16">
+      <c r="S5" s="16">
         <v>8.3000000000000007</v>
       </c>
-      <c r="S5" s="13">
+      <c r="T5" s="13">
         <v>97241</v>
       </c>
-      <c r="T5" s="13">
+      <c r="U5" s="13">
         <v>68</v>
       </c>
-      <c r="U5" s="13">
+      <c r="V5" s="13">
         <v>81</v>
       </c>
-      <c r="V5" s="13" t="s">
+      <c r="W5" s="13" t="s">
         <v>230</v>
       </c>
-      <c r="W5" s="13" t="s">
+      <c r="X5" s="13" t="s">
         <v>231</v>
       </c>
-      <c r="X5" s="13">
+      <c r="Y5" s="13">
         <v>63</v>
       </c>
     </row>
-    <row r="6" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="A6" s="30" t="s">
+    <row r="6" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A6" s="28" t="s">
         <v>9</v>
       </c>
       <c r="B6" s="12" t="s">
@@ -1776,65 +1794,68 @@
         <v>-0.09</v>
       </c>
       <c r="F6" s="13">
+        <v>8</v>
+      </c>
+      <c r="G6" s="13">
         <v>7156</v>
       </c>
-      <c r="G6" s="16">
+      <c r="H6" s="16">
         <v>22.4</v>
       </c>
-      <c r="H6" s="14">
+      <c r="I6" s="14">
         <v>5.0199999999999996</v>
       </c>
-      <c r="I6" s="14">
+      <c r="J6" s="14">
         <v>5.71</v>
       </c>
-      <c r="J6" s="14">
+      <c r="K6" s="14">
         <v>8.83</v>
       </c>
-      <c r="K6" s="16">
+      <c r="L6" s="16">
         <v>25</v>
       </c>
-      <c r="L6" s="16">
+      <c r="M6" s="16">
         <v>34.299999999999997</v>
       </c>
-      <c r="M6" s="16">
+      <c r="N6" s="16">
         <v>31.6</v>
       </c>
-      <c r="N6" s="16">
+      <c r="O6" s="16">
         <v>90</v>
       </c>
-      <c r="O6" s="16">
+      <c r="P6" s="16">
         <v>5.3</v>
       </c>
-      <c r="P6" s="16">
+      <c r="Q6" s="16">
         <v>25.3</v>
       </c>
-      <c r="Q6" s="16">
+      <c r="R6" s="16">
         <v>8.3000000000000007</v>
       </c>
-      <c r="R6" s="16">
+      <c r="S6" s="16">
         <v>6.4</v>
       </c>
-      <c r="S6" s="13">
+      <c r="T6" s="13">
         <v>65326</v>
       </c>
-      <c r="T6" s="13">
+      <c r="U6" s="13">
         <v>65</v>
       </c>
-      <c r="U6" s="13">
+      <c r="V6" s="13">
         <v>62</v>
       </c>
-      <c r="V6" s="13" t="s">
+      <c r="W6" s="13" t="s">
         <v>232</v>
       </c>
-      <c r="W6" s="13" t="s">
+      <c r="X6" s="13" t="s">
         <v>233</v>
       </c>
-      <c r="X6" s="13">
+      <c r="Y6" s="13">
         <v>43.3</v>
       </c>
     </row>
-    <row r="7" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="A7" s="30" t="s">
+    <row r="7" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A7" s="28" t="s">
         <v>11</v>
       </c>
       <c r="B7" s="12" t="s">
@@ -1850,65 +1871,68 @@
         <v>0.42</v>
       </c>
       <c r="F7" s="13">
+        <v>7</v>
+      </c>
+      <c r="G7" s="13">
         <v>5718</v>
       </c>
-      <c r="G7" s="16">
+      <c r="H7" s="16">
         <v>17.3</v>
       </c>
-      <c r="H7" s="14">
+      <c r="I7" s="14">
         <v>4.16</v>
       </c>
-      <c r="I7" s="14">
+      <c r="J7" s="14">
         <v>5.2</v>
       </c>
-      <c r="J7" s="14">
+      <c r="K7" s="14">
         <v>7.15</v>
       </c>
-      <c r="K7" s="16">
+      <c r="L7" s="16">
         <v>21.6</v>
       </c>
-      <c r="L7" s="16">
+      <c r="M7" s="16">
         <v>39.200000000000003</v>
       </c>
-      <c r="M7" s="16">
+      <c r="N7" s="16">
         <v>27.8</v>
       </c>
-      <c r="N7" s="16">
+      <c r="O7" s="16">
         <v>92.7</v>
       </c>
-      <c r="O7" s="16">
+      <c r="P7" s="16">
         <v>3</v>
       </c>
-      <c r="P7" s="16">
+      <c r="Q7" s="16">
         <v>9.1999999999999993</v>
       </c>
-      <c r="Q7" s="16">
+      <c r="R7" s="16">
         <v>15.1</v>
       </c>
-      <c r="R7" s="16">
+      <c r="S7" s="16">
         <v>9.4</v>
       </c>
-      <c r="S7" s="13">
+      <c r="T7" s="13">
         <v>45656</v>
       </c>
-      <c r="T7" s="13">
+      <c r="U7" s="13">
         <v>9</v>
       </c>
-      <c r="U7" s="13">
+      <c r="V7" s="13">
         <v>13</v>
       </c>
-      <c r="V7" s="13" t="s">
+      <c r="W7" s="13" t="s">
         <v>228</v>
       </c>
-      <c r="W7" s="13" t="s">
+      <c r="X7" s="13" t="s">
         <v>234</v>
       </c>
-      <c r="X7" s="13">
+      <c r="Y7" s="13">
         <v>81.099999999999994</v>
       </c>
     </row>
-    <row r="8" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="A8" s="30" t="s">
+    <row r="8" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A8" s="28" t="s">
         <v>13</v>
       </c>
       <c r="B8" s="12" t="s">
@@ -1924,65 +1948,68 @@
         <v>-0.21</v>
       </c>
       <c r="F8" s="13">
+        <v>9</v>
+      </c>
+      <c r="G8" s="13">
         <v>8428</v>
       </c>
-      <c r="G8" s="16">
+      <c r="H8" s="16">
         <v>20.5</v>
       </c>
-      <c r="H8" s="14">
+      <c r="I8" s="14">
         <v>4.4800000000000004</v>
       </c>
-      <c r="I8" s="14">
+      <c r="J8" s="14">
         <v>5.38</v>
       </c>
-      <c r="J8" s="14">
+      <c r="K8" s="14">
         <v>8.23</v>
       </c>
-      <c r="K8" s="16">
+      <c r="L8" s="16">
         <v>25.8</v>
       </c>
-      <c r="L8" s="16">
+      <c r="M8" s="16">
         <v>36.6</v>
       </c>
-      <c r="M8" s="16">
+      <c r="N8" s="16">
         <v>33.799999999999997</v>
       </c>
-      <c r="N8" s="16">
+      <c r="O8" s="16">
         <v>90.2</v>
       </c>
-      <c r="O8" s="16">
+      <c r="P8" s="16">
         <v>5.6</v>
       </c>
-      <c r="P8" s="16">
+      <c r="Q8" s="16">
         <v>15.7</v>
       </c>
-      <c r="Q8" s="16">
+      <c r="R8" s="16">
         <v>14.2</v>
       </c>
-      <c r="R8" s="16">
+      <c r="S8" s="16">
         <v>8.6999999999999993</v>
       </c>
-      <c r="S8" s="13">
+      <c r="T8" s="13">
         <v>67005</v>
       </c>
-      <c r="T8" s="13">
+      <c r="U8" s="13">
         <v>50</v>
       </c>
-      <c r="U8" s="13">
+      <c r="V8" s="13">
         <v>59</v>
       </c>
-      <c r="V8" s="13" t="s">
+      <c r="W8" s="13" t="s">
         <v>232</v>
       </c>
-      <c r="W8" s="13" t="s">
+      <c r="X8" s="13" t="s">
         <v>235</v>
       </c>
-      <c r="X8" s="13">
+      <c r="Y8" s="13">
         <v>72.5</v>
       </c>
     </row>
-    <row r="9" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="A9" s="30" t="s">
+    <row r="9" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A9" s="28" t="s">
         <v>15</v>
       </c>
       <c r="B9" s="12" t="s">
@@ -1998,65 +2025,68 @@
         <v>-0.55000000000000004</v>
       </c>
       <c r="F9" s="13">
+        <v>8</v>
+      </c>
+      <c r="G9" s="13">
         <v>10448</v>
       </c>
-      <c r="G9" s="16">
+      <c r="H9" s="16">
         <v>21.2</v>
       </c>
-      <c r="H9" s="14">
+      <c r="I9" s="14">
         <v>4.68</v>
       </c>
-      <c r="I9" s="14">
+      <c r="J9" s="14">
         <v>5.6</v>
       </c>
-      <c r="J9" s="14">
+      <c r="K9" s="14">
         <v>7.63</v>
       </c>
-      <c r="K9" s="16">
+      <c r="L9" s="16">
         <v>24.4</v>
       </c>
-      <c r="L9" s="16">
+      <c r="M9" s="16">
         <v>37</v>
       </c>
-      <c r="M9" s="16">
+      <c r="N9" s="16">
         <v>32.4</v>
       </c>
-      <c r="N9" s="16">
+      <c r="O9" s="16">
         <v>87.9</v>
       </c>
-      <c r="O9" s="16">
+      <c r="P9" s="16">
         <v>5</v>
       </c>
-      <c r="P9" s="16">
+      <c r="Q9" s="16">
         <v>18</v>
       </c>
-      <c r="Q9" s="16">
+      <c r="R9" s="16">
         <v>6.4</v>
       </c>
-      <c r="R9" s="16">
+      <c r="S9" s="16">
         <v>9</v>
       </c>
-      <c r="S9" s="13">
+      <c r="T9" s="13">
         <v>43431</v>
-      </c>
-      <c r="T9" s="13">
-        <v>73</v>
       </c>
       <c r="U9" s="13">
         <v>73</v>
       </c>
-      <c r="V9" s="13" t="s">
+      <c r="V9" s="13">
+        <v>73</v>
+      </c>
+      <c r="W9" s="13" t="s">
         <v>226</v>
       </c>
-      <c r="W9" s="13" t="s">
+      <c r="X9" s="13" t="s">
         <v>227</v>
       </c>
-      <c r="X9" s="13">
+      <c r="Y9" s="13">
         <v>79.7</v>
       </c>
     </row>
-    <row r="10" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="A10" s="30" t="s">
+    <row r="10" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A10" s="28" t="s">
         <v>17</v>
       </c>
       <c r="B10" s="12" t="s">
@@ -2072,65 +2102,68 @@
         <v>0.05</v>
       </c>
       <c r="F10" s="13">
+        <v>8</v>
+      </c>
+      <c r="G10" s="13">
         <v>9226</v>
       </c>
-      <c r="G10" s="16">
+      <c r="H10" s="16">
         <v>18.7</v>
       </c>
-      <c r="H10" s="14">
+      <c r="I10" s="14">
         <v>4.16</v>
       </c>
-      <c r="I10" s="14">
+      <c r="J10" s="14">
         <v>5.05</v>
       </c>
-      <c r="J10" s="14">
+      <c r="K10" s="14">
         <v>7.89</v>
       </c>
-      <c r="K10" s="16">
+      <c r="L10" s="16">
         <v>21.8</v>
       </c>
-      <c r="L10" s="16">
+      <c r="M10" s="16">
         <v>34.4</v>
       </c>
-      <c r="M10" s="16">
+      <c r="N10" s="16">
         <v>27.6</v>
       </c>
-      <c r="N10" s="16">
+      <c r="O10" s="16">
         <v>90.6</v>
       </c>
-      <c r="O10" s="16">
+      <c r="P10" s="16">
         <v>3.8</v>
       </c>
-      <c r="P10" s="16">
+      <c r="Q10" s="16">
         <v>14.1</v>
       </c>
-      <c r="Q10" s="16">
+      <c r="R10" s="16">
         <v>8.1</v>
       </c>
-      <c r="R10" s="16">
+      <c r="S10" s="16">
         <v>12</v>
       </c>
-      <c r="S10" s="13">
+      <c r="T10" s="13">
         <v>383134</v>
       </c>
-      <c r="T10" s="13">
+      <c r="U10" s="13">
         <v>56</v>
       </c>
-      <c r="U10" s="13">
+      <c r="V10" s="13">
         <v>43</v>
       </c>
-      <c r="V10" s="13" t="s">
+      <c r="W10" s="13" t="s">
         <v>226</v>
       </c>
-      <c r="W10" s="13" t="s">
+      <c r="X10" s="13" t="s">
         <v>227</v>
       </c>
-      <c r="X10" s="13">
+      <c r="Y10" s="13">
         <v>61.8</v>
       </c>
     </row>
-    <row r="11" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="A11" s="30" t="s">
+    <row r="11" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A11" s="28" t="s">
         <v>19</v>
       </c>
       <c r="B11" s="12" t="s">
@@ -2146,65 +2179,68 @@
         <v>-0.17</v>
       </c>
       <c r="F11" s="13">
+        <v>8</v>
+      </c>
+      <c r="G11" s="13">
         <v>8711</v>
       </c>
-      <c r="G11" s="16">
+      <c r="H11" s="16">
         <v>19.8</v>
       </c>
-      <c r="H11" s="14">
+      <c r="I11" s="14">
         <v>4.54</v>
       </c>
-      <c r="I11" s="14">
+      <c r="J11" s="14">
         <v>5.5</v>
       </c>
-      <c r="J11" s="14">
+      <c r="K11" s="14">
         <v>8.17</v>
       </c>
-      <c r="K11" s="16">
+      <c r="L11" s="16">
         <v>24.2</v>
       </c>
-      <c r="L11" s="16">
+      <c r="M11" s="16">
         <v>37.1</v>
       </c>
-      <c r="M11" s="16">
+      <c r="N11" s="16">
         <v>30.2</v>
       </c>
-      <c r="N11" s="16">
+      <c r="O11" s="16">
         <v>89.5</v>
       </c>
-      <c r="O11" s="16">
+      <c r="P11" s="16">
         <v>5</v>
       </c>
-      <c r="P11" s="16">
+      <c r="Q11" s="16">
         <v>18.2</v>
       </c>
-      <c r="Q11" s="16">
+      <c r="R11" s="16">
         <v>14.1</v>
       </c>
-      <c r="R11" s="16">
+      <c r="S11" s="16">
         <v>9.1</v>
       </c>
-      <c r="S11" s="13">
+      <c r="T11" s="13">
         <v>26914</v>
       </c>
-      <c r="T11" s="13">
+      <c r="U11" s="13">
         <v>39</v>
       </c>
-      <c r="U11" s="13">
+      <c r="V11" s="13">
         <v>49</v>
       </c>
-      <c r="V11" s="13" t="s">
+      <c r="W11" s="13" t="s">
         <v>230</v>
       </c>
-      <c r="W11" s="13" t="s">
+      <c r="X11" s="13" t="s">
         <v>231</v>
       </c>
-      <c r="X11" s="13">
+      <c r="Y11" s="13">
         <v>76.3</v>
       </c>
     </row>
-    <row r="12" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="A12" s="30" t="s">
+    <row r="12" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A12" s="28" t="s">
         <v>21</v>
       </c>
       <c r="B12" s="12" t="s">
@@ -2220,65 +2256,68 @@
         <v>0.03</v>
       </c>
       <c r="F12" s="13">
+        <v>8</v>
+      </c>
+      <c r="G12" s="13">
         <v>8385</v>
       </c>
-      <c r="G12" s="16">
+      <c r="H12" s="16">
         <v>19.2</v>
       </c>
-      <c r="H12" s="14">
+      <c r="I12" s="14">
         <v>4.3899999999999997</v>
       </c>
-      <c r="I12" s="14">
+      <c r="J12" s="14">
         <v>5.37</v>
       </c>
-      <c r="J12" s="14">
+      <c r="K12" s="14">
         <v>6.78</v>
       </c>
-      <c r="K12" s="16">
+      <c r="L12" s="16">
         <v>23.5</v>
       </c>
-      <c r="L12" s="16">
+      <c r="M12" s="16">
         <v>38.299999999999997</v>
       </c>
-      <c r="M12" s="16">
+      <c r="N12" s="16">
         <v>29.3</v>
       </c>
-      <c r="N12" s="16">
+      <c r="O12" s="16">
         <v>91.2</v>
       </c>
-      <c r="O12" s="16">
+      <c r="P12" s="16">
         <v>3.7</v>
       </c>
-      <c r="P12" s="16">
+      <c r="Q12" s="16">
         <v>11.1</v>
       </c>
-      <c r="Q12" s="16">
+      <c r="R12" s="16">
         <v>11.8</v>
       </c>
-      <c r="R12" s="16">
+      <c r="S12" s="16">
         <v>9.6999999999999993</v>
       </c>
-      <c r="S12" s="13">
+      <c r="T12" s="13">
         <v>38884</v>
       </c>
-      <c r="T12" s="13">
+      <c r="U12" s="13">
         <v>47</v>
       </c>
-      <c r="U12" s="13">
+      <c r="V12" s="13">
         <v>37</v>
       </c>
-      <c r="V12" s="13" t="s">
+      <c r="W12" s="13" t="s">
         <v>228</v>
       </c>
-      <c r="W12" s="13" t="s">
+      <c r="X12" s="13" t="s">
         <v>234</v>
       </c>
-      <c r="X12" s="13">
+      <c r="Y12" s="13">
         <v>74</v>
       </c>
     </row>
-    <row r="13" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="A13" s="30" t="s">
+    <row r="13" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A13" s="28" t="s">
         <v>23</v>
       </c>
       <c r="B13" s="12" t="s">
@@ -2294,65 +2333,68 @@
         <v>-0.33</v>
       </c>
       <c r="F13" s="13">
+        <v>9</v>
+      </c>
+      <c r="G13" s="13">
         <v>11727</v>
       </c>
-      <c r="G13" s="16">
+      <c r="H13" s="16">
         <v>21.8</v>
       </c>
-      <c r="H13" s="14">
+      <c r="I13" s="14">
         <v>4.68</v>
       </c>
-      <c r="I13" s="14">
+      <c r="J13" s="14">
         <v>5.51</v>
       </c>
-      <c r="J13" s="14">
+      <c r="K13" s="14">
         <v>8.99</v>
       </c>
-      <c r="K13" s="16">
+      <c r="L13" s="16">
         <v>24.9</v>
       </c>
-      <c r="L13" s="16">
+      <c r="M13" s="16">
         <v>40.799999999999997</v>
       </c>
-      <c r="M13" s="16">
+      <c r="N13" s="16">
         <v>30.8</v>
       </c>
-      <c r="N13" s="16">
+      <c r="O13" s="16">
         <v>88.7</v>
       </c>
-      <c r="O13" s="16">
+      <c r="P13" s="16">
         <v>4.3</v>
       </c>
-      <c r="P13" s="16">
+      <c r="Q13" s="16">
         <v>21</v>
       </c>
-      <c r="Q13" s="16">
+      <c r="R13" s="16">
         <v>10.4</v>
       </c>
-      <c r="R13" s="16">
+      <c r="S13" s="16">
         <v>10.5</v>
       </c>
-      <c r="S13" s="13">
+      <c r="T13" s="13">
         <v>134082</v>
       </c>
-      <c r="T13" s="13">
+      <c r="U13" s="13">
         <v>80</v>
       </c>
-      <c r="U13" s="13">
+      <c r="V13" s="13">
         <v>69</v>
       </c>
-      <c r="V13" s="13" t="s">
+      <c r="W13" s="13" t="s">
         <v>228</v>
       </c>
-      <c r="W13" s="13" t="s">
+      <c r="X13" s="13" t="s">
         <v>234</v>
       </c>
-      <c r="X13" s="13">
+      <c r="Y13" s="13">
         <v>63.4</v>
       </c>
     </row>
-    <row r="14" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="A14" s="30" t="s">
+    <row r="14" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A14" s="28" t="s">
         <v>25</v>
       </c>
       <c r="B14" s="12" t="s">
@@ -2368,65 +2410,68 @@
         <v>0.18</v>
       </c>
       <c r="F14" s="13">
+        <v>8</v>
+      </c>
+      <c r="G14" s="13">
         <v>8020</v>
       </c>
-      <c r="G14" s="16">
+      <c r="H14" s="16">
         <v>17.7</v>
       </c>
-      <c r="H14" s="14">
+      <c r="I14" s="14">
         <v>4.09</v>
       </c>
-      <c r="I14" s="14">
+      <c r="J14" s="14">
         <v>5.0999999999999996</v>
       </c>
-      <c r="J14" s="14">
+      <c r="K14" s="14">
         <v>7.32</v>
       </c>
-      <c r="K14" s="16">
+      <c r="L14" s="16">
         <v>23.1</v>
       </c>
-      <c r="L14" s="16">
+      <c r="M14" s="16">
         <v>36.1</v>
       </c>
-      <c r="M14" s="16">
+      <c r="N14" s="16">
         <v>28.5</v>
       </c>
-      <c r="N14" s="16">
+      <c r="O14" s="16">
         <v>90.2</v>
       </c>
-      <c r="O14" s="16">
+      <c r="P14" s="16">
         <v>3.7</v>
       </c>
-      <c r="P14" s="16">
+      <c r="Q14" s="16">
         <v>11.7</v>
       </c>
-      <c r="Q14" s="16">
+      <c r="R14" s="16">
         <v>7.2</v>
       </c>
-      <c r="R14" s="16">
+      <c r="S14" s="16">
         <v>9.9</v>
       </c>
-      <c r="S14" s="13">
+      <c r="T14" s="13">
         <v>206427</v>
-      </c>
-      <c r="T14" s="13">
-        <v>34</v>
       </c>
       <c r="U14" s="13">
         <v>34</v>
       </c>
-      <c r="V14" s="13" t="s">
+      <c r="V14" s="13">
+        <v>34</v>
+      </c>
+      <c r="W14" s="13" t="s">
         <v>226</v>
       </c>
-      <c r="W14" s="13" t="s">
+      <c r="X14" s="13" t="s">
         <v>227</v>
       </c>
-      <c r="X14" s="13">
+      <c r="Y14" s="13">
         <v>66.7</v>
       </c>
     </row>
-    <row r="15" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="A15" s="30" t="s">
+    <row r="15" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A15" s="28" t="s">
         <v>27</v>
       </c>
       <c r="B15" s="12" t="s">
@@ -2442,65 +2487,68 @@
         <v>-0.18</v>
       </c>
       <c r="F15" s="13">
+        <v>8</v>
+      </c>
+      <c r="G15" s="13">
         <v>10441</v>
       </c>
-      <c r="G15" s="16">
+      <c r="H15" s="16">
         <v>20.7</v>
       </c>
-      <c r="H15" s="14">
+      <c r="I15" s="14">
         <v>4.68</v>
       </c>
-      <c r="I15" s="14">
+      <c r="J15" s="14">
         <v>5.57</v>
       </c>
-      <c r="J15" s="14">
+      <c r="K15" s="14">
         <v>7.55</v>
       </c>
-      <c r="K15" s="16">
+      <c r="L15" s="16">
         <v>25.6</v>
       </c>
-      <c r="L15" s="16">
+      <c r="M15" s="16">
         <v>39.5</v>
       </c>
-      <c r="M15" s="16">
+      <c r="N15" s="16">
         <v>32.5</v>
       </c>
-      <c r="N15" s="16">
+      <c r="O15" s="16">
         <v>88.3</v>
       </c>
-      <c r="O15" s="16">
+      <c r="P15" s="16">
         <v>4.7</v>
       </c>
-      <c r="P15" s="16">
+      <c r="Q15" s="16">
         <v>22.2</v>
       </c>
-      <c r="Q15" s="16">
+      <c r="R15" s="16">
         <v>9.8000000000000007</v>
       </c>
-      <c r="R15" s="16">
+      <c r="S15" s="16">
         <v>9.4</v>
       </c>
-      <c r="S15" s="13">
+      <c r="T15" s="13">
         <v>41968</v>
       </c>
-      <c r="T15" s="13">
+      <c r="U15" s="13">
         <v>57</v>
       </c>
-      <c r="U15" s="13">
+      <c r="V15" s="13">
         <v>53</v>
       </c>
-      <c r="V15" s="13" t="s">
+      <c r="W15" s="13" t="s">
         <v>226</v>
       </c>
-      <c r="W15" s="13" t="s">
+      <c r="X15" s="13" t="s">
         <v>227</v>
       </c>
-      <c r="X15" s="13">
+      <c r="Y15" s="13">
         <v>76.2</v>
       </c>
     </row>
-    <row r="16" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="A16" s="30" t="s">
+    <row r="16" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A16" s="28" t="s">
         <v>29</v>
       </c>
       <c r="B16" s="12" t="s">
@@ -2516,65 +2564,68 @@
         <v>-0.31</v>
       </c>
       <c r="F16" s="13">
+        <v>8</v>
+      </c>
+      <c r="G16" s="13">
         <v>8721</v>
       </c>
-      <c r="G16" s="16">
+      <c r="H16" s="16">
         <v>20.9</v>
       </c>
-      <c r="H16" s="14">
+      <c r="I16" s="14">
         <v>4.68</v>
       </c>
-      <c r="I16" s="14">
+      <c r="J16" s="14">
         <v>5.53</v>
       </c>
-      <c r="J16" s="14">
+      <c r="K16" s="14">
         <v>7.36</v>
       </c>
-      <c r="K16" s="16">
+      <c r="L16" s="16">
         <v>25.4</v>
       </c>
-      <c r="L16" s="16">
+      <c r="M16" s="16">
         <v>37.799999999999997</v>
       </c>
-      <c r="M16" s="16">
+      <c r="N16" s="16">
         <v>33</v>
       </c>
-      <c r="N16" s="16">
+      <c r="O16" s="16">
         <v>88.5</v>
       </c>
-      <c r="O16" s="16">
+      <c r="P16" s="16">
         <v>4.8</v>
       </c>
-      <c r="P16" s="16">
+      <c r="Q16" s="16">
         <v>18.100000000000001</v>
       </c>
-      <c r="Q16" s="16">
+      <c r="R16" s="16">
         <v>15.6</v>
       </c>
-      <c r="R16" s="16">
+      <c r="S16" s="16">
         <v>9.4</v>
       </c>
-      <c r="S16" s="13">
+      <c r="T16" s="13">
         <v>101882</v>
       </c>
-      <c r="T16" s="13">
+      <c r="U16" s="13">
         <v>59</v>
       </c>
-      <c r="U16" s="13">
+      <c r="V16" s="13">
         <v>60</v>
       </c>
-      <c r="V16" s="13" t="s">
+      <c r="W16" s="13" t="s">
         <v>230</v>
       </c>
-      <c r="W16" s="13" t="s">
+      <c r="X16" s="13" t="s">
         <v>236</v>
       </c>
-      <c r="X16" s="13">
+      <c r="Y16" s="13">
         <v>73.3</v>
       </c>
     </row>
-    <row r="17" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="A17" s="30" t="s">
+    <row r="17" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A17" s="28" t="s">
         <v>31</v>
       </c>
       <c r="B17" s="12" t="s">
@@ -2590,65 +2641,68 @@
         <v>-0.43</v>
       </c>
       <c r="F17" s="13">
+        <v>7</v>
+      </c>
+      <c r="G17" s="13">
         <v>8827</v>
       </c>
-      <c r="G17" s="16">
+      <c r="H17" s="16">
         <v>22.3</v>
       </c>
-      <c r="H17" s="14">
+      <c r="I17" s="14">
         <v>4.9400000000000004</v>
       </c>
-      <c r="I17" s="14">
+      <c r="J17" s="14">
         <v>5.78</v>
       </c>
-      <c r="J17" s="14">
+      <c r="K17" s="14">
         <v>7.27</v>
       </c>
-      <c r="K17" s="16">
+      <c r="L17" s="16">
         <v>27.3</v>
       </c>
-      <c r="L17" s="16">
+      <c r="M17" s="16">
         <v>38.5</v>
       </c>
-      <c r="M17" s="16">
+      <c r="N17" s="16">
         <v>33.5</v>
       </c>
-      <c r="N17" s="16">
+      <c r="O17" s="16">
         <v>85.5</v>
       </c>
-      <c r="O17" s="16">
+      <c r="P17" s="16">
         <v>5.8</v>
       </c>
-      <c r="P17" s="16">
+      <c r="Q17" s="16">
         <v>18.8</v>
       </c>
-      <c r="Q17" s="16">
+      <c r="R17" s="16">
         <v>11.2</v>
       </c>
-      <c r="R17" s="16">
+      <c r="S17" s="16">
         <v>8.9</v>
       </c>
-      <c r="S17" s="13">
+      <c r="T17" s="13">
         <v>36599</v>
       </c>
-      <c r="T17" s="13">
+      <c r="U17" s="13">
         <v>29</v>
       </c>
-      <c r="U17" s="13">
+      <c r="V17" s="13">
         <v>61</v>
       </c>
-      <c r="V17" s="13" t="s">
+      <c r="W17" s="13" t="s">
         <v>237</v>
       </c>
-      <c r="W17" s="13" t="s">
+      <c r="X17" s="13" t="s">
         <v>238</v>
       </c>
-      <c r="X17" s="13">
+      <c r="Y17" s="13">
         <v>74.599999999999994</v>
       </c>
     </row>
-    <row r="18" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="A18" s="30" t="s">
+    <row r="18" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A18" s="28" t="s">
         <v>33</v>
       </c>
       <c r="B18" s="12" t="s">
@@ -2664,139 +2718,145 @@
         <v>-0.26</v>
       </c>
       <c r="F18" s="13">
+        <v>9</v>
+      </c>
+      <c r="G18" s="13">
         <v>9914</v>
       </c>
-      <c r="G18" s="16">
+      <c r="H18" s="16">
         <v>21.4</v>
       </c>
-      <c r="H18" s="14">
+      <c r="I18" s="14">
         <v>4.79</v>
       </c>
-      <c r="I18" s="14">
+      <c r="J18" s="14">
         <v>5.65</v>
       </c>
-      <c r="J18" s="14">
+      <c r="K18" s="14">
         <v>8.3800000000000008</v>
       </c>
-      <c r="K18" s="16">
+      <c r="L18" s="16">
         <v>26.1</v>
       </c>
-      <c r="L18" s="16">
+      <c r="M18" s="16">
         <v>39</v>
       </c>
-      <c r="M18" s="16">
+      <c r="N18" s="16">
         <v>30.6</v>
       </c>
-      <c r="N18" s="16">
+      <c r="O18" s="16">
         <v>90.2</v>
       </c>
-      <c r="O18" s="16">
+      <c r="P18" s="16">
         <v>4.7</v>
       </c>
-      <c r="P18" s="16">
+      <c r="Q18" s="16">
         <v>23</v>
       </c>
-      <c r="Q18" s="16">
+      <c r="R18" s="16">
         <v>18.600000000000001</v>
       </c>
-      <c r="R18" s="16">
+      <c r="S18" s="16">
         <v>8.9</v>
       </c>
-      <c r="S18" s="13">
+      <c r="T18" s="13">
         <v>41493</v>
       </c>
-      <c r="T18" s="13">
+      <c r="U18" s="13">
         <v>63</v>
       </c>
-      <c r="U18" s="13">
+      <c r="V18" s="13">
         <v>50</v>
       </c>
-      <c r="V18" s="13" t="s">
+      <c r="W18" s="13" t="s">
         <v>237</v>
       </c>
-      <c r="W18" s="13" t="s">
+      <c r="X18" s="13" t="s">
         <v>238</v>
       </c>
-      <c r="X18" s="13">
+      <c r="Y18" s="13">
         <v>75.099999999999994</v>
       </c>
     </row>
-    <row r="19" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="A19" s="31" t="s">
+    <row r="19" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A19" s="29" t="s">
         <v>35</v>
       </c>
-      <c r="B19" s="22" t="s">
-        <v>1</v>
-      </c>
-      <c r="C19" s="22" t="s">
+      <c r="B19" s="21" t="s">
+        <v>1</v>
+      </c>
+      <c r="C19" s="21" t="s">
         <v>36</v>
       </c>
-      <c r="D19" s="21">
+      <c r="D19" s="20">
         <v>-0.33</v>
       </c>
-      <c r="E19" s="21">
+      <c r="E19" s="20">
         <v>-0.06</v>
       </c>
-      <c r="F19" s="21">
+      <c r="F19" s="20">
+        <v>11</v>
+      </c>
+      <c r="G19" s="20">
         <v>8939</v>
       </c>
-      <c r="G19" s="23">
+      <c r="H19" s="22">
         <v>20</v>
       </c>
-      <c r="H19" s="24">
+      <c r="I19" s="23">
         <v>4.34</v>
       </c>
-      <c r="I19" s="24">
+      <c r="J19" s="23">
         <v>5.04</v>
       </c>
-      <c r="J19" s="24">
+      <c r="K19" s="23">
         <v>10.65</v>
       </c>
-      <c r="K19" s="23">
+      <c r="L19" s="22">
         <v>21.5</v>
       </c>
-      <c r="L19" s="23">
+      <c r="M19" s="22">
         <v>36.700000000000003</v>
       </c>
-      <c r="M19" s="23">
+      <c r="N19" s="22">
         <v>28.5</v>
       </c>
-      <c r="N19" s="23">
+      <c r="O19" s="22">
         <v>89.8</v>
       </c>
-      <c r="O19" s="23">
+      <c r="P19" s="22">
         <v>4.2</v>
       </c>
-      <c r="P19" s="23">
+      <c r="Q19" s="22">
         <v>23.6</v>
       </c>
-      <c r="Q19" s="23">
+      <c r="R19" s="22">
         <v>9.1</v>
       </c>
-      <c r="R19" s="23">
+      <c r="S19" s="22">
         <v>10.9</v>
       </c>
-      <c r="S19" s="21">
+      <c r="T19" s="20">
         <v>1235071</v>
       </c>
-      <c r="T19" s="21">
+      <c r="U19" s="20">
         <v>62</v>
       </c>
-      <c r="U19" s="21">
+      <c r="V19" s="20">
         <v>66</v>
       </c>
-      <c r="V19" s="21" t="s">
+      <c r="W19" s="20" t="s">
         <v>230</v>
       </c>
-      <c r="W19" s="21" t="s">
+      <c r="X19" s="20" t="s">
         <v>231</v>
       </c>
-      <c r="X19" s="21">
+      <c r="Y19" s="20">
         <v>33.200000000000003</v>
       </c>
     </row>
-    <row r="20" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="A20" s="30" t="s">
+    <row r="20" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A20" s="28" t="s">
         <v>37</v>
       </c>
       <c r="B20" s="12" t="s">
@@ -2812,65 +2872,68 @@
         <v>0.05</v>
       </c>
       <c r="F20" s="13">
+        <v>5</v>
+      </c>
+      <c r="G20" s="13">
         <v>8865</v>
       </c>
-      <c r="G20" s="16">
+      <c r="H20" s="16">
         <v>20.100000000000001</v>
       </c>
-      <c r="H20" s="14">
+      <c r="I20" s="14">
         <v>4.5</v>
       </c>
-      <c r="I20" s="14">
+      <c r="J20" s="14">
         <v>5.45</v>
       </c>
-      <c r="J20" s="14">
+      <c r="K20" s="14">
         <v>5.71</v>
       </c>
-      <c r="K20" s="16">
+      <c r="L20" s="16">
         <v>24.1</v>
       </c>
-      <c r="L20" s="16">
+      <c r="M20" s="16">
         <v>37.200000000000003</v>
       </c>
-      <c r="M20" s="16">
+      <c r="N20" s="16">
         <v>31</v>
       </c>
-      <c r="N20" s="16">
+      <c r="O20" s="16">
         <v>90.8</v>
       </c>
-      <c r="O20" s="16">
+      <c r="P20" s="16">
         <v>3.7</v>
       </c>
-      <c r="P20" s="16">
+      <c r="Q20" s="16">
         <v>17.100000000000001</v>
       </c>
-      <c r="Q20" s="16">
+      <c r="R20" s="16">
         <v>16.8</v>
       </c>
-      <c r="R20" s="16">
+      <c r="S20" s="16">
         <v>9.6999999999999993</v>
       </c>
-      <c r="S20" s="13">
+      <c r="T20" s="13">
         <v>51112</v>
       </c>
-      <c r="T20" s="13">
+      <c r="U20" s="13">
         <v>33</v>
       </c>
-      <c r="U20" s="13">
+      <c r="V20" s="13">
         <v>29</v>
       </c>
-      <c r="V20" s="13" t="s">
+      <c r="W20" s="13" t="s">
         <v>228</v>
       </c>
-      <c r="W20" s="13" t="s">
+      <c r="X20" s="13" t="s">
         <v>234</v>
       </c>
-      <c r="X20" s="13">
+      <c r="Y20" s="13">
         <v>81.400000000000006</v>
       </c>
     </row>
-    <row r="21" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="A21" s="30" t="s">
+    <row r="21" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A21" s="28" t="s">
         <v>39</v>
       </c>
       <c r="B21" s="12" t="s">
@@ -2886,71 +2949,74 @@
         <v>0.11</v>
       </c>
       <c r="F21" s="13">
+        <v>7</v>
+      </c>
+      <c r="G21" s="13">
         <v>7693</v>
       </c>
-      <c r="G21" s="16">
+      <c r="H21" s="16">
         <v>19.3</v>
       </c>
-      <c r="H21" s="14">
+      <c r="I21" s="14">
         <v>4.26</v>
       </c>
-      <c r="I21" s="14">
+      <c r="J21" s="14">
         <v>5.1100000000000003</v>
       </c>
-      <c r="J21" s="14">
+      <c r="K21" s="14">
         <v>6.71</v>
       </c>
-      <c r="K21" s="16">
+      <c r="L21" s="16">
         <v>21.4</v>
       </c>
-      <c r="L21" s="16">
+      <c r="M21" s="16">
         <v>39</v>
       </c>
-      <c r="M21" s="16">
+      <c r="N21" s="16">
         <v>30.2</v>
       </c>
-      <c r="N21" s="16">
+      <c r="O21" s="16">
         <v>91.2</v>
       </c>
-      <c r="O21" s="16">
+      <c r="P21" s="16">
         <v>4.2</v>
       </c>
-      <c r="P21" s="16">
+      <c r="Q21" s="16">
         <v>13.6</v>
       </c>
-      <c r="Q21" s="16">
+      <c r="R21" s="16">
         <v>15.2</v>
       </c>
-      <c r="R21" s="16">
+      <c r="S21" s="16">
         <v>8.8000000000000007</v>
       </c>
-      <c r="S21" s="13">
+      <c r="T21" s="13">
         <v>38086</v>
-      </c>
-      <c r="T21" s="13">
-        <v>26</v>
       </c>
       <c r="U21" s="13">
         <v>26</v>
       </c>
-      <c r="V21" s="13" t="s">
+      <c r="V21" s="13">
+        <v>26</v>
+      </c>
+      <c r="W21" s="13" t="s">
         <v>239</v>
       </c>
-      <c r="W21" s="13" t="s">
+      <c r="X21" s="13" t="s">
         <v>240</v>
       </c>
-      <c r="X21" s="13">
+      <c r="Y21" s="13">
         <v>68.599999999999994</v>
       </c>
     </row>
-    <row r="22" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="A22" s="30" t="s">
+    <row r="22" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A22" s="28" t="s">
         <v>41</v>
       </c>
       <c r="B22" s="12" t="s">
         <v>1</v>
       </c>
-      <c r="C22" s="25" t="s">
+      <c r="C22" s="12" t="s">
         <v>42</v>
       </c>
       <c r="D22" s="13">
@@ -2960,65 +3026,68 @@
         <v>1.1200000000000001</v>
       </c>
       <c r="F22" s="13">
+        <v>7</v>
+      </c>
+      <c r="G22" s="13">
         <v>4186</v>
       </c>
-      <c r="G22" s="16">
+      <c r="H22" s="16">
         <v>12.7</v>
       </c>
-      <c r="H22" s="14">
+      <c r="I22" s="14">
         <v>3.2</v>
       </c>
-      <c r="I22" s="14">
+      <c r="J22" s="14">
         <v>4.26</v>
       </c>
-      <c r="J22" s="14">
+      <c r="K22" s="14">
         <v>6.19</v>
       </c>
-      <c r="K22" s="16">
+      <c r="L22" s="16">
         <v>15</v>
       </c>
-      <c r="L22" s="16">
+      <c r="M22" s="16">
         <v>30.4</v>
       </c>
-      <c r="M22" s="16">
+      <c r="N22" s="16">
         <v>20.9</v>
       </c>
-      <c r="N22" s="16">
+      <c r="O22" s="16">
         <v>96.4</v>
       </c>
-      <c r="O22" s="16">
+      <c r="P22" s="16">
         <v>3.1</v>
       </c>
-      <c r="P22" s="16">
+      <c r="Q22" s="16">
         <v>5</v>
       </c>
-      <c r="Q22" s="16">
+      <c r="R22" s="16">
         <v>8.4</v>
       </c>
-      <c r="R22" s="16">
+      <c r="S22" s="16">
         <v>10</v>
       </c>
-      <c r="S22" s="13">
+      <c r="T22" s="13">
         <v>209176</v>
       </c>
-      <c r="T22" s="13">
-        <v>1</v>
-      </c>
       <c r="U22" s="13">
         <v>1</v>
       </c>
-      <c r="V22" s="13" t="s">
+      <c r="V22" s="13">
+        <v>1</v>
+      </c>
+      <c r="W22" s="13" t="s">
         <v>237</v>
       </c>
-      <c r="W22" s="13" t="s">
+      <c r="X22" s="13" t="s">
         <v>238</v>
       </c>
-      <c r="X22" s="13">
+      <c r="Y22" s="13">
         <v>52</v>
       </c>
     </row>
-    <row r="23" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="A23" s="30" t="s">
+    <row r="23" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A23" s="28" t="s">
         <v>43</v>
       </c>
       <c r="B23" s="12" t="s">
@@ -3034,65 +3103,68 @@
         <v>-0.03</v>
       </c>
       <c r="F23" s="13">
+        <v>9</v>
+      </c>
+      <c r="G23" s="13">
         <v>8799</v>
       </c>
-      <c r="G23" s="16">
+      <c r="H23" s="16">
         <v>19.8</v>
       </c>
-      <c r="H23" s="14">
+      <c r="I23" s="14">
         <v>4.28</v>
       </c>
-      <c r="I23" s="14">
+      <c r="J23" s="14">
         <v>5.18</v>
       </c>
-      <c r="J23" s="14">
+      <c r="K23" s="14">
         <v>7.88</v>
       </c>
-      <c r="K23" s="16">
+      <c r="L23" s="16">
         <v>23</v>
       </c>
-      <c r="L23" s="16">
+      <c r="M23" s="16">
         <v>40.4</v>
       </c>
-      <c r="M23" s="16">
+      <c r="N23" s="16">
         <v>28.8</v>
       </c>
-      <c r="N23" s="16">
+      <c r="O23" s="16">
         <v>91.8</v>
       </c>
-      <c r="O23" s="16">
+      <c r="P23" s="16">
         <v>4.9000000000000004</v>
       </c>
-      <c r="P23" s="16">
+      <c r="Q23" s="16">
         <v>19.2</v>
       </c>
-      <c r="Q23" s="16">
+      <c r="R23" s="16">
         <v>12.5</v>
       </c>
-      <c r="R23" s="16">
+      <c r="S23" s="16">
         <v>8.8000000000000007</v>
       </c>
-      <c r="S23" s="13">
+      <c r="T23" s="13">
         <v>74266</v>
       </c>
-      <c r="T23" s="13">
+      <c r="U23" s="13">
         <v>55</v>
       </c>
-      <c r="U23" s="13">
+      <c r="V23" s="13">
         <v>39</v>
       </c>
-      <c r="V23" s="13" t="s">
+      <c r="W23" s="13" t="s">
         <v>230</v>
       </c>
-      <c r="W23" s="13" t="s">
+      <c r="X23" s="13" t="s">
         <v>231</v>
       </c>
-      <c r="X23" s="13">
+      <c r="Y23" s="13">
         <v>55.8</v>
       </c>
     </row>
-    <row r="24" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="A24" s="30" t="s">
+    <row r="24" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A24" s="28" t="s">
         <v>45</v>
       </c>
       <c r="B24" s="12" t="s">
@@ -3108,65 +3180,68 @@
         <v>0.24</v>
       </c>
       <c r="F24" s="13">
+        <v>8</v>
+      </c>
+      <c r="G24" s="13">
         <v>7039</v>
       </c>
-      <c r="G24" s="16">
+      <c r="H24" s="16">
         <v>18</v>
       </c>
-      <c r="H24" s="14">
+      <c r="I24" s="14">
         <v>4.05</v>
       </c>
-      <c r="I24" s="14">
+      <c r="J24" s="14">
         <v>5.03</v>
       </c>
-      <c r="J24" s="14">
+      <c r="K24" s="14">
         <v>7.96</v>
       </c>
-      <c r="K24" s="16">
+      <c r="L24" s="16">
         <v>20.8</v>
       </c>
-      <c r="L24" s="16">
+      <c r="M24" s="16">
         <v>38.4</v>
       </c>
-      <c r="M24" s="16">
+      <c r="N24" s="16">
         <v>28.5</v>
       </c>
-      <c r="N24" s="16">
+      <c r="O24" s="16">
         <v>92.6</v>
       </c>
-      <c r="O24" s="16">
+      <c r="P24" s="16">
         <v>3.7</v>
       </c>
-      <c r="P24" s="16">
+      <c r="Q24" s="16">
         <v>11.5</v>
       </c>
-      <c r="Q24" s="16">
+      <c r="R24" s="16">
         <v>10.199999999999999</v>
       </c>
-      <c r="R24" s="16">
+      <c r="S24" s="16">
         <v>9.6999999999999993</v>
       </c>
-      <c r="S24" s="13">
+      <c r="T24" s="13">
         <v>157574</v>
       </c>
-      <c r="T24" s="13">
+      <c r="U24" s="13">
         <v>12</v>
       </c>
-      <c r="U24" s="13">
+      <c r="V24" s="13">
         <v>16</v>
       </c>
-      <c r="V24" s="13" t="s">
+      <c r="W24" s="13" t="s">
         <v>237</v>
       </c>
-      <c r="W24" s="13" t="s">
+      <c r="X24" s="13" t="s">
         <v>238</v>
       </c>
-      <c r="X24" s="13">
+      <c r="Y24" s="13">
         <v>60.7</v>
       </c>
     </row>
-    <row r="25" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="A25" s="30" t="s">
+    <row r="25" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A25" s="28" t="s">
         <v>47</v>
       </c>
       <c r="B25" s="12" t="s">
@@ -3182,65 +3257,68 @@
         <v>-0.41</v>
       </c>
       <c r="F25" s="13">
+        <v>8</v>
+      </c>
+      <c r="G25" s="13">
         <v>12012</v>
       </c>
-      <c r="G25" s="16">
+      <c r="H25" s="16">
         <v>22.9</v>
       </c>
-      <c r="H25" s="14">
+      <c r="I25" s="14">
         <v>4.8499999999999996</v>
       </c>
-      <c r="I25" s="14">
+      <c r="J25" s="14">
         <v>5.67</v>
       </c>
-      <c r="J25" s="14">
+      <c r="K25" s="14">
         <v>8.27</v>
       </c>
-      <c r="K25" s="16">
+      <c r="L25" s="16">
         <v>27.1</v>
       </c>
-      <c r="L25" s="16">
+      <c r="M25" s="16">
         <v>41.6</v>
       </c>
-      <c r="M25" s="16">
+      <c r="N25" s="16">
         <v>34.700000000000003</v>
       </c>
-      <c r="N25" s="16">
+      <c r="O25" s="16">
         <v>85.7</v>
       </c>
-      <c r="O25" s="16">
+      <c r="P25" s="16">
         <v>3.9</v>
       </c>
-      <c r="P25" s="16">
+      <c r="Q25" s="16">
         <v>21</v>
       </c>
-      <c r="Q25" s="16">
+      <c r="R25" s="16">
         <v>10.199999999999999</v>
       </c>
-      <c r="R25" s="16">
+      <c r="S25" s="16">
         <v>9.1999999999999993</v>
       </c>
-      <c r="S25" s="13">
+      <c r="T25" s="13">
         <v>28525</v>
       </c>
-      <c r="T25" s="13">
+      <c r="U25" s="13">
         <v>71</v>
       </c>
-      <c r="U25" s="13">
+      <c r="V25" s="13">
         <v>74</v>
       </c>
-      <c r="V25" s="13" t="s">
+      <c r="W25" s="13" t="s">
         <v>237</v>
       </c>
-      <c r="W25" s="13" t="s">
+      <c r="X25" s="13" t="s">
         <v>238</v>
       </c>
-      <c r="X25" s="13">
+      <c r="Y25" s="13">
         <v>76.5</v>
       </c>
     </row>
-    <row r="26" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="A26" s="30" t="s">
+    <row r="26" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A26" s="28" t="s">
         <v>49</v>
       </c>
       <c r="B26" s="12" t="s">
@@ -3256,65 +3334,68 @@
         <v>0.19</v>
       </c>
       <c r="F26" s="13">
+        <v>9</v>
+      </c>
+      <c r="G26" s="13">
         <v>8285</v>
       </c>
-      <c r="G26" s="16">
+      <c r="H26" s="16">
         <v>18.100000000000001</v>
       </c>
-      <c r="H26" s="14">
+      <c r="I26" s="14">
         <v>4.0999999999999996</v>
       </c>
-      <c r="I26" s="14">
+      <c r="J26" s="14">
         <v>4.87</v>
       </c>
-      <c r="J26" s="14">
+      <c r="K26" s="14">
         <v>9.16</v>
       </c>
-      <c r="K26" s="16">
+      <c r="L26" s="16">
         <v>20.3</v>
       </c>
-      <c r="L26" s="16">
+      <c r="M26" s="16">
         <v>35.9</v>
       </c>
-      <c r="M26" s="16">
+      <c r="N26" s="16">
         <v>28</v>
       </c>
-      <c r="N26" s="16">
+      <c r="O26" s="16">
         <v>91.2</v>
       </c>
-      <c r="O26" s="16">
+      <c r="P26" s="16">
         <v>3.5</v>
       </c>
-      <c r="P26" s="16">
+      <c r="Q26" s="16">
         <v>18.600000000000001</v>
       </c>
-      <c r="Q26" s="16">
+      <c r="R26" s="16">
         <v>9.4</v>
       </c>
-      <c r="R26" s="16">
+      <c r="S26" s="16">
         <v>10</v>
       </c>
-      <c r="S26" s="13">
+      <c r="T26" s="13">
         <v>1316756</v>
       </c>
-      <c r="T26" s="13">
+      <c r="U26" s="13">
         <v>48</v>
       </c>
-      <c r="U26" s="13">
+      <c r="V26" s="13">
         <v>38</v>
       </c>
-      <c r="V26" s="13" t="s">
+      <c r="W26" s="13" t="s">
         <v>237</v>
       </c>
-      <c r="W26" s="13" t="s">
+      <c r="X26" s="13" t="s">
         <v>238</v>
       </c>
-      <c r="X26" s="13">
+      <c r="Y26" s="13">
         <v>34.6</v>
       </c>
     </row>
-    <row r="27" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="A27" s="30" t="s">
+    <row r="27" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A27" s="28" t="s">
         <v>51</v>
       </c>
       <c r="B27" s="12" t="s">
@@ -3330,65 +3411,68 @@
         <v>0.27</v>
       </c>
       <c r="F27" s="13">
+        <v>7</v>
+      </c>
+      <c r="G27" s="13">
         <v>7471</v>
       </c>
-      <c r="G27" s="16">
+      <c r="H27" s="16">
         <v>19.100000000000001</v>
       </c>
-      <c r="H27" s="14">
+      <c r="I27" s="14">
         <v>4.21</v>
       </c>
-      <c r="I27" s="14">
+      <c r="J27" s="14">
         <v>5.1100000000000003</v>
       </c>
-      <c r="J27" s="14">
+      <c r="K27" s="14">
         <v>6.89</v>
       </c>
-      <c r="K27" s="16">
+      <c r="L27" s="16">
         <v>21.1</v>
       </c>
-      <c r="L27" s="16">
+      <c r="M27" s="16">
         <v>37.5</v>
       </c>
-      <c r="M27" s="16">
+      <c r="N27" s="16">
         <v>30.1</v>
       </c>
-      <c r="N27" s="16">
+      <c r="O27" s="16">
         <v>91.3</v>
       </c>
-      <c r="O27" s="16">
+      <c r="P27" s="16">
         <v>4.0999999999999996</v>
       </c>
-      <c r="P27" s="16">
+      <c r="Q27" s="16">
         <v>9.8000000000000007</v>
       </c>
-      <c r="Q27" s="16">
+      <c r="R27" s="16">
         <v>14.5</v>
       </c>
-      <c r="R27" s="16">
+      <c r="S27" s="16">
         <v>8.9</v>
       </c>
-      <c r="S27" s="13">
+      <c r="T27" s="13">
         <v>42126</v>
-      </c>
-      <c r="T27" s="13">
-        <v>15</v>
       </c>
       <c r="U27" s="13">
         <v>15</v>
       </c>
-      <c r="V27" s="13" t="s">
+      <c r="V27" s="13">
+        <v>15</v>
+      </c>
+      <c r="W27" s="13" t="s">
         <v>239</v>
       </c>
-      <c r="W27" s="13" t="s">
+      <c r="X27" s="13" t="s">
         <v>240</v>
       </c>
-      <c r="X27" s="13">
+      <c r="Y27" s="13">
         <v>69.900000000000006</v>
       </c>
     </row>
-    <row r="28" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="A28" s="30" t="s">
+    <row r="28" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A28" s="28" t="s">
         <v>53</v>
       </c>
       <c r="B28" s="12" t="s">
@@ -3404,65 +3488,68 @@
         <v>-0.36</v>
       </c>
       <c r="F28" s="13">
+        <v>10</v>
+      </c>
+      <c r="G28" s="13">
         <v>12844</v>
       </c>
-      <c r="G28" s="16">
+      <c r="H28" s="16">
         <v>22.9</v>
       </c>
-      <c r="H28" s="14">
+      <c r="I28" s="14">
         <v>4.93</v>
       </c>
-      <c r="I28" s="14">
+      <c r="J28" s="14">
         <v>5.74</v>
       </c>
-      <c r="J28" s="14">
+      <c r="K28" s="14">
         <v>9.4600000000000009</v>
       </c>
-      <c r="K28" s="16">
+      <c r="L28" s="16">
         <v>26.5</v>
       </c>
-      <c r="L28" s="16">
+      <c r="M28" s="16">
         <v>41.5</v>
       </c>
-      <c r="M28" s="16">
+      <c r="N28" s="16">
         <v>34.5</v>
       </c>
-      <c r="N28" s="16">
+      <c r="O28" s="16">
         <v>84</v>
       </c>
-      <c r="O28" s="16">
+      <c r="P28" s="16">
         <v>5.4</v>
       </c>
-      <c r="P28" s="16">
+      <c r="Q28" s="16">
         <v>24.9</v>
       </c>
-      <c r="Q28" s="16">
+      <c r="R28" s="16">
         <v>13.4</v>
       </c>
-      <c r="R28" s="16">
+      <c r="S28" s="16">
         <v>8.4</v>
       </c>
-      <c r="S28" s="13">
+      <c r="T28" s="13">
         <v>29898</v>
       </c>
-      <c r="T28" s="13">
+      <c r="U28" s="13">
         <v>86</v>
       </c>
-      <c r="U28" s="13">
+      <c r="V28" s="13">
         <v>78</v>
       </c>
-      <c r="V28" s="13" t="s">
+      <c r="W28" s="13" t="s">
         <v>232</v>
       </c>
-      <c r="W28" s="13" t="s">
+      <c r="X28" s="13" t="s">
         <v>233</v>
       </c>
-      <c r="X28" s="13">
+      <c r="Y28" s="13">
         <v>78.7</v>
       </c>
     </row>
-    <row r="29" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="A29" s="30" t="s">
+    <row r="29" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A29" s="28" t="s">
         <v>55</v>
       </c>
       <c r="B29" s="12" t="s">
@@ -3478,65 +3565,68 @@
         <v>0.55000000000000004</v>
       </c>
       <c r="F29" s="13">
+        <v>6</v>
+      </c>
+      <c r="G29" s="13">
         <v>5305</v>
       </c>
-      <c r="G29" s="16">
+      <c r="H29" s="16">
         <v>16</v>
       </c>
-      <c r="H29" s="14">
+      <c r="I29" s="14">
         <v>3.8</v>
       </c>
-      <c r="I29" s="14">
+      <c r="J29" s="14">
         <v>4.87</v>
       </c>
-      <c r="J29" s="14">
+      <c r="K29" s="14">
         <v>6.52</v>
       </c>
-      <c r="K29" s="16">
+      <c r="L29" s="16">
         <v>19.100000000000001</v>
       </c>
-      <c r="L29" s="16">
+      <c r="M29" s="16">
         <v>35.299999999999997</v>
       </c>
-      <c r="M29" s="16">
+      <c r="N29" s="16">
         <v>26.2</v>
       </c>
-      <c r="N29" s="16">
+      <c r="O29" s="16">
         <v>90.2</v>
       </c>
-      <c r="O29" s="16">
+      <c r="P29" s="16">
         <v>3.5</v>
       </c>
-      <c r="P29" s="16">
+      <c r="Q29" s="16">
         <v>6.2</v>
       </c>
-      <c r="Q29" s="16">
+      <c r="R29" s="16">
         <v>9.6</v>
       </c>
-      <c r="R29" s="16">
+      <c r="S29" s="16">
         <v>9.1</v>
       </c>
-      <c r="S29" s="13">
+      <c r="T29" s="13">
         <v>93648</v>
-      </c>
-      <c r="T29" s="13">
-        <v>3</v>
       </c>
       <c r="U29" s="13">
         <v>3</v>
       </c>
-      <c r="V29" s="13" t="s">
+      <c r="V29" s="13">
+        <v>3</v>
+      </c>
+      <c r="W29" s="13" t="s">
         <v>230</v>
       </c>
-      <c r="W29" s="13" t="s">
+      <c r="X29" s="13" t="s">
         <v>231</v>
       </c>
-      <c r="X29" s="13">
+      <c r="Y29" s="13">
         <v>60.8</v>
       </c>
     </row>
-    <row r="30" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="A30" s="30" t="s">
+    <row r="30" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A30" s="28" t="s">
         <v>57</v>
       </c>
       <c r="B30" s="12" t="s">
@@ -3552,65 +3642,68 @@
         <v>0.5</v>
       </c>
       <c r="F30" s="13">
+        <v>7</v>
+      </c>
+      <c r="G30" s="13">
         <v>6822</v>
       </c>
-      <c r="G30" s="16">
+      <c r="H30" s="16">
         <v>16.8</v>
       </c>
-      <c r="H30" s="14">
+      <c r="I30" s="14">
         <v>3.89</v>
       </c>
-      <c r="I30" s="14">
+      <c r="J30" s="14">
         <v>4.8499999999999996</v>
       </c>
-      <c r="J30" s="14">
+      <c r="K30" s="14">
         <v>7.4</v>
       </c>
-      <c r="K30" s="16">
+      <c r="L30" s="16">
         <v>18.600000000000001</v>
       </c>
-      <c r="L30" s="16">
+      <c r="M30" s="16">
         <v>37</v>
       </c>
-      <c r="M30" s="16">
+      <c r="N30" s="16">
         <v>26.1</v>
       </c>
-      <c r="N30" s="16">
+      <c r="O30" s="16">
         <v>93.8</v>
       </c>
-      <c r="O30" s="16">
+      <c r="P30" s="16">
         <v>3.7</v>
       </c>
-      <c r="P30" s="16">
+      <c r="Q30" s="16">
         <v>12.9</v>
       </c>
-      <c r="Q30" s="16">
+      <c r="R30" s="16">
         <v>9.8000000000000007</v>
       </c>
-      <c r="R30" s="16">
+      <c r="S30" s="16">
         <v>10.3</v>
       </c>
-      <c r="S30" s="13">
+      <c r="T30" s="13">
         <v>168936</v>
       </c>
-      <c r="T30" s="13">
+      <c r="U30" s="13">
         <v>14</v>
       </c>
-      <c r="U30" s="13">
+      <c r="V30" s="13">
         <v>11</v>
       </c>
-      <c r="V30" s="13" t="s">
+      <c r="W30" s="13" t="s">
         <v>228</v>
       </c>
-      <c r="W30" s="13" t="s">
+      <c r="X30" s="13" t="s">
         <v>234</v>
       </c>
-      <c r="X30" s="13">
+      <c r="Y30" s="13">
         <v>58.3</v>
       </c>
     </row>
-    <row r="31" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="A31" s="30" t="s">
+    <row r="31" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A31" s="28" t="s">
         <v>59</v>
       </c>
       <c r="B31" s="12" t="s">
@@ -3626,65 +3719,68 @@
         <v>-0.42</v>
       </c>
       <c r="F31" s="13">
+        <v>8</v>
+      </c>
+      <c r="G31" s="13">
         <v>10031</v>
       </c>
-      <c r="G31" s="16">
+      <c r="H31" s="16">
         <v>22.2</v>
       </c>
-      <c r="H31" s="14">
+      <c r="I31" s="14">
         <v>4.96</v>
       </c>
-      <c r="I31" s="14">
+      <c r="J31" s="14">
         <v>5.77</v>
       </c>
-      <c r="J31" s="14">
+      <c r="K31" s="14">
         <v>8.4499999999999993</v>
       </c>
-      <c r="K31" s="16">
+      <c r="L31" s="16">
         <v>26.2</v>
       </c>
-      <c r="L31" s="16">
+      <c r="M31" s="16">
         <v>37.6</v>
       </c>
-      <c r="M31" s="16">
+      <c r="N31" s="16">
         <v>32.200000000000003</v>
       </c>
-      <c r="N31" s="16">
+      <c r="O31" s="16">
         <v>85.5</v>
       </c>
-      <c r="O31" s="16">
+      <c r="P31" s="16">
         <v>5.5</v>
       </c>
-      <c r="P31" s="16">
+      <c r="Q31" s="16">
         <v>22.2</v>
       </c>
-      <c r="Q31" s="16">
+      <c r="R31" s="16">
         <v>15.7</v>
       </c>
-      <c r="R31" s="16">
+      <c r="S31" s="16">
         <v>8.6</v>
       </c>
-      <c r="S31" s="13">
+      <c r="T31" s="13">
         <v>38874</v>
       </c>
-      <c r="T31" s="13">
+      <c r="U31" s="13">
         <v>75</v>
       </c>
-      <c r="U31" s="13">
+      <c r="V31" s="13">
         <v>67</v>
       </c>
-      <c r="V31" s="13" t="s">
+      <c r="W31" s="13" t="s">
         <v>232</v>
       </c>
-      <c r="W31" s="13" t="s">
+      <c r="X31" s="13" t="s">
         <v>235</v>
       </c>
-      <c r="X31" s="13">
+      <c r="Y31" s="13">
         <v>74.900000000000006</v>
       </c>
     </row>
-    <row r="32" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="A32" s="30" t="s">
+    <row r="32" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A32" s="28" t="s">
         <v>61</v>
       </c>
       <c r="B32" s="12" t="s">
@@ -3700,65 +3796,68 @@
         <v>0.16</v>
       </c>
       <c r="F32" s="13">
+        <v>10</v>
+      </c>
+      <c r="G32" s="13">
         <v>9110</v>
       </c>
-      <c r="G32" s="16">
+      <c r="H32" s="16">
         <v>18.2</v>
       </c>
-      <c r="H32" s="14">
+      <c r="I32" s="14">
         <v>4.1500000000000004</v>
       </c>
-      <c r="I32" s="14">
+      <c r="J32" s="14">
         <v>4.97</v>
       </c>
-      <c r="J32" s="14">
+      <c r="K32" s="14">
         <v>9.48</v>
       </c>
-      <c r="K32" s="16">
+      <c r="L32" s="16">
         <v>20</v>
       </c>
-      <c r="L32" s="16">
+      <c r="M32" s="16">
         <v>33.700000000000003</v>
       </c>
-      <c r="M32" s="16">
+      <c r="N32" s="16">
         <v>27.6</v>
       </c>
-      <c r="N32" s="16">
+      <c r="O32" s="16">
         <v>91.4</v>
       </c>
-      <c r="O32" s="16">
+      <c r="P32" s="16">
         <v>3.8</v>
       </c>
-      <c r="P32" s="16">
+      <c r="Q32" s="16">
         <v>20.8</v>
       </c>
-      <c r="Q32" s="16">
+      <c r="R32" s="16">
         <v>10.5</v>
       </c>
-      <c r="R32" s="16">
+      <c r="S32" s="16">
         <v>12</v>
       </c>
-      <c r="S32" s="13">
+      <c r="T32" s="13">
         <v>817472</v>
       </c>
-      <c r="T32" s="13">
+      <c r="U32" s="13">
         <v>61</v>
       </c>
-      <c r="U32" s="13">
+      <c r="V32" s="13">
         <v>45</v>
       </c>
-      <c r="V32" s="13" t="s">
+      <c r="W32" s="13" t="s">
         <v>226</v>
       </c>
-      <c r="W32" s="13" t="s">
+      <c r="X32" s="13" t="s">
         <v>227</v>
       </c>
-      <c r="X32" s="13">
+      <c r="Y32" s="13">
         <v>41.4</v>
       </c>
     </row>
-    <row r="33" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="A33" s="30" t="s">
+    <row r="33" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A33" s="28" t="s">
         <v>63</v>
       </c>
       <c r="B33" s="12" t="s">
@@ -3774,65 +3873,68 @@
         <v>0.35</v>
       </c>
       <c r="F33" s="13">
+        <v>8</v>
+      </c>
+      <c r="G33" s="13">
         <v>7731</v>
       </c>
-      <c r="G33" s="16">
+      <c r="H33" s="16">
         <v>17.5</v>
       </c>
-      <c r="H33" s="14">
+      <c r="I33" s="14">
         <v>4.07</v>
       </c>
-      <c r="I33" s="14">
+      <c r="J33" s="14">
         <v>5.01</v>
       </c>
-      <c r="J33" s="14">
+      <c r="K33" s="14">
         <v>7.95</v>
       </c>
-      <c r="K33" s="16">
+      <c r="L33" s="16">
         <v>21.1</v>
       </c>
-      <c r="L33" s="16">
+      <c r="M33" s="16">
         <v>32.200000000000003</v>
       </c>
-      <c r="M33" s="16">
+      <c r="N33" s="16">
         <v>26.9</v>
       </c>
-      <c r="N33" s="16">
+      <c r="O33" s="16">
         <v>92.5</v>
       </c>
-      <c r="O33" s="16">
+      <c r="P33" s="16">
         <v>3.2</v>
       </c>
-      <c r="P33" s="16">
+      <c r="Q33" s="16">
         <v>11.2</v>
       </c>
-      <c r="Q33" s="16">
+      <c r="R33" s="16">
         <v>12.4</v>
       </c>
-      <c r="R33" s="16">
+      <c r="S33" s="16">
         <v>8.8000000000000007</v>
       </c>
-      <c r="S33" s="13">
+      <c r="T33" s="13">
         <v>75782</v>
       </c>
-      <c r="T33" s="13">
+      <c r="U33" s="13">
         <v>24</v>
       </c>
-      <c r="U33" s="13">
+      <c r="V33" s="13">
         <v>14</v>
       </c>
-      <c r="V33" s="13" t="s">
+      <c r="W33" s="13" t="s">
         <v>239</v>
       </c>
-      <c r="W33" s="13" t="s">
+      <c r="X33" s="13" t="s">
         <v>240</v>
       </c>
-      <c r="X33" s="13">
+      <c r="Y33" s="13">
         <v>67.8</v>
       </c>
     </row>
-    <row r="34" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="A34" s="30" t="s">
+    <row r="34" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A34" s="28" t="s">
         <v>65</v>
       </c>
       <c r="B34" s="12" t="s">
@@ -3848,65 +3950,68 @@
         <v>-0.17</v>
       </c>
       <c r="F34" s="13">
+        <v>8</v>
+      </c>
+      <c r="G34" s="13">
         <v>7650</v>
       </c>
-      <c r="G34" s="16">
+      <c r="H34" s="16">
         <v>20.7</v>
       </c>
-      <c r="H34" s="14">
+      <c r="I34" s="14">
         <v>4.66</v>
       </c>
-      <c r="I34" s="14">
+      <c r="J34" s="14">
         <v>5.55</v>
       </c>
-      <c r="J34" s="14">
+      <c r="K34" s="14">
         <v>7.5</v>
       </c>
-      <c r="K34" s="16">
+      <c r="L34" s="16">
         <v>24.5</v>
       </c>
-      <c r="L34" s="16">
+      <c r="M34" s="16">
         <v>38.5</v>
       </c>
-      <c r="M34" s="16">
+      <c r="N34" s="16">
         <v>31</v>
       </c>
-      <c r="N34" s="16">
+      <c r="O34" s="16">
         <v>89.5</v>
       </c>
-      <c r="O34" s="16">
+      <c r="P34" s="16">
         <v>4.2</v>
       </c>
-      <c r="P34" s="16">
+      <c r="Q34" s="16">
         <v>18.2</v>
       </c>
-      <c r="Q34" s="16">
+      <c r="R34" s="16">
         <v>11.8</v>
       </c>
-      <c r="R34" s="16">
+      <c r="S34" s="16">
         <v>8.9</v>
       </c>
-      <c r="S34" s="13">
+      <c r="T34" s="13">
         <v>31365</v>
       </c>
-      <c r="T34" s="13">
+      <c r="U34" s="13">
         <v>52</v>
       </c>
-      <c r="U34" s="13">
+      <c r="V34" s="13">
         <v>64</v>
       </c>
-      <c r="V34" s="13" t="s">
+      <c r="W34" s="13" t="s">
         <v>237</v>
       </c>
-      <c r="W34" s="13" t="s">
+      <c r="X34" s="13" t="s">
         <v>238</v>
       </c>
-      <c r="X34" s="13">
+      <c r="Y34" s="13">
         <v>76</v>
       </c>
     </row>
-    <row r="35" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="A35" s="30" t="s">
+    <row r="35" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A35" s="28" t="s">
         <v>67</v>
       </c>
       <c r="B35" s="12" t="s">
@@ -3922,65 +4027,68 @@
         <v>-0.38</v>
       </c>
       <c r="F35" s="13">
+        <v>6</v>
+      </c>
+      <c r="G35" s="13">
         <v>7855</v>
       </c>
-      <c r="G35" s="16">
+      <c r="H35" s="16">
         <v>22</v>
       </c>
-      <c r="H35" s="14">
+      <c r="I35" s="14">
         <v>4.82</v>
       </c>
-      <c r="I35" s="14">
+      <c r="J35" s="14">
         <v>5.71</v>
       </c>
-      <c r="J35" s="14">
+      <c r="K35" s="14">
         <v>5.5</v>
       </c>
-      <c r="K35" s="16">
+      <c r="L35" s="16">
         <v>27.8</v>
       </c>
-      <c r="L35" s="16">
+      <c r="M35" s="16">
         <v>36.5</v>
       </c>
-      <c r="M35" s="16">
+      <c r="N35" s="16">
         <v>32.799999999999997</v>
       </c>
-      <c r="N35" s="16">
+      <c r="O35" s="16">
         <v>86.8</v>
       </c>
-      <c r="O35" s="16">
+      <c r="P35" s="16">
         <v>5.3</v>
       </c>
-      <c r="P35" s="16">
+      <c r="Q35" s="16">
         <v>21.7</v>
       </c>
-      <c r="Q35" s="16">
+      <c r="R35" s="16">
         <v>16.600000000000001</v>
       </c>
-      <c r="R35" s="16">
+      <c r="S35" s="16">
         <v>7.6</v>
       </c>
-      <c r="S35" s="13">
+      <c r="T35" s="13">
         <v>15040</v>
       </c>
-      <c r="T35" s="13">
+      <c r="U35" s="13">
         <v>44</v>
       </c>
-      <c r="U35" s="13">
+      <c r="V35" s="13">
         <v>68</v>
       </c>
-      <c r="V35" s="13" t="s">
+      <c r="W35" s="13" t="s">
         <v>232</v>
       </c>
-      <c r="W35" s="13" t="s">
+      <c r="X35" s="13" t="s">
         <v>235</v>
       </c>
-      <c r="X35" s="13">
+      <c r="Y35" s="13">
         <v>76.2</v>
       </c>
     </row>
-    <row r="36" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="A36" s="30" t="s">
+    <row r="36" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A36" s="28" t="s">
         <v>69</v>
       </c>
       <c r="B36" s="12" t="s">
@@ -3996,65 +4104,68 @@
         <v>0.1</v>
       </c>
       <c r="F36" s="13">
+        <v>8</v>
+      </c>
+      <c r="G36" s="13">
         <v>7720</v>
       </c>
-      <c r="G36" s="16">
+      <c r="H36" s="16">
         <v>18.7</v>
       </c>
-      <c r="H36" s="14">
+      <c r="I36" s="14">
         <v>4.1500000000000004</v>
       </c>
-      <c r="I36" s="14">
+      <c r="J36" s="14">
         <v>5.08</v>
       </c>
-      <c r="J36" s="14">
+      <c r="K36" s="14">
         <v>6.63</v>
       </c>
-      <c r="K36" s="16">
+      <c r="L36" s="16">
         <v>21.6</v>
       </c>
-      <c r="L36" s="16">
+      <c r="M36" s="16">
         <v>36.4</v>
       </c>
-      <c r="M36" s="16">
+      <c r="N36" s="16">
         <v>27.2</v>
       </c>
-      <c r="N36" s="16">
+      <c r="O36" s="16">
         <v>93.5</v>
       </c>
-      <c r="O36" s="16">
+      <c r="P36" s="16">
         <v>4.5999999999999996</v>
       </c>
-      <c r="P36" s="16">
+      <c r="Q36" s="16">
         <v>10.4</v>
       </c>
-      <c r="Q36" s="16">
+      <c r="R36" s="16">
         <v>15.6</v>
       </c>
-      <c r="R36" s="16">
+      <c r="S36" s="16">
         <v>8.8000000000000007</v>
       </c>
-      <c r="S36" s="13">
+      <c r="T36" s="13">
         <v>27005</v>
-      </c>
-      <c r="T36" s="13">
-        <v>10</v>
       </c>
       <c r="U36" s="13">
         <v>10</v>
       </c>
-      <c r="V36" s="13" t="s">
+      <c r="V36" s="13">
+        <v>10</v>
+      </c>
+      <c r="W36" s="13" t="s">
         <v>239</v>
       </c>
-      <c r="W36" s="13" t="s">
+      <c r="X36" s="13" t="s">
         <v>240</v>
       </c>
-      <c r="X36" s="13">
+      <c r="Y36" s="13">
         <v>72</v>
       </c>
     </row>
-    <row r="37" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="A37" s="30" t="s">
+    <row r="37" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A37" s="28" t="s">
         <v>71</v>
       </c>
       <c r="B37" s="12" t="s">
@@ -4070,65 +4181,68 @@
         <v>-0.44</v>
       </c>
       <c r="F37" s="13">
+        <v>8</v>
+      </c>
+      <c r="G37" s="13">
         <v>9672</v>
       </c>
-      <c r="G37" s="16">
+      <c r="H37" s="16">
         <v>23.4</v>
       </c>
-      <c r="H37" s="14">
+      <c r="I37" s="14">
         <v>5.07</v>
       </c>
-      <c r="I37" s="14">
+      <c r="J37" s="14">
         <v>5.86</v>
       </c>
-      <c r="J37" s="14">
+      <c r="K37" s="14">
         <v>7.56</v>
       </c>
-      <c r="K37" s="16">
+      <c r="L37" s="16">
         <v>28.5</v>
       </c>
-      <c r="L37" s="16">
+      <c r="M37" s="16">
         <v>41</v>
       </c>
-      <c r="M37" s="16">
+      <c r="N37" s="16">
         <v>34.299999999999997</v>
       </c>
-      <c r="N37" s="16">
+      <c r="O37" s="16">
         <v>85.1</v>
       </c>
-      <c r="O37" s="16">
+      <c r="P37" s="16">
         <v>5.2</v>
       </c>
-      <c r="P37" s="16">
+      <c r="Q37" s="16">
         <v>22.7</v>
       </c>
-      <c r="Q37" s="16">
+      <c r="R37" s="16">
         <v>12.3</v>
       </c>
-      <c r="R37" s="16">
+      <c r="S37" s="16">
         <v>8.8000000000000007</v>
       </c>
-      <c r="S37" s="13">
+      <c r="T37" s="13">
         <v>43161</v>
       </c>
-      <c r="T37" s="13">
+      <c r="U37" s="13">
         <v>79</v>
       </c>
-      <c r="U37" s="13">
+      <c r="V37" s="13">
         <v>70</v>
       </c>
-      <c r="V37" s="13" t="s">
+      <c r="W37" s="13" t="s">
         <v>226</v>
       </c>
-      <c r="W37" s="13" t="s">
+      <c r="X37" s="13" t="s">
         <v>227</v>
       </c>
-      <c r="X37" s="13">
+      <c r="Y37" s="13">
         <v>80.7</v>
       </c>
     </row>
-    <row r="38" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="A38" s="30" t="s">
+    <row r="38" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A38" s="28" t="s">
         <v>73</v>
       </c>
       <c r="B38" s="12" t="s">
@@ -4144,65 +4258,68 @@
         <v>-0.25</v>
       </c>
       <c r="F38" s="13">
+        <v>8</v>
+      </c>
+      <c r="G38" s="13">
         <v>9566</v>
       </c>
-      <c r="G38" s="16">
+      <c r="H38" s="16">
         <v>21.5</v>
       </c>
-      <c r="H38" s="14">
+      <c r="I38" s="14">
         <v>4.72</v>
       </c>
-      <c r="I38" s="14">
+      <c r="J38" s="14">
         <v>5.62</v>
       </c>
-      <c r="J38" s="14">
+      <c r="K38" s="14">
         <v>6.99</v>
       </c>
-      <c r="K38" s="16">
+      <c r="L38" s="16">
         <v>25.9</v>
       </c>
-      <c r="L38" s="16">
+      <c r="M38" s="16">
         <v>37.1</v>
       </c>
-      <c r="M38" s="16">
+      <c r="N38" s="16">
         <v>32.6</v>
       </c>
-      <c r="N38" s="16">
+      <c r="O38" s="16">
         <v>89.1</v>
       </c>
-      <c r="O38" s="16">
+      <c r="P38" s="16">
         <v>4.5999999999999996</v>
       </c>
-      <c r="P38" s="16">
+      <c r="Q38" s="16">
         <v>21.3</v>
       </c>
-      <c r="Q38" s="16">
+      <c r="R38" s="16">
         <v>8.8000000000000007</v>
       </c>
-      <c r="R38" s="16">
+      <c r="S38" s="16">
         <v>8.5</v>
       </c>
-      <c r="S38" s="13">
+      <c r="T38" s="13">
         <v>28264</v>
       </c>
-      <c r="T38" s="13">
+      <c r="U38" s="13">
         <v>54</v>
       </c>
-      <c r="U38" s="13">
+      <c r="V38" s="13">
         <v>46</v>
       </c>
-      <c r="V38" s="13" t="s">
+      <c r="W38" s="13" t="s">
         <v>237</v>
       </c>
-      <c r="W38" s="13" t="s">
+      <c r="X38" s="13" t="s">
         <v>238</v>
       </c>
-      <c r="X38" s="13">
+      <c r="Y38" s="13">
         <v>71.099999999999994</v>
       </c>
     </row>
-    <row r="39" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="A39" s="30" t="s">
+    <row r="39" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A39" s="28" t="s">
         <v>75</v>
       </c>
       <c r="B39" s="12" t="s">
@@ -4218,65 +4335,68 @@
         <v>-0.3</v>
       </c>
       <c r="F39" s="13">
+        <v>4</v>
+      </c>
+      <c r="G39" s="13">
         <v>5011</v>
       </c>
-      <c r="G39" s="16">
+      <c r="H39" s="16">
         <v>24.9</v>
       </c>
-      <c r="H39" s="14">
+      <c r="I39" s="14">
         <v>5.17</v>
       </c>
-      <c r="I39" s="14">
+      <c r="J39" s="14">
         <v>6.02</v>
       </c>
-      <c r="J39" s="14">
+      <c r="K39" s="14">
         <v>4.26</v>
       </c>
-      <c r="K39" s="16">
+      <c r="L39" s="16">
         <v>28.9</v>
       </c>
-      <c r="L39" s="16">
+      <c r="M39" s="16">
         <v>35.799999999999997</v>
       </c>
-      <c r="M39" s="16">
+      <c r="N39" s="16">
         <v>33.5</v>
       </c>
-      <c r="N39" s="16">
+      <c r="O39" s="16">
         <v>56.9</v>
       </c>
-      <c r="O39" s="16">
+      <c r="P39" s="16">
         <v>3</v>
       </c>
-      <c r="P39" s="16">
+      <c r="Q39" s="16">
         <v>13</v>
       </c>
-      <c r="Q39" s="16">
+      <c r="R39" s="16">
         <v>11.4</v>
       </c>
-      <c r="R39" s="16">
+      <c r="S39" s="16">
         <v>9.1999999999999993</v>
       </c>
-      <c r="S39" s="13">
+      <c r="T39" s="13">
         <v>43959</v>
       </c>
-      <c r="T39" s="13">
+      <c r="U39" s="13">
         <v>5</v>
       </c>
-      <c r="U39" s="13">
+      <c r="V39" s="13">
         <v>35</v>
       </c>
-      <c r="V39" s="13" t="s">
+      <c r="W39" s="13" t="s">
         <v>230</v>
       </c>
-      <c r="W39" s="13" t="s">
+      <c r="X39" s="13" t="s">
         <v>231</v>
       </c>
-      <c r="X39" s="13">
+      <c r="Y39" s="13">
         <v>82.2</v>
       </c>
     </row>
-    <row r="40" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="A40" s="30" t="s">
+    <row r="40" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A40" s="28" t="s">
         <v>77</v>
       </c>
       <c r="B40" s="12" t="s">
@@ -4292,65 +4412,68 @@
         <v>-0.23</v>
       </c>
       <c r="F40" s="13">
+        <v>7</v>
+      </c>
+      <c r="G40" s="13">
         <v>8818</v>
       </c>
-      <c r="G40" s="16">
+      <c r="H40" s="16">
         <v>21.3</v>
       </c>
-      <c r="H40" s="14">
+      <c r="I40" s="14">
         <v>4.7</v>
       </c>
-      <c r="I40" s="14">
+      <c r="J40" s="14">
         <v>5.49</v>
       </c>
-      <c r="J40" s="14">
+      <c r="K40" s="14">
         <v>6.71</v>
       </c>
-      <c r="K40" s="16">
+      <c r="L40" s="16">
         <v>24</v>
       </c>
-      <c r="L40" s="16">
+      <c r="M40" s="16">
         <v>36.4</v>
       </c>
-      <c r="M40" s="16">
+      <c r="N40" s="16">
         <v>31.6</v>
       </c>
-      <c r="N40" s="16">
+      <c r="O40" s="16">
         <v>88.5</v>
       </c>
-      <c r="O40" s="16">
+      <c r="P40" s="16">
         <v>5.7</v>
       </c>
-      <c r="P40" s="16">
+      <c r="Q40" s="16">
         <v>15.3</v>
       </c>
-      <c r="Q40" s="16">
+      <c r="R40" s="16">
         <v>11.8</v>
       </c>
-      <c r="R40" s="16">
+      <c r="S40" s="16">
         <v>8.6999999999999993</v>
       </c>
-      <c r="S40" s="13">
+      <c r="T40" s="13">
         <v>58266</v>
       </c>
-      <c r="T40" s="13">
+      <c r="U40" s="13">
         <v>32</v>
       </c>
-      <c r="U40" s="13">
+      <c r="V40" s="13">
         <v>54</v>
       </c>
-      <c r="V40" s="13" t="s">
+      <c r="W40" s="13" t="s">
         <v>230</v>
       </c>
-      <c r="W40" s="13" t="s">
+      <c r="X40" s="13" t="s">
         <v>231</v>
       </c>
-      <c r="X40" s="13">
+      <c r="Y40" s="13">
         <v>70.900000000000006</v>
       </c>
     </row>
-    <row r="41" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="A41" s="30" t="s">
+    <row r="41" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A41" s="28" t="s">
         <v>79</v>
       </c>
       <c r="B41" s="12" t="s">
@@ -4366,65 +4489,68 @@
         <v>-0.48</v>
       </c>
       <c r="F41" s="13">
+        <v>8</v>
+      </c>
+      <c r="G41" s="13">
         <v>12004</v>
       </c>
-      <c r="G41" s="16">
+      <c r="H41" s="16">
         <v>24.3</v>
       </c>
-      <c r="H41" s="14">
+      <c r="I41" s="14">
         <v>5.09</v>
       </c>
-      <c r="I41" s="14">
+      <c r="J41" s="14">
         <v>5.88</v>
       </c>
-      <c r="J41" s="14">
+      <c r="K41" s="14">
         <v>8.5399999999999991</v>
       </c>
-      <c r="K41" s="16">
+      <c r="L41" s="16">
         <v>26.4</v>
       </c>
-      <c r="L41" s="16">
+      <c r="M41" s="16">
         <v>40.799999999999997</v>
       </c>
-      <c r="M41" s="16">
+      <c r="N41" s="16">
         <v>33.9</v>
       </c>
-      <c r="N41" s="16">
+      <c r="O41" s="16">
         <v>83.5</v>
       </c>
-      <c r="O41" s="16">
+      <c r="P41" s="16">
         <v>6.2</v>
       </c>
-      <c r="P41" s="16">
+      <c r="Q41" s="16">
         <v>26.7</v>
       </c>
-      <c r="Q41" s="16">
+      <c r="R41" s="16">
         <v>11.4</v>
       </c>
-      <c r="R41" s="16">
+      <c r="S41" s="16">
         <v>8.3000000000000007</v>
       </c>
-      <c r="S41" s="13">
+      <c r="T41" s="13">
         <v>32413</v>
-      </c>
-      <c r="T41" s="13">
-        <v>82</v>
       </c>
       <c r="U41" s="13">
         <v>82</v>
       </c>
-      <c r="V41" s="13" t="s">
+      <c r="V41" s="13">
+        <v>82</v>
+      </c>
+      <c r="W41" s="13" t="s">
         <v>232</v>
       </c>
-      <c r="W41" s="13" t="s">
+      <c r="X41" s="13" t="s">
         <v>233</v>
       </c>
-      <c r="X41" s="13">
+      <c r="Y41" s="13">
         <v>77.900000000000006</v>
       </c>
     </row>
-    <row r="42" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="A42" s="30" t="s">
+    <row r="42" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A42" s="28" t="s">
         <v>81</v>
       </c>
       <c r="B42" s="12" t="s">
@@ -4440,65 +4566,68 @@
         <v>-0.43</v>
       </c>
       <c r="F42" s="13">
+        <v>9</v>
+      </c>
+      <c r="G42" s="13">
         <v>10642</v>
       </c>
-      <c r="G42" s="16">
+      <c r="H42" s="16">
         <v>21.6</v>
       </c>
-      <c r="H42" s="14">
+      <c r="I42" s="14">
         <v>4.75</v>
       </c>
-      <c r="I42" s="14">
+      <c r="J42" s="14">
         <v>5.62</v>
       </c>
-      <c r="J42" s="14">
+      <c r="K42" s="14">
         <v>8.5299999999999994</v>
       </c>
-      <c r="K42" s="16">
+      <c r="L42" s="16">
         <v>26.4</v>
       </c>
-      <c r="L42" s="16">
+      <c r="M42" s="16">
         <v>38.1</v>
       </c>
-      <c r="M42" s="16">
+      <c r="N42" s="16">
         <v>33.9</v>
       </c>
-      <c r="N42" s="16">
+      <c r="O42" s="16">
         <v>91</v>
       </c>
-      <c r="O42" s="16">
+      <c r="P42" s="16">
         <v>5.9</v>
       </c>
-      <c r="P42" s="16">
+      <c r="Q42" s="16">
         <v>25.4</v>
       </c>
-      <c r="Q42" s="16">
+      <c r="R42" s="16">
         <v>18.8</v>
       </c>
-      <c r="R42" s="16">
+      <c r="S42" s="16">
         <v>9.1999999999999993</v>
       </c>
-      <c r="S42" s="13">
+      <c r="T42" s="13">
         <v>65324</v>
       </c>
-      <c r="T42" s="13">
+      <c r="U42" s="13">
         <v>78</v>
       </c>
-      <c r="U42" s="13">
+      <c r="V42" s="13">
         <v>76</v>
       </c>
-      <c r="V42" s="13" t="s">
+      <c r="W42" s="13" t="s">
         <v>232</v>
       </c>
-      <c r="W42" s="13" t="s">
+      <c r="X42" s="13" t="s">
         <v>235</v>
       </c>
-      <c r="X42" s="13">
+      <c r="Y42" s="13">
         <v>70.5</v>
       </c>
     </row>
-    <row r="43" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="A43" s="30" t="s">
+    <row r="43" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A43" s="28" t="s">
         <v>83</v>
       </c>
       <c r="B43" s="12" t="s">
@@ -4514,65 +4643,68 @@
         <v>0.1</v>
       </c>
       <c r="F43" s="13">
+        <v>7</v>
+      </c>
+      <c r="G43" s="13">
         <v>7276</v>
       </c>
-      <c r="G43" s="16">
+      <c r="H43" s="16">
         <v>18.3</v>
       </c>
-      <c r="H43" s="14">
+      <c r="I43" s="14">
         <v>4.3499999999999996</v>
       </c>
-      <c r="I43" s="14">
+      <c r="J43" s="14">
         <v>5.34</v>
       </c>
-      <c r="J43" s="14">
+      <c r="K43" s="14">
         <v>7.06</v>
       </c>
-      <c r="K43" s="16">
+      <c r="L43" s="16">
         <v>21.7</v>
       </c>
-      <c r="L43" s="16">
+      <c r="M43" s="16">
         <v>36.799999999999997</v>
       </c>
-      <c r="M43" s="16">
+      <c r="N43" s="16">
         <v>28.4</v>
       </c>
-      <c r="N43" s="16">
+      <c r="O43" s="16">
         <v>91.3</v>
       </c>
-      <c r="O43" s="16">
+      <c r="P43" s="16">
         <v>3.9</v>
       </c>
-      <c r="P43" s="16">
+      <c r="Q43" s="16">
         <v>16.7</v>
       </c>
-      <c r="Q43" s="16">
+      <c r="R43" s="16">
         <v>13.2</v>
       </c>
-      <c r="R43" s="16">
+      <c r="S43" s="16">
         <v>9.1</v>
       </c>
-      <c r="S43" s="13">
+      <c r="T43" s="13">
         <v>62321</v>
       </c>
-      <c r="T43" s="13">
+      <c r="U43" s="13">
         <v>38</v>
       </c>
-      <c r="U43" s="13">
+      <c r="V43" s="13">
         <v>23</v>
       </c>
-      <c r="V43" s="13" t="s">
+      <c r="W43" s="13" t="s">
         <v>237</v>
       </c>
-      <c r="W43" s="13" t="s">
+      <c r="X43" s="13" t="s">
         <v>238</v>
       </c>
-      <c r="X43" s="13">
+      <c r="Y43" s="13">
         <v>71.099999999999994</v>
       </c>
     </row>
-    <row r="44" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="A44" s="30" t="s">
+    <row r="44" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A44" s="28" t="s">
         <v>85</v>
       </c>
       <c r="B44" s="12" t="s">
@@ -4588,65 +4720,68 @@
         <v>0.3</v>
       </c>
       <c r="F44" s="13">
+        <v>7</v>
+      </c>
+      <c r="G44" s="13">
         <v>7239</v>
       </c>
-      <c r="G44" s="16">
+      <c r="H44" s="16">
         <v>16.8</v>
       </c>
-      <c r="H44" s="14">
+      <c r="I44" s="14">
         <v>3.96</v>
       </c>
-      <c r="I44" s="14">
+      <c r="J44" s="14">
         <v>4.95</v>
       </c>
-      <c r="J44" s="14">
+      <c r="K44" s="14">
         <v>7.22</v>
       </c>
-      <c r="K44" s="16">
+      <c r="L44" s="16">
         <v>20.5</v>
       </c>
-      <c r="L44" s="16">
+      <c r="M44" s="16">
         <v>34.4</v>
       </c>
-      <c r="M44" s="16">
+      <c r="N44" s="16">
         <v>26.2</v>
       </c>
-      <c r="N44" s="16">
+      <c r="O44" s="16">
         <v>92.3</v>
       </c>
-      <c r="O44" s="16">
+      <c r="P44" s="16">
         <v>3.7</v>
       </c>
-      <c r="P44" s="16">
+      <c r="Q44" s="16">
         <v>11.2</v>
       </c>
-      <c r="Q44" s="16">
+      <c r="R44" s="16">
         <v>8.6</v>
       </c>
-      <c r="R44" s="16">
+      <c r="S44" s="16">
         <v>6.5</v>
       </c>
-      <c r="S44" s="13">
+      <c r="T44" s="13">
         <v>230148</v>
       </c>
-      <c r="T44" s="13">
+      <c r="U44" s="13">
         <v>17</v>
       </c>
-      <c r="U44" s="13">
+      <c r="V44" s="13">
         <v>12</v>
       </c>
-      <c r="V44" s="13" t="s">
+      <c r="W44" s="13" t="s">
         <v>230</v>
       </c>
-      <c r="W44" s="13" t="s">
+      <c r="X44" s="13" t="s">
         <v>231</v>
       </c>
-      <c r="X44" s="13">
+      <c r="Y44" s="13">
         <v>56</v>
       </c>
     </row>
-    <row r="45" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="A45" s="30" t="s">
+    <row r="45" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A45" s="28" t="s">
         <v>87</v>
       </c>
       <c r="B45" s="12" t="s">
@@ -4662,65 +4797,68 @@
         <v>-0.48</v>
       </c>
       <c r="F45" s="13">
+        <v>10</v>
+      </c>
+      <c r="G45" s="13">
         <v>11569</v>
       </c>
-      <c r="G45" s="16">
+      <c r="H45" s="16">
         <v>23.5</v>
       </c>
-      <c r="H45" s="14">
+      <c r="I45" s="14">
         <v>4.91</v>
       </c>
-      <c r="I45" s="14">
+      <c r="J45" s="14">
         <v>5.75</v>
       </c>
-      <c r="J45" s="14">
+      <c r="K45" s="14">
         <v>8.83</v>
       </c>
-      <c r="K45" s="16">
+      <c r="L45" s="16">
         <v>27.2</v>
       </c>
-      <c r="L45" s="16">
+      <c r="M45" s="16">
         <v>39.799999999999997</v>
       </c>
-      <c r="M45" s="16">
+      <c r="N45" s="16">
         <v>35.299999999999997</v>
       </c>
-      <c r="N45" s="16">
+      <c r="O45" s="16">
         <v>87.5</v>
       </c>
-      <c r="O45" s="16">
+      <c r="P45" s="16">
         <v>5.2</v>
       </c>
-      <c r="P45" s="16">
+      <c r="Q45" s="16">
         <v>22.6</v>
       </c>
-      <c r="Q45" s="16">
+      <c r="R45" s="16">
         <v>8.6999999999999993</v>
       </c>
-      <c r="R45" s="16">
+      <c r="S45" s="16">
         <v>6.8</v>
       </c>
-      <c r="S45" s="13">
+      <c r="T45" s="13">
         <v>59463</v>
       </c>
-      <c r="T45" s="13">
+      <c r="U45" s="13">
         <v>83</v>
       </c>
-      <c r="U45" s="13">
+      <c r="V45" s="13">
         <v>72</v>
       </c>
-      <c r="V45" s="13" t="s">
+      <c r="W45" s="13" t="s">
         <v>232</v>
       </c>
-      <c r="W45" s="13" t="s">
+      <c r="X45" s="13" t="s">
         <v>233</v>
       </c>
-      <c r="X45" s="13">
+      <c r="Y45" s="13">
         <v>73.900000000000006</v>
       </c>
     </row>
-    <row r="46" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="A46" s="30" t="s">
+    <row r="46" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A46" s="28" t="s">
         <v>89</v>
       </c>
       <c r="B46" s="12" t="s">
@@ -4736,65 +4874,68 @@
         <v>0.3</v>
       </c>
       <c r="F46" s="13">
+        <v>7</v>
+      </c>
+      <c r="G46" s="13">
         <v>7203</v>
       </c>
-      <c r="G46" s="16">
+      <c r="H46" s="16">
         <v>18.3</v>
       </c>
-      <c r="H46" s="14">
+      <c r="I46" s="14">
         <v>4.2</v>
       </c>
-      <c r="I46" s="14">
+      <c r="J46" s="14">
         <v>5.17</v>
       </c>
-      <c r="J46" s="14">
+      <c r="K46" s="14">
         <v>7.7</v>
       </c>
-      <c r="K46" s="16">
+      <c r="L46" s="16">
         <v>21.8</v>
       </c>
-      <c r="L46" s="16">
+      <c r="M46" s="16">
         <v>34.799999999999997</v>
       </c>
-      <c r="M46" s="16">
+      <c r="N46" s="16">
         <v>29.5</v>
       </c>
-      <c r="N46" s="16">
+      <c r="O46" s="16">
         <v>91.5</v>
       </c>
-      <c r="O46" s="16">
+      <c r="P46" s="16">
         <v>3.7</v>
       </c>
-      <c r="P46" s="16">
+      <c r="Q46" s="16">
         <v>12.4</v>
       </c>
-      <c r="Q46" s="16">
+      <c r="R46" s="16">
         <v>10</v>
       </c>
-      <c r="R46" s="16">
+      <c r="S46" s="16">
         <v>9.8000000000000007</v>
       </c>
-      <c r="S46" s="13">
+      <c r="T46" s="13">
         <v>176862</v>
       </c>
-      <c r="T46" s="13">
+      <c r="U46" s="13">
         <v>25</v>
       </c>
-      <c r="U46" s="13">
+      <c r="V46" s="13">
         <v>19</v>
       </c>
-      <c r="V46" s="13" t="s">
+      <c r="W46" s="13" t="s">
         <v>237</v>
       </c>
-      <c r="W46" s="13" t="s">
+      <c r="X46" s="13" t="s">
         <v>238</v>
       </c>
-      <c r="X46" s="13">
+      <c r="Y46" s="13">
         <v>63.7</v>
       </c>
     </row>
-    <row r="47" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="A47" s="30" t="s">
+    <row r="47" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A47" s="28" t="s">
         <v>91</v>
       </c>
       <c r="B47" s="12" t="s">
@@ -4810,65 +4951,68 @@
         <v>7.0000000000000007E-2</v>
       </c>
       <c r="F47" s="13">
+        <v>7</v>
+      </c>
+      <c r="G47" s="13">
         <v>9427</v>
       </c>
-      <c r="G47" s="16">
+      <c r="H47" s="16">
         <v>19.399999999999999</v>
       </c>
-      <c r="H47" s="14">
+      <c r="I47" s="14">
         <v>4.4400000000000004</v>
       </c>
-      <c r="I47" s="14">
+      <c r="J47" s="14">
         <v>5.4</v>
       </c>
-      <c r="J47" s="14">
+      <c r="K47" s="14">
         <v>7.31</v>
       </c>
-      <c r="K47" s="16">
+      <c r="L47" s="16">
         <v>24.1</v>
       </c>
-      <c r="L47" s="16">
+      <c r="M47" s="16">
         <v>37.700000000000003</v>
       </c>
-      <c r="M47" s="16">
+      <c r="N47" s="16">
         <v>31.4</v>
       </c>
-      <c r="N47" s="16">
+      <c r="O47" s="16">
         <v>92.6</v>
       </c>
-      <c r="O47" s="16">
+      <c r="P47" s="16">
         <v>3.6</v>
       </c>
-      <c r="P47" s="16">
+      <c r="Q47" s="16">
         <v>14.6</v>
       </c>
-      <c r="Q47" s="16">
+      <c r="R47" s="16">
         <v>12.5</v>
       </c>
-      <c r="R47" s="16">
+      <c r="S47" s="16">
         <v>9.3000000000000007</v>
       </c>
-      <c r="S47" s="13">
+      <c r="T47" s="13">
         <v>45672</v>
       </c>
-      <c r="T47" s="13">
+      <c r="U47" s="13">
         <v>42</v>
       </c>
-      <c r="U47" s="13">
+      <c r="V47" s="13">
         <v>27</v>
       </c>
-      <c r="V47" s="13" t="s">
+      <c r="W47" s="13" t="s">
         <v>228</v>
       </c>
-      <c r="W47" s="13" t="s">
+      <c r="X47" s="13" t="s">
         <v>234</v>
       </c>
-      <c r="X47" s="13">
+      <c r="Y47" s="13">
         <v>76.400000000000006</v>
       </c>
     </row>
-    <row r="48" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="A48" s="30" t="s">
+    <row r="48" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A48" s="28" t="s">
         <v>93</v>
       </c>
       <c r="B48" s="12" t="s">
@@ -4884,65 +5028,68 @@
         <v>-0.05</v>
       </c>
       <c r="F48" s="13">
+        <v>9</v>
+      </c>
+      <c r="G48" s="13">
         <v>7932</v>
       </c>
-      <c r="G48" s="16">
+      <c r="H48" s="16">
         <v>19.899999999999999</v>
       </c>
-      <c r="H48" s="14">
+      <c r="I48" s="14">
         <v>4.28</v>
       </c>
-      <c r="I48" s="14">
+      <c r="J48" s="14">
         <v>5.07</v>
       </c>
-      <c r="J48" s="14">
+      <c r="K48" s="14">
         <v>8.1300000000000008</v>
       </c>
-      <c r="K48" s="16">
+      <c r="L48" s="16">
         <v>21.6</v>
       </c>
-      <c r="L48" s="16">
+      <c r="M48" s="16">
         <v>39</v>
       </c>
-      <c r="M48" s="16">
+      <c r="N48" s="16">
         <v>30.9</v>
       </c>
-      <c r="N48" s="16">
+      <c r="O48" s="16">
         <v>89.7</v>
       </c>
-      <c r="O48" s="16">
+      <c r="P48" s="16">
         <v>4.3</v>
       </c>
-      <c r="P48" s="16">
+      <c r="Q48" s="16">
         <v>20.3</v>
       </c>
-      <c r="Q48" s="16">
+      <c r="R48" s="16">
         <v>9.6</v>
       </c>
-      <c r="R48" s="16">
+      <c r="S48" s="16">
         <v>7.4</v>
       </c>
-      <c r="S48" s="13">
+      <c r="T48" s="13">
         <v>309833</v>
       </c>
-      <c r="T48" s="13">
+      <c r="U48" s="13">
         <v>43</v>
       </c>
-      <c r="U48" s="13">
+      <c r="V48" s="13">
         <v>51</v>
       </c>
-      <c r="V48" s="13" t="s">
+      <c r="W48" s="13" t="s">
         <v>230</v>
       </c>
-      <c r="W48" s="13" t="s">
+      <c r="X48" s="13" t="s">
         <v>231</v>
       </c>
-      <c r="X48" s="13">
+      <c r="Y48" s="13">
         <v>51.7</v>
       </c>
     </row>
-    <row r="49" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="A49" s="30" t="s">
+    <row r="49" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A49" s="28" t="s">
         <v>95</v>
       </c>
       <c r="B49" s="12" t="s">
@@ -4958,65 +5105,68 @@
         <v>-0.14000000000000001</v>
       </c>
       <c r="F49" s="13">
+        <v>10</v>
+      </c>
+      <c r="G49" s="13">
         <v>9889</v>
       </c>
-      <c r="G49" s="16">
+      <c r="H49" s="16">
         <v>21.7</v>
       </c>
-      <c r="H49" s="14">
+      <c r="I49" s="14">
         <v>4.58</v>
       </c>
-      <c r="I49" s="14">
+      <c r="J49" s="14">
         <v>5.28</v>
       </c>
-      <c r="J49" s="14">
+      <c r="K49" s="14">
         <v>9.7200000000000006</v>
       </c>
-      <c r="K49" s="16">
+      <c r="L49" s="16">
         <v>23.5</v>
       </c>
-      <c r="L49" s="16">
+      <c r="M49" s="16">
         <v>37.299999999999997</v>
       </c>
-      <c r="M49" s="16">
+      <c r="N49" s="16">
         <v>31.6</v>
       </c>
-      <c r="N49" s="16">
+      <c r="O49" s="16">
         <v>89.3</v>
       </c>
-      <c r="O49" s="16">
+      <c r="P49" s="16">
         <v>4.7</v>
       </c>
-      <c r="P49" s="16">
+      <c r="Q49" s="16">
         <v>26.3</v>
       </c>
-      <c r="Q49" s="16">
+      <c r="R49" s="16">
         <v>9.6</v>
       </c>
-      <c r="R49" s="16">
+      <c r="S49" s="16">
         <v>8.8000000000000007</v>
       </c>
-      <c r="S49" s="13">
+      <c r="T49" s="13">
         <v>428348</v>
       </c>
-      <c r="T49" s="13">
+      <c r="U49" s="13">
         <v>69</v>
       </c>
-      <c r="U49" s="13">
+      <c r="V49" s="13">
         <v>79</v>
       </c>
-      <c r="V49" s="13" t="s">
+      <c r="W49" s="13" t="s">
         <v>239</v>
       </c>
-      <c r="W49" s="13" t="s">
+      <c r="X49" s="13" t="s">
         <v>240</v>
       </c>
-      <c r="X49" s="13">
+      <c r="Y49" s="13">
         <v>42.5</v>
       </c>
     </row>
-    <row r="50" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="A50" s="30" t="s">
+    <row r="50" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A50" s="28" t="s">
         <v>97</v>
       </c>
       <c r="B50" s="12" t="s">
@@ -5032,65 +5182,68 @@
         <v>0.04</v>
       </c>
       <c r="F50" s="13">
+        <v>7</v>
+      </c>
+      <c r="G50" s="13">
         <v>8240</v>
       </c>
-      <c r="G50" s="16">
+      <c r="H50" s="16">
         <v>19.600000000000001</v>
       </c>
-      <c r="H50" s="14">
+      <c r="I50" s="14">
         <v>4.32</v>
       </c>
-      <c r="I50" s="14">
+      <c r="J50" s="14">
         <v>5.19</v>
       </c>
-      <c r="J50" s="14">
+      <c r="K50" s="14">
         <v>7.4</v>
       </c>
-      <c r="K50" s="16">
+      <c r="L50" s="16">
         <v>23.1</v>
       </c>
-      <c r="L50" s="16">
+      <c r="M50" s="16">
         <v>38.799999999999997</v>
       </c>
-      <c r="M50" s="16">
+      <c r="N50" s="16">
         <v>30.3</v>
       </c>
-      <c r="N50" s="16">
+      <c r="O50" s="16">
         <v>87</v>
       </c>
-      <c r="O50" s="16">
+      <c r="P50" s="16">
         <v>3.4</v>
       </c>
-      <c r="P50" s="16">
+      <c r="Q50" s="16">
         <v>12.4</v>
       </c>
-      <c r="Q50" s="16">
+      <c r="R50" s="16">
         <v>9.1999999999999993</v>
       </c>
-      <c r="R50" s="16">
+      <c r="S50" s="16">
         <v>9.9</v>
       </c>
-      <c r="S50" s="13">
+      <c r="T50" s="13">
         <v>44731</v>
       </c>
-      <c r="T50" s="13">
+      <c r="U50" s="13">
         <v>41</v>
       </c>
-      <c r="U50" s="13">
+      <c r="V50" s="13">
         <v>36</v>
       </c>
-      <c r="V50" s="13" t="s">
+      <c r="W50" s="13" t="s">
         <v>237</v>
       </c>
-      <c r="W50" s="13" t="s">
+      <c r="X50" s="13" t="s">
         <v>238</v>
       </c>
-      <c r="X50" s="13">
+      <c r="Y50" s="13">
         <v>70.400000000000006</v>
       </c>
     </row>
-    <row r="51" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="A51" s="30" t="s">
+    <row r="51" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A51" s="28" t="s">
         <v>99</v>
       </c>
       <c r="B51" s="12" t="s">
@@ -5106,65 +5259,68 @@
         <v>-0.22</v>
       </c>
       <c r="F51" s="13">
+        <v>11</v>
+      </c>
+      <c r="G51" s="13">
         <v>9341</v>
       </c>
-      <c r="G51" s="16">
+      <c r="H51" s="16">
         <v>21.9</v>
       </c>
-      <c r="H51" s="14">
+      <c r="I51" s="14">
         <v>4.55</v>
       </c>
-      <c r="I51" s="14">
+      <c r="J51" s="14">
         <v>5.26</v>
       </c>
-      <c r="J51" s="14">
+      <c r="K51" s="14">
         <v>10.69</v>
       </c>
-      <c r="K51" s="16">
+      <c r="L51" s="16">
         <v>23.5</v>
       </c>
-      <c r="L51" s="16">
+      <c r="M51" s="16">
         <v>39.6</v>
       </c>
-      <c r="M51" s="16">
+      <c r="N51" s="16">
         <v>32.700000000000003</v>
       </c>
-      <c r="N51" s="16">
+      <c r="O51" s="16">
         <v>90.9</v>
       </c>
-      <c r="O51" s="16">
+      <c r="P51" s="16">
         <v>5.7</v>
       </c>
-      <c r="P51" s="16">
+      <c r="Q51" s="16">
         <v>27.4</v>
       </c>
-      <c r="Q51" s="16">
+      <c r="R51" s="16">
         <v>12.7</v>
       </c>
-      <c r="R51" s="16">
+      <c r="S51" s="16">
         <v>8.4</v>
       </c>
-      <c r="S51" s="13">
+      <c r="T51" s="13">
         <v>228682</v>
       </c>
-      <c r="T51" s="13">
+      <c r="U51" s="13">
         <v>67</v>
       </c>
-      <c r="U51" s="13">
+      <c r="V51" s="13">
         <v>63</v>
       </c>
-      <c r="V51" s="13" t="s">
+      <c r="W51" s="13" t="s">
         <v>230</v>
       </c>
-      <c r="W51" s="13" t="s">
+      <c r="X51" s="13" t="s">
         <v>236</v>
       </c>
-      <c r="X51" s="13">
+      <c r="Y51" s="13">
         <v>53.6</v>
       </c>
     </row>
-    <row r="52" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="A52" s="30" t="s">
+    <row r="52" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A52" s="28" t="s">
         <v>101</v>
       </c>
       <c r="B52" s="12" t="s">
@@ -5180,65 +5336,68 @@
         <v>-0.46</v>
       </c>
       <c r="F52" s="13">
+        <v>8</v>
+      </c>
+      <c r="G52" s="13">
         <v>10216</v>
       </c>
-      <c r="G52" s="16">
+      <c r="H52" s="16">
         <v>22.7</v>
       </c>
-      <c r="H52" s="14">
+      <c r="I52" s="14">
         <v>4.83</v>
       </c>
-      <c r="I52" s="14">
+      <c r="J52" s="14">
         <v>5.56</v>
       </c>
-      <c r="J52" s="14">
+      <c r="K52" s="14">
         <v>8.83</v>
       </c>
-      <c r="K52" s="16">
+      <c r="L52" s="16">
         <v>27.8</v>
       </c>
-      <c r="L52" s="16">
+      <c r="M52" s="16">
         <v>38.299999999999997</v>
       </c>
-      <c r="M52" s="16">
+      <c r="N52" s="16">
         <v>33.9</v>
       </c>
-      <c r="N52" s="16">
+      <c r="O52" s="16">
         <v>87.9</v>
       </c>
-      <c r="O52" s="16">
+      <c r="P52" s="16">
         <v>4.0999999999999996</v>
       </c>
-      <c r="P52" s="16">
+      <c r="Q52" s="16">
         <v>20.3</v>
       </c>
-      <c r="Q52" s="16">
+      <c r="R52" s="16">
         <v>12.6</v>
       </c>
-      <c r="R52" s="16">
+      <c r="S52" s="16">
         <v>9.1999999999999993</v>
       </c>
-      <c r="S52" s="13">
+      <c r="T52" s="13">
         <v>65092</v>
       </c>
-      <c r="T52" s="13">
+      <c r="U52" s="13">
         <v>76</v>
       </c>
-      <c r="U52" s="13">
+      <c r="V52" s="13">
         <v>85</v>
       </c>
-      <c r="V52" s="13" t="s">
+      <c r="W52" s="13" t="s">
         <v>237</v>
       </c>
-      <c r="W52" s="13" t="s">
+      <c r="X52" s="13" t="s">
         <v>238</v>
       </c>
-      <c r="X52" s="13">
+      <c r="Y52" s="13">
         <v>69.5</v>
       </c>
     </row>
-    <row r="53" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="A53" s="30" t="s">
+    <row r="53" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A53" s="28" t="s">
         <v>103</v>
       </c>
       <c r="B53" s="12" t="s">
@@ -5254,65 +5413,68 @@
         <v>0.59</v>
       </c>
       <c r="F53" s="13">
+        <v>6</v>
+      </c>
+      <c r="G53" s="13">
         <v>5644</v>
       </c>
-      <c r="G53" s="16">
+      <c r="H53" s="16">
         <v>15.1</v>
       </c>
-      <c r="H53" s="14">
+      <c r="I53" s="14">
         <v>3.69</v>
       </c>
-      <c r="I53" s="14">
+      <c r="J53" s="14">
         <v>4.78</v>
       </c>
-      <c r="J53" s="14">
+      <c r="K53" s="14">
         <v>6.74</v>
       </c>
-      <c r="K53" s="16">
+      <c r="L53" s="16">
         <v>18.3</v>
       </c>
-      <c r="L53" s="16">
+      <c r="M53" s="16">
         <v>33.4</v>
       </c>
-      <c r="M53" s="16">
+      <c r="N53" s="16">
         <v>24.9</v>
       </c>
-      <c r="N53" s="16">
+      <c r="O53" s="16">
         <v>95.1</v>
       </c>
-      <c r="O53" s="16">
+      <c r="P53" s="16">
         <v>3.4</v>
       </c>
-      <c r="P53" s="16">
+      <c r="Q53" s="16">
         <v>7</v>
       </c>
-      <c r="Q53" s="16">
+      <c r="R53" s="16">
         <v>8.6999999999999993</v>
       </c>
-      <c r="R53" s="16">
+      <c r="S53" s="16">
         <v>8.3000000000000007</v>
       </c>
-      <c r="S53" s="13">
+      <c r="T53" s="13">
         <v>179745</v>
       </c>
-      <c r="T53" s="13">
+      <c r="U53" s="13">
         <v>4</v>
       </c>
-      <c r="U53" s="13">
+      <c r="V53" s="13">
         <v>5</v>
       </c>
-      <c r="V53" s="13" t="s">
+      <c r="W53" s="13" t="s">
         <v>230</v>
       </c>
-      <c r="W53" s="13" t="s">
+      <c r="X53" s="13" t="s">
         <v>231</v>
       </c>
-      <c r="X53" s="13">
+      <c r="Y53" s="13">
         <v>61.2</v>
       </c>
     </row>
-    <row r="54" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="A54" s="30" t="s">
+    <row r="54" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A54" s="28" t="s">
         <v>105</v>
       </c>
       <c r="B54" s="12" t="s">
@@ -5328,65 +5490,68 @@
         <v>-0.68</v>
       </c>
       <c r="F54" s="13">
+        <v>9</v>
+      </c>
+      <c r="G54" s="13">
         <v>11544</v>
       </c>
-      <c r="G54" s="16">
+      <c r="H54" s="16">
         <v>23.3</v>
       </c>
-      <c r="H54" s="14">
+      <c r="I54" s="14">
         <v>5.1100000000000003</v>
       </c>
-      <c r="I54" s="14">
+      <c r="J54" s="14">
         <v>5.91</v>
       </c>
-      <c r="J54" s="14">
+      <c r="K54" s="14">
         <v>9.48</v>
       </c>
-      <c r="K54" s="16">
+      <c r="L54" s="16">
         <v>28.2</v>
       </c>
-      <c r="L54" s="16">
+      <c r="M54" s="16">
         <v>37.799999999999997</v>
       </c>
-      <c r="M54" s="16">
+      <c r="N54" s="16">
         <v>33.799999999999997</v>
       </c>
-      <c r="N54" s="16">
+      <c r="O54" s="16">
         <v>83.6</v>
       </c>
-      <c r="O54" s="16">
+      <c r="P54" s="16">
         <v>6.9</v>
       </c>
-      <c r="P54" s="16">
+      <c r="Q54" s="16">
         <v>23.7</v>
       </c>
-      <c r="Q54" s="16">
+      <c r="R54" s="16">
         <v>15.7</v>
       </c>
-      <c r="R54" s="16">
+      <c r="S54" s="16">
         <v>8.4</v>
       </c>
-      <c r="S54" s="13">
+      <c r="T54" s="13">
         <v>22906</v>
       </c>
-      <c r="T54" s="13">
+      <c r="U54" s="13">
         <v>85</v>
       </c>
-      <c r="U54" s="13">
+      <c r="V54" s="13">
         <v>87</v>
       </c>
-      <c r="V54" s="13" t="s">
+      <c r="W54" s="13" t="s">
         <v>232</v>
       </c>
-      <c r="W54" s="13" t="s">
+      <c r="X54" s="13" t="s">
         <v>233</v>
       </c>
-      <c r="X54" s="13">
+      <c r="Y54" s="13">
         <v>77.099999999999994</v>
       </c>
     </row>
-    <row r="55" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="A55" s="30" t="s">
+    <row r="55" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A55" s="28" t="s">
         <v>107</v>
       </c>
       <c r="B55" s="12" t="s">
@@ -5402,65 +5567,68 @@
         <v>0.42</v>
       </c>
       <c r="F55" s="13">
+        <v>6</v>
+      </c>
+      <c r="G55" s="13">
         <v>5756</v>
       </c>
-      <c r="G55" s="16">
+      <c r="H55" s="16">
         <v>17.7</v>
       </c>
-      <c r="H55" s="14">
+      <c r="I55" s="14">
         <v>4.2</v>
       </c>
-      <c r="I55" s="14">
+      <c r="J55" s="14">
         <v>5.21</v>
       </c>
-      <c r="J55" s="14">
+      <c r="K55" s="14">
         <v>5.43</v>
       </c>
-      <c r="K55" s="16">
+      <c r="L55" s="16">
         <v>21.7</v>
       </c>
-      <c r="L55" s="16">
+      <c r="M55" s="16">
         <v>35.299999999999997</v>
       </c>
-      <c r="M55" s="16">
+      <c r="N55" s="16">
         <v>28.5</v>
       </c>
-      <c r="N55" s="16">
+      <c r="O55" s="16">
         <v>92.1</v>
       </c>
-      <c r="O55" s="16">
+      <c r="P55" s="16">
         <v>2.6</v>
       </c>
-      <c r="P55" s="16">
+      <c r="Q55" s="16">
         <v>8.8000000000000007</v>
       </c>
-      <c r="Q55" s="16">
+      <c r="R55" s="16">
         <v>11.9</v>
       </c>
-      <c r="R55" s="16">
+      <c r="S55" s="16">
         <v>9.4</v>
       </c>
-      <c r="S55" s="13">
+      <c r="T55" s="13">
         <v>41171</v>
       </c>
-      <c r="T55" s="13">
+      <c r="U55" s="13">
         <v>8</v>
       </c>
-      <c r="U55" s="13">
+      <c r="V55" s="13">
         <v>6</v>
       </c>
-      <c r="V55" s="13" t="s">
+      <c r="W55" s="13" t="s">
         <v>228</v>
       </c>
-      <c r="W55" s="13" t="s">
+      <c r="X55" s="13" t="s">
         <v>234</v>
       </c>
-      <c r="X55" s="13">
+      <c r="Y55" s="13">
         <v>82.2</v>
       </c>
     </row>
-    <row r="56" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="A56" s="30" t="s">
+    <row r="56" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A56" s="28" t="s">
         <v>109</v>
       </c>
       <c r="B56" s="12" t="s">
@@ -5476,65 +5644,68 @@
         <v>0.27</v>
       </c>
       <c r="F56" s="13">
+        <v>7</v>
+      </c>
+      <c r="G56" s="13">
         <v>7500</v>
       </c>
-      <c r="G56" s="16">
+      <c r="H56" s="16">
         <v>18.2</v>
       </c>
-      <c r="H56" s="14">
+      <c r="I56" s="14">
         <v>4.21</v>
       </c>
-      <c r="I56" s="14">
+      <c r="J56" s="14">
         <v>5.21</v>
       </c>
-      <c r="J56" s="14">
+      <c r="K56" s="14">
         <v>6.36</v>
       </c>
-      <c r="K56" s="16">
+      <c r="L56" s="16">
         <v>22.6</v>
       </c>
-      <c r="L56" s="16">
+      <c r="M56" s="16">
         <v>38.299999999999997</v>
       </c>
-      <c r="M56" s="16">
+      <c r="N56" s="16">
         <v>27.2</v>
       </c>
-      <c r="N56" s="16">
+      <c r="O56" s="16">
         <v>91.2</v>
       </c>
-      <c r="O56" s="16">
+      <c r="P56" s="16">
         <v>3.7</v>
       </c>
-      <c r="P56" s="16">
+      <c r="Q56" s="16">
         <v>11.9</v>
       </c>
-      <c r="Q56" s="16">
+      <c r="R56" s="16">
         <v>12</v>
       </c>
-      <c r="R56" s="16">
+      <c r="S56" s="16">
         <v>10.1</v>
       </c>
-      <c r="S56" s="13">
+      <c r="T56" s="13">
         <v>106986</v>
       </c>
-      <c r="T56" s="13">
+      <c r="U56" s="13">
         <v>22</v>
       </c>
-      <c r="U56" s="13">
+      <c r="V56" s="13">
         <v>20</v>
       </c>
-      <c r="V56" s="13" t="s">
+      <c r="W56" s="13" t="s">
         <v>228</v>
       </c>
-      <c r="W56" s="13" t="s">
+      <c r="X56" s="13" t="s">
         <v>234</v>
       </c>
-      <c r="X56" s="13">
+      <c r="Y56" s="13">
         <v>71.3</v>
       </c>
     </row>
-    <row r="57" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="A57" s="30" t="s">
+    <row r="57" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A57" s="28" t="s">
         <v>111</v>
       </c>
       <c r="B57" s="12" t="s">
@@ -5550,65 +5721,68 @@
         <v>-0.49</v>
       </c>
       <c r="F57" s="13">
+        <v>7</v>
+      </c>
+      <c r="G57" s="13">
         <v>7689</v>
       </c>
-      <c r="G57" s="16">
+      <c r="H57" s="16">
         <v>21.8</v>
       </c>
-      <c r="H57" s="14">
+      <c r="I57" s="14">
         <v>4.8899999999999997</v>
       </c>
-      <c r="I57" s="14">
+      <c r="J57" s="14">
         <v>5.74</v>
       </c>
-      <c r="J57" s="14">
+      <c r="K57" s="14">
         <v>7.43</v>
       </c>
-      <c r="K57" s="16">
+      <c r="L57" s="16">
         <v>27.5</v>
       </c>
-      <c r="L57" s="16">
+      <c r="M57" s="16">
         <v>36.9</v>
       </c>
-      <c r="M57" s="16">
+      <c r="N57" s="16">
         <v>32.6</v>
       </c>
-      <c r="N57" s="16">
+      <c r="O57" s="16">
         <v>89.1</v>
       </c>
-      <c r="O57" s="16">
+      <c r="P57" s="16">
         <v>8.3000000000000007</v>
       </c>
-      <c r="P57" s="16">
+      <c r="Q57" s="16">
         <v>20.2</v>
       </c>
-      <c r="Q57" s="16">
+      <c r="R57" s="16">
         <v>16.100000000000001</v>
       </c>
-      <c r="R57" s="16">
+      <c r="S57" s="16">
         <v>8.1999999999999993</v>
       </c>
-      <c r="S57" s="13">
+      <c r="T57" s="13">
         <v>13654</v>
       </c>
-      <c r="T57" s="13">
+      <c r="U57" s="13">
         <v>36</v>
       </c>
-      <c r="U57" s="13">
+      <c r="V57" s="13">
         <v>75</v>
       </c>
-      <c r="V57" s="13" t="s">
+      <c r="W57" s="13" t="s">
         <v>232</v>
       </c>
-      <c r="W57" s="13" t="s">
+      <c r="X57" s="13" t="s">
         <v>235</v>
       </c>
-      <c r="X57" s="13">
+      <c r="Y57" s="13">
         <v>78.2</v>
       </c>
     </row>
-    <row r="58" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="A58" s="30" t="s">
+    <row r="58" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A58" s="28" t="s">
         <v>113</v>
       </c>
       <c r="B58" s="12" t="s">
@@ -5624,65 +5798,68 @@
         <v>-0.06</v>
       </c>
       <c r="F58" s="13">
+        <v>9</v>
+      </c>
+      <c r="G58" s="13">
         <v>11171</v>
       </c>
-      <c r="G58" s="16">
+      <c r="H58" s="16">
         <v>20.8</v>
       </c>
-      <c r="H58" s="14">
+      <c r="I58" s="14">
         <v>4.4400000000000004</v>
       </c>
-      <c r="I58" s="14">
+      <c r="J58" s="14">
         <v>5.24</v>
       </c>
-      <c r="J58" s="14">
+      <c r="K58" s="14">
         <v>9.2899999999999991</v>
       </c>
-      <c r="K58" s="16">
+      <c r="L58" s="16">
         <v>21.8</v>
       </c>
-      <c r="L58" s="16">
+      <c r="M58" s="16">
         <v>36.5</v>
       </c>
-      <c r="M58" s="16">
+      <c r="N58" s="16">
         <v>30.2</v>
       </c>
-      <c r="N58" s="16">
+      <c r="O58" s="16">
         <v>90.1</v>
       </c>
-      <c r="O58" s="16">
+      <c r="P58" s="16">
         <v>4.2</v>
       </c>
-      <c r="P58" s="16">
+      <c r="Q58" s="16">
         <v>22.5</v>
       </c>
-      <c r="Q58" s="16">
+      <c r="R58" s="16">
         <v>10.6</v>
       </c>
-      <c r="R58" s="16">
+      <c r="S58" s="16">
         <v>10.5</v>
       </c>
-      <c r="S58" s="13">
+      <c r="T58" s="13">
         <v>531687</v>
       </c>
-      <c r="T58" s="13">
+      <c r="U58" s="13">
         <v>81</v>
       </c>
-      <c r="U58" s="13">
+      <c r="V58" s="13">
         <v>65</v>
       </c>
-      <c r="V58" s="13" t="s">
+      <c r="W58" s="13" t="s">
         <v>228</v>
       </c>
-      <c r="W58" s="13" t="s">
+      <c r="X58" s="13" t="s">
         <v>234</v>
       </c>
-      <c r="X58" s="13">
+      <c r="Y58" s="13">
         <v>48.6</v>
       </c>
     </row>
-    <row r="59" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="A59" s="30" t="s">
+    <row r="59" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A59" s="28" t="s">
         <v>115</v>
       </c>
       <c r="B59" s="12" t="s">
@@ -5698,65 +5875,68 @@
         <v>-0.6</v>
       </c>
       <c r="F59" s="13">
+        <v>6</v>
+      </c>
+      <c r="G59" s="13">
         <v>9086</v>
       </c>
-      <c r="G59" s="16">
+      <c r="H59" s="16">
         <v>24.5</v>
       </c>
-      <c r="H59" s="14">
+      <c r="I59" s="14">
         <v>5.29</v>
       </c>
-      <c r="I59" s="14">
+      <c r="J59" s="14">
         <v>6.01</v>
       </c>
-      <c r="J59" s="14">
+      <c r="K59" s="14">
         <v>6.5</v>
       </c>
-      <c r="K59" s="16">
+      <c r="L59" s="16">
         <v>28.8</v>
       </c>
-      <c r="L59" s="16">
+      <c r="M59" s="16">
         <v>41</v>
       </c>
-      <c r="M59" s="16">
+      <c r="N59" s="16">
         <v>34.6</v>
       </c>
-      <c r="N59" s="16">
+      <c r="O59" s="16">
         <v>85.3</v>
       </c>
-      <c r="O59" s="16">
+      <c r="P59" s="16">
         <v>6.5</v>
       </c>
-      <c r="P59" s="16">
+      <c r="Q59" s="16">
         <v>21.4</v>
       </c>
-      <c r="Q59" s="16">
+      <c r="R59" s="16">
         <v>11</v>
       </c>
-      <c r="R59" s="16">
+      <c r="S59" s="16">
         <v>8.1999999999999993</v>
       </c>
-      <c r="S59" s="13">
+      <c r="T59" s="13">
         <v>14507</v>
       </c>
-      <c r="T59" s="13">
+      <c r="U59" s="13">
         <v>58</v>
       </c>
-      <c r="U59" s="13">
+      <c r="V59" s="13">
         <v>80</v>
       </c>
-      <c r="V59" s="13" t="s">
+      <c r="W59" s="13" t="s">
         <v>237</v>
       </c>
-      <c r="W59" s="13" t="s">
+      <c r="X59" s="13" t="s">
         <v>238</v>
       </c>
-      <c r="X59" s="13">
+      <c r="Y59" s="13">
         <v>74.900000000000006</v>
       </c>
     </row>
-    <row r="60" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="A60" s="30" t="s">
+    <row r="60" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A60" s="28" t="s">
         <v>117</v>
       </c>
       <c r="B60" s="12" t="s">
@@ -5772,65 +5952,68 @@
         <v>-0.03</v>
       </c>
       <c r="F60" s="13">
+        <v>7</v>
+      </c>
+      <c r="G60" s="13">
         <v>7753</v>
       </c>
-      <c r="G60" s="16">
+      <c r="H60" s="16">
         <v>20.2</v>
       </c>
-      <c r="H60" s="14">
+      <c r="I60" s="14">
         <v>4.5199999999999996</v>
       </c>
-      <c r="I60" s="14">
+      <c r="J60" s="14">
         <v>5.48</v>
       </c>
-      <c r="J60" s="14">
+      <c r="K60" s="14">
         <v>6.42</v>
       </c>
-      <c r="K60" s="16">
+      <c r="L60" s="16">
         <v>24.8</v>
       </c>
-      <c r="L60" s="16">
+      <c r="M60" s="16">
         <v>40.299999999999997</v>
       </c>
-      <c r="M60" s="16">
+      <c r="N60" s="16">
         <v>32.200000000000003</v>
       </c>
-      <c r="N60" s="16">
+      <c r="O60" s="16">
         <v>87.7</v>
       </c>
-      <c r="O60" s="16">
+      <c r="P60" s="16">
         <v>4.0999999999999996</v>
       </c>
-      <c r="P60" s="16">
+      <c r="Q60" s="16">
         <v>13.6</v>
       </c>
-      <c r="Q60" s="16">
+      <c r="R60" s="16">
         <v>6.8</v>
       </c>
-      <c r="R60" s="16">
+      <c r="S60" s="16">
         <v>9.1</v>
       </c>
-      <c r="S60" s="13">
+      <c r="T60" s="13">
         <v>35327</v>
       </c>
-      <c r="T60" s="13">
+      <c r="U60" s="13">
         <v>35</v>
       </c>
-      <c r="U60" s="13">
+      <c r="V60" s="13">
         <v>47</v>
       </c>
-      <c r="V60" s="13" t="s">
+      <c r="W60" s="13" t="s">
         <v>237</v>
       </c>
-      <c r="W60" s="13" t="s">
+      <c r="X60" s="13" t="s">
         <v>238</v>
       </c>
-      <c r="X60" s="13">
+      <c r="Y60" s="13">
         <v>76.599999999999994</v>
       </c>
     </row>
-    <row r="61" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="A61" s="30" t="s">
+    <row r="61" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A61" s="28" t="s">
         <v>119</v>
       </c>
       <c r="B61" s="12" t="s">
@@ -5846,65 +6029,68 @@
         <v>-0.27</v>
       </c>
       <c r="F61" s="13">
+        <v>8</v>
+      </c>
+      <c r="G61" s="13">
         <v>9620</v>
       </c>
-      <c r="G61" s="16">
+      <c r="H61" s="16">
         <v>21</v>
       </c>
-      <c r="H61" s="14">
+      <c r="I61" s="14">
         <v>4.8</v>
       </c>
-      <c r="I61" s="14">
+      <c r="J61" s="14">
         <v>5.67</v>
       </c>
-      <c r="J61" s="14">
+      <c r="K61" s="14">
         <v>8.1199999999999992</v>
       </c>
-      <c r="K61" s="16">
+      <c r="L61" s="16">
         <v>26.1</v>
       </c>
-      <c r="L61" s="16">
+      <c r="M61" s="16">
         <v>39.4</v>
       </c>
-      <c r="M61" s="16">
+      <c r="N61" s="16">
         <v>30.8</v>
       </c>
-      <c r="N61" s="16">
+      <c r="O61" s="16">
         <v>87.8</v>
       </c>
-      <c r="O61" s="16">
+      <c r="P61" s="16">
         <v>4.9000000000000004</v>
       </c>
-      <c r="P61" s="16">
+      <c r="Q61" s="16">
         <v>21.4</v>
       </c>
-      <c r="Q61" s="16">
+      <c r="R61" s="16">
         <v>13</v>
       </c>
-      <c r="R61" s="16">
+      <c r="S61" s="16">
         <v>8.9</v>
       </c>
-      <c r="S61" s="13">
+      <c r="T61" s="13">
         <v>86215</v>
       </c>
-      <c r="T61" s="13">
+      <c r="U61" s="13">
         <v>66</v>
       </c>
-      <c r="U61" s="13">
+      <c r="V61" s="13">
         <v>56</v>
       </c>
-      <c r="V61" s="13" t="s">
+      <c r="W61" s="13" t="s">
         <v>237</v>
       </c>
-      <c r="W61" s="13" t="s">
+      <c r="X61" s="13" t="s">
         <v>241</v>
       </c>
-      <c r="X61" s="13">
+      <c r="Y61" s="13">
         <v>70.599999999999994</v>
       </c>
     </row>
-    <row r="62" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="A62" s="30" t="s">
+    <row r="62" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A62" s="28" t="s">
         <v>121</v>
       </c>
       <c r="B62" s="12" t="s">
@@ -5920,65 +6106,68 @@
         <v>-0.48</v>
       </c>
       <c r="F62" s="13">
+        <v>7</v>
+      </c>
+      <c r="G62" s="13">
         <v>7266</v>
       </c>
-      <c r="G62" s="16">
+      <c r="H62" s="16">
         <v>22.4</v>
       </c>
-      <c r="H62" s="14">
+      <c r="I62" s="14">
         <v>4.8099999999999996</v>
       </c>
-      <c r="I62" s="14">
+      <c r="J62" s="14">
         <v>5.65</v>
       </c>
-      <c r="J62" s="14">
+      <c r="K62" s="14">
         <v>6.45</v>
       </c>
-      <c r="K62" s="16">
+      <c r="L62" s="16">
         <v>26.7</v>
       </c>
-      <c r="L62" s="16">
+      <c r="M62" s="16">
         <v>39</v>
       </c>
-      <c r="M62" s="16">
+      <c r="N62" s="16">
         <v>33.4</v>
       </c>
-      <c r="N62" s="16">
+      <c r="O62" s="16">
         <v>84.7</v>
       </c>
-      <c r="O62" s="16">
+      <c r="P62" s="16">
         <v>6.9</v>
       </c>
-      <c r="P62" s="16">
+      <c r="Q62" s="16">
         <v>16</v>
       </c>
-      <c r="Q62" s="16">
+      <c r="R62" s="16">
         <v>12.5</v>
       </c>
-      <c r="R62" s="16">
+      <c r="S62" s="16">
         <v>8.3000000000000007</v>
       </c>
-      <c r="S62" s="13">
+      <c r="T62" s="13">
         <v>14423</v>
       </c>
-      <c r="T62" s="13">
+      <c r="U62" s="13">
         <v>16</v>
       </c>
-      <c r="U62" s="13">
+      <c r="V62" s="13">
         <v>55</v>
       </c>
-      <c r="V62" s="13" t="s">
+      <c r="W62" s="13" t="s">
         <v>232</v>
       </c>
-      <c r="W62" s="13" t="s">
+      <c r="X62" s="13" t="s">
         <v>235</v>
       </c>
-      <c r="X62" s="13">
+      <c r="Y62" s="13">
         <v>80.8</v>
       </c>
     </row>
-    <row r="63" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="A63" s="30" t="s">
+    <row r="63" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A63" s="28" t="s">
         <v>123</v>
       </c>
       <c r="B63" s="12" t="s">
@@ -5994,65 +6183,68 @@
         <v>0.13</v>
       </c>
       <c r="F63" s="13">
+        <v>8</v>
+      </c>
+      <c r="G63" s="13">
         <v>8549</v>
       </c>
-      <c r="G63" s="16">
+      <c r="H63" s="16">
         <v>18.100000000000001</v>
       </c>
-      <c r="H63" s="14">
+      <c r="I63" s="14">
         <v>4.18</v>
       </c>
-      <c r="I63" s="14">
+      <c r="J63" s="14">
         <v>5.0999999999999996</v>
       </c>
-      <c r="J63" s="14">
+      <c r="K63" s="14">
         <v>7.63</v>
       </c>
-      <c r="K63" s="16">
+      <c r="L63" s="16">
         <v>21.6</v>
       </c>
-      <c r="L63" s="16">
+      <c r="M63" s="16">
         <v>34.700000000000003</v>
       </c>
-      <c r="M63" s="16">
+      <c r="N63" s="16">
         <v>30.1</v>
       </c>
-      <c r="N63" s="16">
+      <c r="O63" s="16">
         <v>91.7</v>
       </c>
-      <c r="O63" s="16">
+      <c r="P63" s="16">
         <v>5.6</v>
       </c>
-      <c r="P63" s="16">
+      <c r="Q63" s="16">
         <v>12.1</v>
       </c>
-      <c r="Q63" s="16">
+      <c r="R63" s="16">
         <v>13.6</v>
       </c>
-      <c r="R63" s="16">
+      <c r="S63" s="16">
         <v>9.1999999999999993</v>
       </c>
-      <c r="S63" s="13">
+      <c r="T63" s="13">
         <v>40525</v>
       </c>
-      <c r="T63" s="13">
+      <c r="U63" s="13">
         <v>31</v>
       </c>
-      <c r="U63" s="13">
+      <c r="V63" s="13">
         <v>24</v>
       </c>
-      <c r="V63" s="13" t="s">
+      <c r="W63" s="13" t="s">
         <v>239</v>
       </c>
-      <c r="W63" s="13" t="s">
+      <c r="X63" s="13" t="s">
         <v>240</v>
       </c>
-      <c r="X63" s="13">
+      <c r="Y63" s="13">
         <v>61.4</v>
       </c>
     </row>
-    <row r="64" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="A64" s="30" t="s">
+    <row r="64" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A64" s="28" t="s">
         <v>125</v>
       </c>
       <c r="B64" s="12" t="s">
@@ -6068,65 +6260,68 @@
         <v>-0.17</v>
       </c>
       <c r="F64" s="13">
+        <v>8</v>
+      </c>
+      <c r="G64" s="13">
         <v>7581</v>
       </c>
-      <c r="G64" s="16">
+      <c r="H64" s="16">
         <v>19.399999999999999</v>
       </c>
-      <c r="H64" s="14">
+      <c r="I64" s="14">
         <v>4.3600000000000003</v>
       </c>
-      <c r="I64" s="14">
+      <c r="J64" s="14">
         <v>5.29</v>
       </c>
-      <c r="J64" s="14">
+      <c r="K64" s="14">
         <v>7.41</v>
       </c>
-      <c r="K64" s="16">
+      <c r="L64" s="16">
         <v>23.2</v>
       </c>
-      <c r="L64" s="16">
+      <c r="M64" s="16">
         <v>35.700000000000003</v>
       </c>
-      <c r="M64" s="16">
+      <c r="N64" s="16">
         <v>30.4</v>
       </c>
-      <c r="N64" s="16">
+      <c r="O64" s="16">
         <v>90.5</v>
       </c>
-      <c r="O64" s="16">
+      <c r="P64" s="16">
         <v>3.8</v>
       </c>
-      <c r="P64" s="16">
+      <c r="Q64" s="16">
         <v>13.2</v>
       </c>
-      <c r="Q64" s="16">
+      <c r="R64" s="16">
         <v>13.9</v>
       </c>
-      <c r="R64" s="16">
+      <c r="S64" s="16">
         <v>8.8000000000000007</v>
       </c>
-      <c r="S64" s="13">
+      <c r="T64" s="13">
         <v>18672</v>
       </c>
-      <c r="T64" s="13">
+      <c r="U64" s="13">
         <v>27</v>
       </c>
-      <c r="U64" s="13">
+      <c r="V64" s="13">
         <v>32</v>
       </c>
-      <c r="V64" s="13" t="s">
+      <c r="W64" s="13" t="s">
         <v>228</v>
       </c>
-      <c r="W64" s="13" t="s">
+      <c r="X64" s="13" t="s">
         <v>242</v>
       </c>
-      <c r="X64" s="13">
+      <c r="Y64" s="13">
         <v>76.5</v>
       </c>
     </row>
-    <row r="65" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="A65" s="30" t="s">
+    <row r="65" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A65" s="28" t="s">
         <v>127</v>
       </c>
       <c r="B65" s="12" t="s">
@@ -6142,65 +6337,68 @@
         <v>-0.39</v>
       </c>
       <c r="F65" s="13">
+        <v>7</v>
+      </c>
+      <c r="G65" s="13">
         <v>8033</v>
       </c>
-      <c r="G65" s="16">
+      <c r="H65" s="16">
         <v>22.2</v>
       </c>
-      <c r="H65" s="14">
+      <c r="I65" s="14">
         <v>4.9000000000000004</v>
       </c>
-      <c r="I65" s="14">
+      <c r="J65" s="14">
         <v>5.76</v>
       </c>
-      <c r="J65" s="14">
+      <c r="K65" s="14">
         <v>7.72</v>
       </c>
-      <c r="K65" s="16">
+      <c r="L65" s="16">
         <v>27.5</v>
       </c>
-      <c r="L65" s="16">
+      <c r="M65" s="16">
         <v>33.799999999999997</v>
       </c>
-      <c r="M65" s="16">
+      <c r="N65" s="16">
         <v>33.299999999999997</v>
       </c>
-      <c r="N65" s="16">
+      <c r="O65" s="16">
         <v>87.3</v>
       </c>
-      <c r="O65" s="16">
+      <c r="P65" s="16">
         <v>5.2</v>
       </c>
-      <c r="P65" s="16">
+      <c r="Q65" s="16">
         <v>20.6</v>
       </c>
-      <c r="Q65" s="16">
+      <c r="R65" s="16">
         <v>8.6</v>
       </c>
-      <c r="R65" s="16">
+      <c r="S65" s="16">
         <v>8.8000000000000007</v>
       </c>
-      <c r="S65" s="13">
+      <c r="T65" s="13">
         <v>36133</v>
       </c>
-      <c r="T65" s="13">
+      <c r="U65" s="13">
         <v>45</v>
       </c>
-      <c r="U65" s="13">
+      <c r="V65" s="13">
         <v>71</v>
       </c>
-      <c r="V65" s="13" t="s">
+      <c r="W65" s="13" t="s">
         <v>237</v>
       </c>
-      <c r="W65" s="13" t="s">
+      <c r="X65" s="13" t="s">
         <v>238</v>
       </c>
-      <c r="X65" s="13">
+      <c r="Y65" s="13">
         <v>75.900000000000006</v>
       </c>
     </row>
-    <row r="66" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="A66" s="30" t="s">
+    <row r="66" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A66" s="28" t="s">
         <v>129</v>
       </c>
       <c r="B66" s="12" t="s">
@@ -6216,65 +6414,68 @@
         <v>-7.0000000000000007E-2</v>
       </c>
       <c r="F66" s="13">
+        <v>7</v>
+      </c>
+      <c r="G66" s="13">
         <v>9207</v>
       </c>
-      <c r="G66" s="16">
+      <c r="H66" s="16">
         <v>19.899999999999999</v>
       </c>
-      <c r="H66" s="14">
+      <c r="I66" s="14">
         <v>4.42</v>
       </c>
-      <c r="I66" s="14">
+      <c r="J66" s="14">
         <v>5.32</v>
       </c>
-      <c r="J66" s="14">
+      <c r="K66" s="14">
         <v>7.81</v>
       </c>
-      <c r="K66" s="16">
+      <c r="L66" s="16">
         <v>24</v>
       </c>
-      <c r="L66" s="16">
+      <c r="M66" s="16">
         <v>39.5</v>
       </c>
-      <c r="M66" s="16">
+      <c r="N66" s="16">
         <v>29.3</v>
       </c>
-      <c r="N66" s="16">
+      <c r="O66" s="16">
         <v>87.2</v>
       </c>
-      <c r="O66" s="16">
+      <c r="P66" s="16">
         <v>4</v>
       </c>
-      <c r="P66" s="16">
+      <c r="Q66" s="16">
         <v>15.2</v>
       </c>
-      <c r="Q66" s="16">
+      <c r="R66" s="16">
         <v>8.1999999999999993</v>
       </c>
-      <c r="R66" s="16">
+      <c r="S66" s="16">
         <v>9.5</v>
       </c>
-      <c r="S66" s="13">
+      <c r="T66" s="13">
         <v>58456</v>
-      </c>
-      <c r="T66" s="13">
-        <v>40</v>
       </c>
       <c r="U66" s="13">
         <v>40</v>
       </c>
-      <c r="V66" s="13" t="s">
+      <c r="V66" s="13">
+        <v>40</v>
+      </c>
+      <c r="W66" s="13" t="s">
         <v>237</v>
       </c>
-      <c r="W66" s="13" t="s">
+      <c r="X66" s="13" t="s">
         <v>238</v>
       </c>
-      <c r="X66" s="13">
+      <c r="Y66" s="13">
         <v>73</v>
       </c>
     </row>
-    <row r="67" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="A67" s="30" t="s">
+    <row r="67" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A67" s="28" t="s">
         <v>131</v>
       </c>
       <c r="B67" s="12" t="s">
@@ -6290,65 +6491,68 @@
         <v>-0.57999999999999996</v>
       </c>
       <c r="F67" s="13">
+        <v>9</v>
+      </c>
+      <c r="G67" s="13">
         <v>13588</v>
       </c>
-      <c r="G67" s="16">
+      <c r="H67" s="16">
         <v>25.5</v>
       </c>
-      <c r="H67" s="14">
+      <c r="I67" s="14">
         <v>5.25</v>
       </c>
-      <c r="I67" s="14">
+      <c r="J67" s="14">
         <v>6</v>
       </c>
-      <c r="J67" s="14">
+      <c r="K67" s="14">
         <v>8.8699999999999992</v>
       </c>
-      <c r="K67" s="16">
+      <c r="L67" s="16">
         <v>27.3</v>
       </c>
-      <c r="L67" s="16">
+      <c r="M67" s="16">
         <v>38.700000000000003</v>
       </c>
-      <c r="M67" s="16">
+      <c r="N67" s="16">
         <v>36.200000000000003</v>
       </c>
-      <c r="N67" s="16">
+      <c r="O67" s="16">
         <v>80.2</v>
       </c>
-      <c r="O67" s="16">
+      <c r="P67" s="16">
         <v>6.2</v>
       </c>
-      <c r="P67" s="16">
+      <c r="Q67" s="16">
         <v>27.1</v>
       </c>
-      <c r="Q67" s="16">
+      <c r="R67" s="16">
         <v>7.6</v>
       </c>
-      <c r="R67" s="16">
+      <c r="S67" s="16">
         <v>8.5</v>
       </c>
-      <c r="S67" s="13">
+      <c r="T67" s="13">
         <v>27772</v>
       </c>
-      <c r="T67" s="13">
+      <c r="U67" s="13">
         <v>87</v>
       </c>
-      <c r="U67" s="13">
+      <c r="V67" s="13">
         <v>83</v>
       </c>
-      <c r="V67" s="13" t="s">
+      <c r="W67" s="13" t="s">
         <v>237</v>
       </c>
-      <c r="W67" s="13" t="s">
+      <c r="X67" s="13" t="s">
         <v>238</v>
       </c>
-      <c r="X67" s="13">
+      <c r="Y67" s="13">
         <v>75.7</v>
       </c>
     </row>
-    <row r="68" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="A68" s="30" t="s">
+    <row r="68" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A68" s="28" t="s">
         <v>133</v>
       </c>
       <c r="B68" s="12" t="s">
@@ -6364,65 +6568,68 @@
         <v>0.24</v>
       </c>
       <c r="F68" s="13">
+        <v>8</v>
+      </c>
+      <c r="G68" s="13">
         <v>7185</v>
       </c>
-      <c r="G68" s="16">
+      <c r="H68" s="16">
         <v>17.8</v>
       </c>
-      <c r="H68" s="14">
+      <c r="I68" s="14">
         <v>4.1900000000000004</v>
       </c>
-      <c r="I68" s="14">
+      <c r="J68" s="14">
         <v>5.15</v>
       </c>
-      <c r="J68" s="14">
+      <c r="K68" s="14">
         <v>7.96</v>
       </c>
-      <c r="K68" s="16">
+      <c r="L68" s="16">
         <v>21.7</v>
       </c>
-      <c r="L68" s="16">
+      <c r="M68" s="16">
         <v>37.200000000000003</v>
       </c>
-      <c r="M68" s="16">
+      <c r="N68" s="16">
         <v>28</v>
       </c>
-      <c r="N68" s="16">
+      <c r="O68" s="16">
         <v>92.4</v>
       </c>
-      <c r="O68" s="16">
+      <c r="P68" s="16">
         <v>4.2</v>
       </c>
-      <c r="P68" s="16">
+      <c r="Q68" s="16">
         <v>13.4</v>
       </c>
-      <c r="Q68" s="16">
+      <c r="R68" s="16">
         <v>8.4</v>
       </c>
-      <c r="R68" s="16">
+      <c r="S68" s="16">
         <v>7.5</v>
       </c>
-      <c r="S68" s="13">
+      <c r="T68" s="13">
         <v>162466</v>
-      </c>
-      <c r="T68" s="13">
-        <v>28</v>
       </c>
       <c r="U68" s="13">
         <v>28</v>
       </c>
-      <c r="V68" s="13" t="s">
+      <c r="V68" s="13">
+        <v>28</v>
+      </c>
+      <c r="W68" s="13" t="s">
         <v>230</v>
       </c>
-      <c r="W68" s="13" t="s">
+      <c r="X68" s="13" t="s">
         <v>231</v>
       </c>
-      <c r="X68" s="13">
+      <c r="Y68" s="13">
         <v>56.6</v>
       </c>
     </row>
-    <row r="69" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="A69" s="30" t="s">
+    <row r="69" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A69" s="28" t="s">
         <v>135</v>
       </c>
       <c r="B69" s="12" t="s">
@@ -6438,65 +6645,68 @@
         <v>0.03</v>
       </c>
       <c r="F69" s="13">
+        <v>8</v>
+      </c>
+      <c r="G69" s="13">
         <v>9792</v>
       </c>
-      <c r="G69" s="16">
+      <c r="H69" s="16">
         <v>18.5</v>
       </c>
-      <c r="H69" s="14">
+      <c r="I69" s="14">
         <v>4.3499999999999996</v>
       </c>
-      <c r="I69" s="14">
+      <c r="J69" s="14">
         <v>5.38</v>
       </c>
-      <c r="J69" s="14">
+      <c r="K69" s="14">
         <v>8.31</v>
       </c>
-      <c r="K69" s="16">
+      <c r="L69" s="16">
         <v>23.4</v>
       </c>
-      <c r="L69" s="16">
+      <c r="M69" s="16">
         <v>38</v>
       </c>
-      <c r="M69" s="16">
+      <c r="N69" s="16">
         <v>30.2</v>
       </c>
-      <c r="N69" s="16">
+      <c r="O69" s="16">
         <v>90.4</v>
       </c>
-      <c r="O69" s="16">
+      <c r="P69" s="16">
         <v>3.8</v>
       </c>
-      <c r="P69" s="16">
+      <c r="Q69" s="16">
         <v>13.3</v>
       </c>
-      <c r="Q69" s="16">
+      <c r="R69" s="16">
         <v>7.3</v>
       </c>
-      <c r="R69" s="16">
+      <c r="S69" s="16">
         <v>8.6999999999999993</v>
       </c>
-      <c r="S69" s="13">
+      <c r="T69" s="13">
         <v>40881</v>
       </c>
-      <c r="T69" s="13">
+      <c r="U69" s="13">
         <v>70</v>
       </c>
-      <c r="U69" s="13">
+      <c r="V69" s="13">
         <v>31</v>
       </c>
-      <c r="V69" s="13" t="s">
+      <c r="W69" s="13" t="s">
         <v>228</v>
       </c>
-      <c r="W69" s="13" t="s">
+      <c r="X69" s="13" t="s">
         <v>234</v>
       </c>
-      <c r="X69" s="13">
+      <c r="Y69" s="13">
         <v>78.3</v>
       </c>
     </row>
-    <row r="70" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="A70" s="30" t="s">
+    <row r="70" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A70" s="28" t="s">
         <v>137</v>
       </c>
       <c r="B70" s="12" t="s">
@@ -6512,65 +6722,68 @@
         <v>0.62</v>
       </c>
       <c r="F70" s="13">
+        <v>6</v>
+      </c>
+      <c r="G70" s="13">
         <v>4612</v>
       </c>
-      <c r="G70" s="16">
+      <c r="H70" s="16">
         <v>16.5</v>
       </c>
-      <c r="H70" s="14">
+      <c r="I70" s="14">
         <v>4.0199999999999996</v>
       </c>
-      <c r="I70" s="14">
+      <c r="J70" s="14">
         <v>5.01</v>
       </c>
-      <c r="J70" s="14">
+      <c r="K70" s="14">
         <v>6.48</v>
       </c>
-      <c r="K70" s="16">
+      <c r="L70" s="16">
         <v>19.399999999999999</v>
       </c>
-      <c r="L70" s="16">
+      <c r="M70" s="16">
         <v>36.700000000000003</v>
       </c>
-      <c r="M70" s="16">
+      <c r="N70" s="16">
         <v>28.2</v>
       </c>
-      <c r="N70" s="16">
+      <c r="O70" s="16">
         <v>92.8</v>
       </c>
-      <c r="O70" s="16">
+      <c r="P70" s="16">
         <v>3.1</v>
       </c>
-      <c r="P70" s="16">
+      <c r="Q70" s="16">
         <v>7.9</v>
       </c>
-      <c r="Q70" s="16">
+      <c r="R70" s="16">
         <v>13.9</v>
       </c>
-      <c r="R70" s="16">
+      <c r="S70" s="16">
         <v>8.6999999999999993</v>
       </c>
-      <c r="S70" s="13">
+      <c r="T70" s="13">
         <v>33861</v>
       </c>
-      <c r="T70" s="13">
+      <c r="U70" s="13">
         <v>2</v>
       </c>
-      <c r="U70" s="13">
+      <c r="V70" s="13">
         <v>4</v>
       </c>
-      <c r="V70" s="13" t="s">
+      <c r="W70" s="13" t="s">
         <v>239</v>
       </c>
-      <c r="W70" s="13" t="s">
+      <c r="X70" s="13" t="s">
         <v>240</v>
       </c>
-      <c r="X70" s="13">
+      <c r="Y70" s="13">
         <v>83</v>
       </c>
     </row>
-    <row r="71" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="A71" s="30" t="s">
+    <row r="71" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A71" s="28" t="s">
         <v>139</v>
       </c>
       <c r="B71" s="12" t="s">
@@ -6586,65 +6799,68 @@
         <v>-0.22</v>
       </c>
       <c r="F71" s="13">
+        <v>8</v>
+      </c>
+      <c r="G71" s="13">
         <v>9760</v>
       </c>
-      <c r="G71" s="16">
+      <c r="H71" s="16">
         <v>20.9</v>
       </c>
-      <c r="H71" s="14">
+      <c r="I71" s="14">
         <v>4.6399999999999997</v>
       </c>
-      <c r="I71" s="14">
+      <c r="J71" s="14">
         <v>5.45</v>
       </c>
-      <c r="J71" s="14">
+      <c r="K71" s="14">
         <v>7.82</v>
       </c>
-      <c r="K71" s="16">
+      <c r="L71" s="16">
         <v>25.3</v>
       </c>
-      <c r="L71" s="16">
+      <c r="M71" s="16">
         <v>39.799999999999997</v>
       </c>
-      <c r="M71" s="16">
+      <c r="N71" s="16">
         <v>33.1</v>
       </c>
-      <c r="N71" s="16">
+      <c r="O71" s="16">
         <v>86.9</v>
       </c>
-      <c r="O71" s="16">
+      <c r="P71" s="16">
         <v>4.5</v>
       </c>
-      <c r="P71" s="16">
+      <c r="Q71" s="16">
         <v>20.399999999999999</v>
       </c>
-      <c r="Q71" s="16">
+      <c r="R71" s="16">
         <v>14.7</v>
       </c>
-      <c r="R71" s="16">
+      <c r="S71" s="16">
         <v>9</v>
       </c>
-      <c r="S71" s="13">
+      <c r="T71" s="13">
         <v>121153</v>
       </c>
-      <c r="T71" s="13">
+      <c r="U71" s="13">
         <v>64</v>
       </c>
-      <c r="U71" s="13">
+      <c r="V71" s="13">
         <v>52</v>
       </c>
-      <c r="V71" s="13" t="s">
+      <c r="W71" s="13" t="s">
         <v>230</v>
       </c>
-      <c r="W71" s="13" t="s">
+      <c r="X71" s="13" t="s">
         <v>231</v>
       </c>
-      <c r="X71" s="13">
+      <c r="Y71" s="13">
         <v>69.900000000000006</v>
       </c>
     </row>
-    <row r="72" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="A72" s="30" t="s">
+    <row r="72" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A72" s="28" t="s">
         <v>141</v>
       </c>
       <c r="B72" s="12" t="s">
@@ -6660,65 +6876,68 @@
         <v>-0.13</v>
       </c>
       <c r="F72" s="13">
+        <v>9</v>
+      </c>
+      <c r="G72" s="13">
         <v>9606</v>
       </c>
-      <c r="G72" s="16">
+      <c r="H72" s="16">
         <v>22.8</v>
       </c>
-      <c r="H72" s="14">
+      <c r="I72" s="14">
         <v>4.8099999999999996</v>
       </c>
-      <c r="I72" s="14">
+      <c r="J72" s="14">
         <v>5.59</v>
       </c>
-      <c r="J72" s="14">
+      <c r="K72" s="14">
         <v>9.19</v>
       </c>
-      <c r="K72" s="16">
+      <c r="L72" s="16">
         <v>27</v>
       </c>
-      <c r="L72" s="16">
+      <c r="M72" s="16">
         <v>42.3</v>
       </c>
-      <c r="M72" s="16">
+      <c r="N72" s="16">
         <v>33.1</v>
       </c>
-      <c r="N72" s="16">
+      <c r="O72" s="16">
         <v>87.6</v>
       </c>
-      <c r="O72" s="16">
+      <c r="P72" s="16">
         <v>4.2</v>
       </c>
-      <c r="P72" s="16">
+      <c r="Q72" s="16">
         <v>20.2</v>
       </c>
-      <c r="Q72" s="16">
+      <c r="R72" s="16">
         <v>10.199999999999999</v>
       </c>
-      <c r="R72" s="16">
+      <c r="S72" s="16">
         <v>8.9</v>
       </c>
-      <c r="S72" s="13">
+      <c r="T72" s="13">
         <v>76666</v>
       </c>
-      <c r="T72" s="13">
+      <c r="U72" s="13">
         <v>77</v>
       </c>
-      <c r="U72" s="13">
+      <c r="V72" s="13">
         <v>57</v>
       </c>
-      <c r="V72" s="13" t="s">
+      <c r="W72" s="13" t="s">
         <v>237</v>
       </c>
-      <c r="W72" s="13" t="s">
+      <c r="X72" s="13" t="s">
         <v>238</v>
       </c>
-      <c r="X72" s="13">
+      <c r="Y72" s="13">
         <v>68.5</v>
       </c>
     </row>
-    <row r="73" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="A73" s="30" t="s">
+    <row r="73" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A73" s="28" t="s">
         <v>143</v>
       </c>
       <c r="B73" s="12" t="s">
@@ -6734,65 +6953,68 @@
         <v>0</v>
       </c>
       <c r="F73" s="13">
+        <v>7</v>
+      </c>
+      <c r="G73" s="13">
         <v>8730</v>
       </c>
-      <c r="G73" s="16">
+      <c r="H73" s="16">
         <v>20.100000000000001</v>
       </c>
-      <c r="H73" s="14">
+      <c r="I73" s="14">
         <v>4.42</v>
       </c>
-      <c r="I73" s="14">
+      <c r="J73" s="14">
         <v>5.23</v>
       </c>
-      <c r="J73" s="14">
+      <c r="K73" s="14">
         <v>7.4</v>
       </c>
-      <c r="K73" s="16">
+      <c r="L73" s="16">
         <v>21.7</v>
       </c>
-      <c r="L73" s="16">
+      <c r="M73" s="16">
         <v>38.299999999999997</v>
       </c>
-      <c r="M73" s="16">
+      <c r="N73" s="16">
         <v>28.9</v>
       </c>
-      <c r="N73" s="16">
+      <c r="O73" s="16">
         <v>90.4</v>
       </c>
-      <c r="O73" s="16">
+      <c r="P73" s="16">
         <v>4.3</v>
       </c>
-      <c r="P73" s="16">
+      <c r="Q73" s="16">
         <v>14.1</v>
       </c>
-      <c r="Q73" s="16">
+      <c r="R73" s="16">
         <v>12.8</v>
       </c>
-      <c r="R73" s="16">
+      <c r="S73" s="16">
         <v>9</v>
       </c>
-      <c r="S73" s="13">
+      <c r="T73" s="13">
         <v>58518</v>
       </c>
-      <c r="T73" s="13">
+      <c r="U73" s="13">
         <v>46</v>
       </c>
-      <c r="U73" s="13">
+      <c r="V73" s="13">
         <v>25</v>
       </c>
-      <c r="V73" s="13" t="s">
+      <c r="W73" s="13" t="s">
         <v>239</v>
       </c>
-      <c r="W73" s="13" t="s">
+      <c r="X73" s="13" t="s">
         <v>240</v>
       </c>
-      <c r="X73" s="13">
+      <c r="Y73" s="13">
         <v>64.3</v>
       </c>
     </row>
-    <row r="74" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="A74" s="30" t="s">
+    <row r="74" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A74" s="28" t="s">
         <v>145</v>
       </c>
       <c r="B74" s="12" t="s">
@@ -6808,65 +7030,68 @@
         <v>-0.72</v>
       </c>
       <c r="F74" s="13">
+        <v>8</v>
+      </c>
+      <c r="G74" s="13">
         <v>14056</v>
       </c>
-      <c r="G74" s="16">
+      <c r="H74" s="16">
         <v>25.3</v>
       </c>
-      <c r="H74" s="14">
+      <c r="I74" s="14">
         <v>5.21</v>
       </c>
-      <c r="I74" s="14">
+      <c r="J74" s="14">
         <v>5.91</v>
       </c>
-      <c r="J74" s="14">
+      <c r="K74" s="14">
         <v>7.99</v>
       </c>
-      <c r="K74" s="16">
+      <c r="L74" s="16">
         <v>29.3</v>
       </c>
-      <c r="L74" s="16">
+      <c r="M74" s="16">
         <v>39.200000000000003</v>
       </c>
-      <c r="M74" s="16">
+      <c r="N74" s="16">
         <v>35.299999999999997</v>
       </c>
-      <c r="N74" s="16">
+      <c r="O74" s="16">
         <v>84.9</v>
       </c>
-      <c r="O74" s="16">
+      <c r="P74" s="16">
         <v>6.3</v>
       </c>
-      <c r="P74" s="16">
+      <c r="Q74" s="16">
         <v>30.1</v>
       </c>
-      <c r="Q74" s="16">
+      <c r="R74" s="16">
         <v>10.4</v>
       </c>
-      <c r="R74" s="16">
+      <c r="S74" s="16">
         <v>6.8</v>
       </c>
-      <c r="S74" s="13">
+      <c r="T74" s="13">
         <v>75314</v>
-      </c>
-      <c r="T74" s="13">
-        <v>84</v>
       </c>
       <c r="U74" s="13">
         <v>84</v>
       </c>
-      <c r="V74" s="13" t="s">
+      <c r="V74" s="13">
+        <v>84</v>
+      </c>
+      <c r="W74" s="13" t="s">
         <v>232</v>
       </c>
-      <c r="W74" s="13" t="s">
+      <c r="X74" s="13" t="s">
         <v>233</v>
       </c>
-      <c r="X74" s="13">
+      <c r="Y74" s="13">
         <v>73</v>
       </c>
     </row>
-    <row r="75" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="A75" s="30" t="s">
+    <row r="75" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A75" s="28" t="s">
         <v>147</v>
       </c>
       <c r="B75" s="12" t="s">
@@ -6882,65 +7107,68 @@
         <v>0.01</v>
       </c>
       <c r="F75" s="13">
+        <v>8</v>
+      </c>
+      <c r="G75" s="13">
         <v>7938</v>
       </c>
-      <c r="G75" s="16">
+      <c r="H75" s="16">
         <v>20.5</v>
       </c>
-      <c r="H75" s="14">
+      <c r="I75" s="14">
         <v>4.51</v>
       </c>
-      <c r="I75" s="14">
+      <c r="J75" s="14">
         <v>5.36</v>
       </c>
-      <c r="J75" s="14">
+      <c r="K75" s="14">
         <v>8.24</v>
       </c>
-      <c r="K75" s="16">
+      <c r="L75" s="16">
         <v>23.3</v>
       </c>
-      <c r="L75" s="16">
+      <c r="M75" s="16">
         <v>38.700000000000003</v>
       </c>
-      <c r="M75" s="16">
+      <c r="N75" s="16">
         <v>30</v>
       </c>
-      <c r="N75" s="16">
+      <c r="O75" s="16">
         <v>91.7</v>
       </c>
-      <c r="O75" s="16">
+      <c r="P75" s="16">
         <v>4.0999999999999996</v>
       </c>
-      <c r="P75" s="16">
+      <c r="Q75" s="16">
         <v>16.8</v>
       </c>
-      <c r="Q75" s="16">
+      <c r="R75" s="16">
         <v>14.5</v>
       </c>
-      <c r="R75" s="16">
+      <c r="S75" s="16">
         <v>8.8000000000000007</v>
       </c>
-      <c r="S75" s="13">
+      <c r="T75" s="13">
         <v>55178</v>
       </c>
-      <c r="T75" s="13">
+      <c r="U75" s="13">
         <v>30</v>
       </c>
-      <c r="U75" s="13">
+      <c r="V75" s="13">
         <v>33</v>
       </c>
-      <c r="V75" s="13" t="s">
+      <c r="W75" s="13" t="s">
         <v>239</v>
       </c>
-      <c r="W75" s="13" t="s">
+      <c r="X75" s="13" t="s">
         <v>240</v>
       </c>
-      <c r="X75" s="13">
+      <c r="Y75" s="13">
         <v>67.2</v>
       </c>
     </row>
-    <row r="76" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="A76" s="30" t="s">
+    <row r="76" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A76" s="28" t="s">
         <v>149</v>
       </c>
       <c r="B76" s="12" t="s">
@@ -6956,65 +7184,68 @@
         <v>0.11</v>
       </c>
       <c r="F76" s="13">
+        <v>7</v>
+      </c>
+      <c r="G76" s="13">
         <v>7851</v>
       </c>
-      <c r="G76" s="16">
+      <c r="H76" s="16">
         <v>18.8</v>
       </c>
-      <c r="H76" s="14">
+      <c r="I76" s="14">
         <v>4.32</v>
       </c>
-      <c r="I76" s="14">
+      <c r="J76" s="14">
         <v>5.31</v>
       </c>
-      <c r="J76" s="14">
+      <c r="K76" s="14">
         <v>6.65</v>
       </c>
-      <c r="K76" s="16">
+      <c r="L76" s="16">
         <v>22.7</v>
       </c>
-      <c r="L76" s="16">
+      <c r="M76" s="16">
         <v>34</v>
       </c>
-      <c r="M76" s="16">
+      <c r="N76" s="16">
         <v>28.1</v>
       </c>
-      <c r="N76" s="16">
+      <c r="O76" s="16">
         <v>90.2</v>
       </c>
-      <c r="O76" s="16">
+      <c r="P76" s="16">
         <v>3.5</v>
       </c>
-      <c r="P76" s="16">
+      <c r="Q76" s="16">
         <v>11.7</v>
       </c>
-      <c r="Q76" s="16">
+      <c r="R76" s="16">
         <v>10.3</v>
       </c>
-      <c r="R76" s="16">
+      <c r="S76" s="16">
         <v>9.6</v>
       </c>
-      <c r="S76" s="13">
+      <c r="T76" s="13">
         <v>48589</v>
       </c>
-      <c r="T76" s="13">
+      <c r="U76" s="13">
         <v>13</v>
       </c>
-      <c r="U76" s="13">
+      <c r="V76" s="13">
         <v>22</v>
       </c>
-      <c r="V76" s="13" t="s">
+      <c r="W76" s="13" t="s">
         <v>228</v>
       </c>
-      <c r="W76" s="13" t="s">
+      <c r="X76" s="13" t="s">
         <v>234</v>
       </c>
-      <c r="X76" s="13">
+      <c r="Y76" s="13">
         <v>81.3</v>
       </c>
     </row>
-    <row r="77" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="A77" s="30" t="s">
+    <row r="77" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A77" s="28" t="s">
         <v>151</v>
       </c>
       <c r="B77" s="12" t="s">
@@ -7030,65 +7261,68 @@
         <v>0.04</v>
       </c>
       <c r="F77" s="13">
+        <v>9</v>
+      </c>
+      <c r="G77" s="13">
         <v>8372</v>
       </c>
-      <c r="G77" s="16">
+      <c r="H77" s="16">
         <v>19.600000000000001</v>
       </c>
-      <c r="H77" s="14">
+      <c r="I77" s="14">
         <v>4.38</v>
       </c>
-      <c r="I77" s="14">
+      <c r="J77" s="14">
         <v>5.32</v>
       </c>
-      <c r="J77" s="14">
+      <c r="K77" s="14">
         <v>8.5</v>
       </c>
-      <c r="K77" s="16">
+      <c r="L77" s="16">
         <v>22.9</v>
       </c>
-      <c r="L77" s="16">
+      <c r="M77" s="16">
         <v>36.1</v>
       </c>
-      <c r="M77" s="16">
+      <c r="N77" s="16">
         <v>28</v>
       </c>
-      <c r="N77" s="16">
+      <c r="O77" s="16">
         <v>91.6</v>
       </c>
-      <c r="O77" s="16">
+      <c r="P77" s="16">
         <v>4.5</v>
       </c>
-      <c r="P77" s="16">
+      <c r="Q77" s="16">
         <v>18.7</v>
       </c>
-      <c r="Q77" s="16">
+      <c r="R77" s="16">
         <v>12.3</v>
       </c>
-      <c r="R77" s="16">
+      <c r="S77" s="16">
         <v>10.3</v>
       </c>
-      <c r="S77" s="13">
+      <c r="T77" s="13">
         <v>370605</v>
       </c>
-      <c r="T77" s="13">
+      <c r="U77" s="13">
         <v>49</v>
       </c>
-      <c r="U77" s="13">
+      <c r="V77" s="13">
         <v>44</v>
       </c>
-      <c r="V77" s="13" t="s">
+      <c r="W77" s="13" t="s">
         <v>230</v>
       </c>
-      <c r="W77" s="13" t="s">
+      <c r="X77" s="13" t="s">
         <v>231</v>
       </c>
-      <c r="X77" s="13">
+      <c r="Y77" s="13">
         <v>59.9</v>
       </c>
     </row>
-    <row r="78" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="A78" s="30" t="s">
+    <row r="78" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A78" s="28" t="s">
         <v>153</v>
       </c>
       <c r="B78" s="12" t="s">
@@ -7104,65 +7338,68 @@
         <v>0.11</v>
       </c>
       <c r="F78" s="13">
+        <v>9</v>
+      </c>
+      <c r="G78" s="13">
         <v>8522</v>
       </c>
-      <c r="G78" s="16">
+      <c r="H78" s="16">
         <v>18.8</v>
       </c>
-      <c r="H78" s="14">
+      <c r="I78" s="14">
         <v>4.1500000000000004</v>
       </c>
-      <c r="I78" s="14">
+      <c r="J78" s="14">
         <v>5.04</v>
       </c>
-      <c r="J78" s="14">
+      <c r="K78" s="14">
         <v>9.0500000000000007</v>
       </c>
-      <c r="K78" s="16">
+      <c r="L78" s="16">
         <v>21.3</v>
       </c>
-      <c r="L78" s="16">
+      <c r="M78" s="16">
         <v>34.4</v>
       </c>
-      <c r="M78" s="16">
+      <c r="N78" s="16">
         <v>27.7</v>
       </c>
-      <c r="N78" s="16">
+      <c r="O78" s="16">
         <v>91.7</v>
       </c>
-      <c r="O78" s="16">
+      <c r="P78" s="16">
         <v>4.3</v>
       </c>
-      <c r="P78" s="16">
+      <c r="Q78" s="16">
         <v>21</v>
       </c>
-      <c r="Q78" s="16">
+      <c r="R78" s="16">
         <v>11.1</v>
       </c>
-      <c r="R78" s="16">
+      <c r="S78" s="16">
         <v>9</v>
       </c>
-      <c r="S78" s="13">
+      <c r="T78" s="13">
         <v>541012</v>
       </c>
-      <c r="T78" s="13">
+      <c r="U78" s="13">
         <v>53</v>
       </c>
-      <c r="U78" s="13">
+      <c r="V78" s="13">
         <v>41</v>
       </c>
-      <c r="V78" s="13" t="s">
+      <c r="W78" s="13" t="s">
         <v>230</v>
       </c>
-      <c r="W78" s="13" t="s">
+      <c r="X78" s="13" t="s">
         <v>231</v>
       </c>
-      <c r="X78" s="13">
+      <c r="Y78" s="13">
         <v>45.3</v>
       </c>
     </row>
-    <row r="79" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="A79" s="30" t="s">
+    <row r="79" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A79" s="28" t="s">
         <v>155</v>
       </c>
       <c r="B79" s="12" t="s">
@@ -7178,65 +7415,68 @@
         <v>-0.41</v>
       </c>
       <c r="F79" s="13">
+        <v>9</v>
+      </c>
+      <c r="G79" s="13">
         <v>10571</v>
       </c>
-      <c r="G79" s="16">
+      <c r="H79" s="16">
         <v>21.7</v>
       </c>
-      <c r="H79" s="14">
+      <c r="I79" s="14">
         <v>4.74</v>
       </c>
-      <c r="I79" s="14">
+      <c r="J79" s="14">
         <v>5.57</v>
       </c>
-      <c r="J79" s="14">
+      <c r="K79" s="14">
         <v>8.6199999999999992</v>
       </c>
-      <c r="K79" s="16">
+      <c r="L79" s="16">
         <v>26.8</v>
       </c>
-      <c r="L79" s="16">
+      <c r="M79" s="16">
         <v>37.1</v>
       </c>
-      <c r="M79" s="16">
+      <c r="N79" s="16">
         <v>32.299999999999997</v>
       </c>
-      <c r="N79" s="16">
+      <c r="O79" s="16">
         <v>89.4</v>
       </c>
-      <c r="O79" s="16">
+      <c r="P79" s="16">
         <v>6.1</v>
       </c>
-      <c r="P79" s="16">
+      <c r="Q79" s="16">
         <v>24.8</v>
       </c>
-      <c r="Q79" s="16">
+      <c r="R79" s="16">
         <v>11.8</v>
       </c>
-      <c r="R79" s="16">
+      <c r="S79" s="16">
         <v>7.4</v>
       </c>
-      <c r="S79" s="13">
+      <c r="T79" s="13">
         <v>197973</v>
       </c>
-      <c r="T79" s="13">
+      <c r="U79" s="13">
         <v>72</v>
       </c>
-      <c r="U79" s="13">
+      <c r="V79" s="13">
         <v>77</v>
       </c>
-      <c r="V79" s="13" t="s">
+      <c r="W79" s="13" t="s">
         <v>230</v>
       </c>
-      <c r="W79" s="13" t="s">
+      <c r="X79" s="13" t="s">
         <v>236</v>
       </c>
-      <c r="X79" s="13">
+      <c r="Y79" s="13">
         <v>57.1</v>
       </c>
     </row>
-    <row r="80" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="A80" s="30" t="s">
+    <row r="80" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A80" s="28" t="s">
         <v>157</v>
       </c>
       <c r="B80" s="12" t="s">
@@ -7252,65 +7492,68 @@
         <v>-0.06</v>
       </c>
       <c r="F80" s="13">
+        <v>7</v>
+      </c>
+      <c r="G80" s="13">
         <v>7509</v>
       </c>
-      <c r="G80" s="16">
+      <c r="H80" s="16">
         <v>20.7</v>
       </c>
-      <c r="H80" s="14">
+      <c r="I80" s="14">
         <v>4.62</v>
       </c>
-      <c r="I80" s="14">
+      <c r="J80" s="14">
         <v>5.5</v>
       </c>
-      <c r="J80" s="14">
+      <c r="K80" s="14">
         <v>7.17</v>
       </c>
-      <c r="K80" s="16">
+      <c r="L80" s="16">
         <v>23.7</v>
       </c>
-      <c r="L80" s="16">
+      <c r="M80" s="16">
         <v>38.200000000000003</v>
       </c>
-      <c r="M80" s="16">
+      <c r="N80" s="16">
         <v>30</v>
       </c>
-      <c r="N80" s="16">
+      <c r="O80" s="16">
         <v>86</v>
       </c>
-      <c r="O80" s="16">
+      <c r="P80" s="16">
         <v>4.3</v>
       </c>
-      <c r="P80" s="16">
+      <c r="Q80" s="16">
         <v>15.8</v>
       </c>
-      <c r="Q80" s="16">
+      <c r="R80" s="16">
         <v>17.3</v>
       </c>
-      <c r="R80" s="16">
+      <c r="S80" s="16">
         <v>9.4</v>
       </c>
-      <c r="S80" s="13">
+      <c r="T80" s="13">
         <v>91987</v>
       </c>
-      <c r="T80" s="13">
+      <c r="U80" s="13">
         <v>23</v>
       </c>
-      <c r="U80" s="13">
+      <c r="V80" s="13">
         <v>48</v>
       </c>
-      <c r="V80" s="13" t="s">
+      <c r="W80" s="13" t="s">
         <v>230</v>
       </c>
-      <c r="W80" s="13" t="s">
+      <c r="X80" s="13" t="s">
         <v>231</v>
       </c>
-      <c r="X80" s="13">
+      <c r="Y80" s="13">
         <v>70.3</v>
       </c>
     </row>
-    <row r="81" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="A81" s="30" t="s">
+    <row r="81" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A81" s="28" t="s">
         <v>159</v>
       </c>
       <c r="B81" s="12" t="s">
@@ -7326,65 +7569,68 @@
         <v>0.75</v>
       </c>
       <c r="F81" s="13">
+        <v>7</v>
+      </c>
+      <c r="G81" s="13">
         <v>5707</v>
       </c>
-      <c r="G81" s="16">
+      <c r="H81" s="16">
         <v>15.9</v>
       </c>
-      <c r="H81" s="14">
+      <c r="I81" s="14">
         <v>3.74</v>
       </c>
-      <c r="I81" s="14">
+      <c r="J81" s="14">
         <v>4.8099999999999996</v>
       </c>
-      <c r="J81" s="14">
+      <c r="K81" s="14">
         <v>6.53</v>
       </c>
-      <c r="K81" s="16">
+      <c r="L81" s="16">
         <v>19.100000000000001</v>
       </c>
-      <c r="L81" s="16">
+      <c r="M81" s="16">
         <v>35.200000000000003</v>
       </c>
-      <c r="M81" s="16">
+      <c r="N81" s="16">
         <v>26.2</v>
       </c>
-      <c r="N81" s="16">
+      <c r="O81" s="16">
         <v>93.4</v>
       </c>
-      <c r="O81" s="16">
+      <c r="P81" s="16">
         <v>3.2</v>
       </c>
-      <c r="P81" s="16">
+      <c r="Q81" s="16">
         <v>5.7</v>
       </c>
-      <c r="Q81" s="16">
+      <c r="R81" s="16">
         <v>11.2</v>
       </c>
-      <c r="R81" s="16">
+      <c r="S81" s="16">
         <v>9.8000000000000007</v>
       </c>
-      <c r="S81" s="13">
+      <c r="T81" s="13">
         <v>58988</v>
-      </c>
-      <c r="T81" s="13">
-        <v>7</v>
       </c>
       <c r="U81" s="13">
         <v>7</v>
       </c>
-      <c r="V81" s="13" t="s">
+      <c r="V81" s="13">
+        <v>7</v>
+      </c>
+      <c r="W81" s="13" t="s">
         <v>237</v>
       </c>
-      <c r="W81" s="13" t="s">
+      <c r="X81" s="13" t="s">
         <v>238</v>
       </c>
-      <c r="X81" s="13">
+      <c r="Y81" s="13">
         <v>63.3</v>
       </c>
     </row>
-    <row r="82" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="A82" s="30" t="s">
+    <row r="82" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A82" s="28" t="s">
         <v>161</v>
       </c>
       <c r="B82" s="12" t="s">
@@ -7400,65 +7646,68 @@
         <v>0.23</v>
       </c>
       <c r="F82" s="13">
+        <v>8</v>
+      </c>
+      <c r="G82" s="13">
         <v>7406</v>
       </c>
-      <c r="G82" s="16">
+      <c r="H82" s="16">
         <v>19.399999999999999</v>
       </c>
-      <c r="H82" s="14">
+      <c r="I82" s="14">
         <v>4.45</v>
       </c>
-      <c r="I82" s="14">
+      <c r="J82" s="14">
         <v>5.37</v>
       </c>
-      <c r="J82" s="14">
+      <c r="K82" s="14">
         <v>7.85</v>
       </c>
-      <c r="K82" s="16">
+      <c r="L82" s="16">
         <v>23.3</v>
       </c>
-      <c r="L82" s="16">
+      <c r="M82" s="16">
         <v>39.200000000000003</v>
       </c>
-      <c r="M82" s="16">
+      <c r="N82" s="16">
         <v>29.9</v>
       </c>
-      <c r="N82" s="16">
+      <c r="O82" s="16">
         <v>91.3</v>
       </c>
-      <c r="O82" s="16">
+      <c r="P82" s="16">
         <v>3.3</v>
       </c>
-      <c r="P82" s="16">
+      <c r="Q82" s="16">
         <v>12</v>
       </c>
-      <c r="Q82" s="16">
+      <c r="R82" s="16">
         <v>16.3</v>
       </c>
-      <c r="R82" s="16">
+      <c r="S82" s="16">
         <v>9</v>
       </c>
-      <c r="S82" s="13">
+      <c r="T82" s="13">
         <v>28274</v>
       </c>
-      <c r="T82" s="13">
+      <c r="U82" s="13">
         <v>37</v>
       </c>
-      <c r="U82" s="13">
+      <c r="V82" s="13">
         <v>9</v>
       </c>
-      <c r="V82" s="13" t="s">
+      <c r="W82" s="13" t="s">
         <v>228</v>
       </c>
-      <c r="W82" s="13" t="s">
+      <c r="X82" s="13" t="s">
         <v>242</v>
       </c>
-      <c r="X82" s="13">
+      <c r="Y82" s="13">
         <v>78</v>
       </c>
     </row>
-    <row r="83" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="A83" s="30" t="s">
+    <row r="83" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A83" s="28" t="s">
         <v>163</v>
       </c>
       <c r="B83" s="12" t="s">
@@ -7474,65 +7723,68 @@
         <v>-0.74</v>
       </c>
       <c r="F83" s="13">
+        <v>9</v>
+      </c>
+      <c r="G83" s="13">
         <v>10705</v>
       </c>
-      <c r="G83" s="16">
+      <c r="H83" s="16">
         <v>24.7</v>
       </c>
-      <c r="H83" s="14">
+      <c r="I83" s="14">
         <v>5.24</v>
       </c>
-      <c r="I83" s="14">
+      <c r="J83" s="14">
         <v>5.98</v>
       </c>
-      <c r="J83" s="14">
+      <c r="K83" s="14">
         <v>8.09</v>
       </c>
-      <c r="K83" s="16">
+      <c r="L83" s="16">
         <v>28.6</v>
       </c>
-      <c r="L83" s="16">
+      <c r="M83" s="16">
         <v>39.299999999999997</v>
       </c>
-      <c r="M83" s="16">
+      <c r="N83" s="16">
         <v>39.1</v>
       </c>
-      <c r="N83" s="16">
+      <c r="O83" s="16">
         <v>80.7</v>
       </c>
-      <c r="O83" s="16">
+      <c r="P83" s="16">
         <v>5.6</v>
       </c>
-      <c r="P83" s="16">
+      <c r="Q83" s="16">
         <v>28.1</v>
       </c>
-      <c r="Q83" s="16">
+      <c r="R83" s="16">
         <v>3.8</v>
       </c>
-      <c r="R83" s="16">
+      <c r="S83" s="16">
         <v>8.1999999999999993</v>
       </c>
-      <c r="S83" s="13">
+      <c r="T83" s="13">
         <v>13084</v>
       </c>
-      <c r="T83" s="13">
+      <c r="U83" s="13">
         <v>74</v>
       </c>
-      <c r="U83" s="13">
+      <c r="V83" s="13">
         <v>86</v>
       </c>
-      <c r="V83" s="13" t="s">
+      <c r="W83" s="13" t="s">
         <v>232</v>
       </c>
-      <c r="W83" s="13" t="s">
+      <c r="X83" s="13" t="s">
         <v>233</v>
       </c>
-      <c r="X83" s="13">
+      <c r="Y83" s="13">
         <v>77.7</v>
       </c>
     </row>
-    <row r="84" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="A84" s="30" t="s">
+    <row r="84" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A84" s="28" t="s">
         <v>165</v>
       </c>
       <c r="B84" s="12" t="s">
@@ -7548,65 +7800,68 @@
         <v>0.69</v>
       </c>
       <c r="F84" s="13">
+        <v>7</v>
+      </c>
+      <c r="G84" s="13">
         <v>5921</v>
       </c>
-      <c r="G84" s="16">
+      <c r="H84" s="16">
         <v>14.7</v>
       </c>
-      <c r="H84" s="14">
+      <c r="I84" s="14">
         <v>3.47</v>
       </c>
-      <c r="I84" s="14">
+      <c r="J84" s="14">
         <v>4.51</v>
       </c>
-      <c r="J84" s="14">
+      <c r="K84" s="14">
         <v>7.07</v>
       </c>
-      <c r="K84" s="16">
+      <c r="L84" s="16">
         <v>17</v>
       </c>
-      <c r="L84" s="16">
+      <c r="M84" s="16">
         <v>31.4</v>
       </c>
-      <c r="M84" s="16">
+      <c r="N84" s="16">
         <v>22.6</v>
       </c>
-      <c r="N84" s="16">
+      <c r="O84" s="16">
         <v>93.8</v>
       </c>
-      <c r="O84" s="16">
+      <c r="P84" s="16">
         <v>3.5</v>
       </c>
-      <c r="P84" s="16">
+      <c r="Q84" s="16">
         <v>5.0999999999999996</v>
       </c>
-      <c r="Q84" s="16">
+      <c r="R84" s="16">
         <v>8.5</v>
       </c>
-      <c r="R84" s="16">
+      <c r="S84" s="16">
         <v>10.5</v>
       </c>
-      <c r="S84" s="13">
+      <c r="T84" s="13">
         <v>234602</v>
       </c>
-      <c r="T84" s="13">
+      <c r="U84" s="13">
         <v>6</v>
       </c>
-      <c r="U84" s="13">
+      <c r="V84" s="13">
         <v>2</v>
       </c>
-      <c r="V84" s="13" t="s">
+      <c r="W84" s="13" t="s">
         <v>226</v>
       </c>
-      <c r="W84" s="13" t="s">
+      <c r="X84" s="13" t="s">
         <v>227</v>
       </c>
-      <c r="X84" s="13">
+      <c r="Y84" s="13">
         <v>64.400000000000006</v>
       </c>
     </row>
-    <row r="85" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="A85" s="30" t="s">
+    <row r="85" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A85" s="28" t="s">
         <v>167</v>
       </c>
       <c r="B85" s="12" t="s">
@@ -7622,65 +7877,68 @@
         <v>-0.14000000000000001</v>
       </c>
       <c r="F85" s="13">
+        <v>7</v>
+      </c>
+      <c r="G85" s="13">
         <v>8480</v>
       </c>
-      <c r="G85" s="16">
+      <c r="H85" s="16">
         <v>20.100000000000001</v>
       </c>
-      <c r="H85" s="14">
+      <c r="I85" s="14">
         <v>4.53</v>
       </c>
-      <c r="I85" s="14">
+      <c r="J85" s="14">
         <v>5.46</v>
       </c>
-      <c r="J85" s="14">
+      <c r="K85" s="14">
         <v>7.2</v>
       </c>
-      <c r="K85" s="16">
+      <c r="L85" s="16">
         <v>23.5</v>
       </c>
-      <c r="L85" s="16">
+      <c r="M85" s="16">
         <v>38.6</v>
       </c>
-      <c r="M85" s="16">
+      <c r="N85" s="16">
         <v>31.3</v>
       </c>
-      <c r="N85" s="16">
+      <c r="O85" s="16">
         <v>90.6</v>
       </c>
-      <c r="O85" s="16">
+      <c r="P85" s="16">
         <v>5.4</v>
       </c>
-      <c r="P85" s="16">
+      <c r="Q85" s="16">
         <v>15.2</v>
       </c>
-      <c r="Q85" s="16">
+      <c r="R85" s="16">
         <v>12.9</v>
       </c>
-      <c r="R85" s="16">
+      <c r="S85" s="16">
         <v>8.6999999999999993</v>
       </c>
-      <c r="S85" s="13">
+      <c r="T85" s="13">
         <v>59910</v>
       </c>
-      <c r="T85" s="13">
+      <c r="U85" s="13">
         <v>51</v>
       </c>
-      <c r="U85" s="13">
+      <c r="V85" s="13">
         <v>42</v>
       </c>
-      <c r="V85" s="13" t="s">
+      <c r="W85" s="13" t="s">
         <v>232</v>
       </c>
-      <c r="W85" s="13" t="s">
+      <c r="X85" s="13" t="s">
         <v>243</v>
       </c>
-      <c r="X85" s="13">
+      <c r="Y85" s="13">
         <v>70.599999999999994</v>
       </c>
     </row>
-    <row r="86" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="A86" s="30" t="s">
+    <row r="86" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A86" s="28" t="s">
         <v>169</v>
       </c>
       <c r="B86" s="12" t="s">
@@ -7696,65 +7954,68 @@
         <v>0.1</v>
       </c>
       <c r="F86" s="13">
+        <v>6</v>
+      </c>
+      <c r="G86" s="13">
         <v>7601</v>
       </c>
-      <c r="G86" s="16">
+      <c r="H86" s="16">
         <v>20</v>
       </c>
-      <c r="H86" s="14">
+      <c r="I86" s="14">
         <v>4.42</v>
       </c>
-      <c r="I86" s="14">
+      <c r="J86" s="14">
         <v>5.36</v>
       </c>
-      <c r="J86" s="14">
+      <c r="K86" s="14">
         <v>5.98</v>
       </c>
-      <c r="K86" s="16">
+      <c r="L86" s="16">
         <v>22.9</v>
       </c>
-      <c r="L86" s="16">
+      <c r="M86" s="16">
         <v>38.4</v>
       </c>
-      <c r="M86" s="16">
+      <c r="N86" s="16">
         <v>29.9</v>
       </c>
-      <c r="N86" s="16">
+      <c r="O86" s="16">
         <v>86.5</v>
       </c>
-      <c r="O86" s="16">
+      <c r="P86" s="16">
         <v>3.2</v>
       </c>
-      <c r="P86" s="16">
+      <c r="Q86" s="16">
         <v>13.9</v>
       </c>
-      <c r="Q86" s="16">
+      <c r="R86" s="16">
         <v>13.8</v>
       </c>
-      <c r="R86" s="16">
+      <c r="S86" s="16">
         <v>9.6</v>
       </c>
-      <c r="S86" s="13">
+      <c r="T86" s="13">
         <v>115710</v>
-      </c>
-      <c r="T86" s="13">
-        <v>18</v>
       </c>
       <c r="U86" s="13">
         <v>18</v>
       </c>
-      <c r="V86" s="13" t="s">
+      <c r="V86" s="13">
+        <v>18</v>
+      </c>
+      <c r="W86" s="13" t="s">
         <v>230</v>
       </c>
-      <c r="W86" s="13" t="s">
+      <c r="X86" s="13" t="s">
         <v>231</v>
       </c>
-      <c r="X86" s="13">
+      <c r="Y86" s="13">
         <v>68.3</v>
       </c>
     </row>
-    <row r="87" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="A87" s="30" t="s">
+    <row r="87" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A87" s="28" t="s">
         <v>171</v>
       </c>
       <c r="B87" s="12" t="s">
@@ -7770,65 +8031,68 @@
         <v>0.08</v>
       </c>
       <c r="F87" s="13">
+        <v>6</v>
+      </c>
+      <c r="G87" s="13">
         <v>7686</v>
       </c>
-      <c r="G87" s="16">
+      <c r="H87" s="16">
         <v>19.7</v>
       </c>
-      <c r="H87" s="14">
+      <c r="I87" s="14">
         <v>4.38</v>
       </c>
-      <c r="I87" s="14">
+      <c r="J87" s="14">
         <v>5.29</v>
       </c>
-      <c r="J87" s="14">
+      <c r="K87" s="14">
         <v>5.7</v>
       </c>
-      <c r="K87" s="16">
+      <c r="L87" s="16">
         <v>23.9</v>
       </c>
-      <c r="L87" s="16">
+      <c r="M87" s="16">
         <v>37.5</v>
       </c>
-      <c r="M87" s="16">
+      <c r="N87" s="16">
         <v>30.3</v>
       </c>
-      <c r="N87" s="16">
+      <c r="O87" s="16">
         <v>90.5</v>
       </c>
-      <c r="O87" s="16">
+      <c r="P87" s="16">
         <v>3.3</v>
       </c>
-      <c r="P87" s="16">
+      <c r="Q87" s="16">
         <v>13.3</v>
       </c>
-      <c r="Q87" s="16">
+      <c r="R87" s="16">
         <v>18</v>
       </c>
-      <c r="R87" s="16">
+      <c r="S87" s="16">
         <v>8.6999999999999993</v>
       </c>
-      <c r="S87" s="13">
+      <c r="T87" s="13">
         <v>36691</v>
       </c>
-      <c r="T87" s="13">
+      <c r="U87" s="13">
         <v>20</v>
       </c>
-      <c r="U87" s="13">
+      <c r="V87" s="13">
         <v>30</v>
       </c>
-      <c r="V87" s="13" t="s">
+      <c r="W87" s="13" t="s">
         <v>239</v>
       </c>
-      <c r="W87" s="13" t="s">
+      <c r="X87" s="13" t="s">
         <v>240</v>
       </c>
-      <c r="X87" s="13">
+      <c r="Y87" s="13">
         <v>72.7</v>
       </c>
     </row>
-    <row r="88" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="A88" s="30" t="s">
+    <row r="88" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A88" s="28" t="s">
         <v>173</v>
       </c>
       <c r="B88" s="12" t="s">
@@ -7844,65 +8108,68 @@
         <v>0.41</v>
       </c>
       <c r="F88" s="13">
+        <v>7</v>
+      </c>
+      <c r="G88" s="13">
         <v>5645</v>
       </c>
-      <c r="G88" s="16">
+      <c r="H88" s="16">
         <v>17.100000000000001</v>
       </c>
-      <c r="H88" s="14">
+      <c r="I88" s="14">
         <v>4.08</v>
       </c>
-      <c r="I88" s="14">
+      <c r="J88" s="14">
         <v>4.99</v>
       </c>
-      <c r="J88" s="14">
+      <c r="K88" s="14">
         <v>6.86</v>
       </c>
-      <c r="K88" s="16">
+      <c r="L88" s="16">
         <v>19.5</v>
       </c>
-      <c r="L88" s="16">
+      <c r="M88" s="16">
         <v>39.200000000000003</v>
       </c>
-      <c r="M88" s="16">
+      <c r="N88" s="16">
         <v>27.6</v>
       </c>
-      <c r="N88" s="16">
+      <c r="O88" s="16">
         <v>94.3</v>
       </c>
-      <c r="O88" s="16">
+      <c r="P88" s="16">
         <v>3.7</v>
       </c>
-      <c r="P88" s="16">
+      <c r="Q88" s="16">
         <v>9.8000000000000007</v>
       </c>
-      <c r="Q88" s="16">
+      <c r="R88" s="16">
         <v>11.6</v>
       </c>
-      <c r="R88" s="16">
+      <c r="S88" s="16">
         <v>9.4</v>
       </c>
-      <c r="S88" s="13">
+      <c r="T88" s="13">
         <v>130817</v>
       </c>
-      <c r="T88" s="13">
+      <c r="U88" s="13">
         <v>11</v>
       </c>
-      <c r="U88" s="13">
+      <c r="V88" s="13">
         <v>8</v>
       </c>
-      <c r="V88" s="13" t="s">
+      <c r="W88" s="13" t="s">
         <v>239</v>
       </c>
-      <c r="W88" s="13" t="s">
+      <c r="X88" s="13" t="s">
         <v>240</v>
       </c>
-      <c r="X88" s="13">
+      <c r="Y88" s="13">
         <v>53.9</v>
       </c>
     </row>
-    <row r="89" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="A89" s="30" t="s">
+    <row r="89" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A89" s="28" t="s">
         <v>175</v>
       </c>
       <c r="B89" s="12" t="s">
@@ -7918,65 +8185,68 @@
         <v>0.36</v>
       </c>
       <c r="F89" s="13">
+        <v>7</v>
+      </c>
+      <c r="G89" s="13">
         <v>8275</v>
       </c>
-      <c r="G89" s="16">
+      <c r="H89" s="16">
         <v>19.600000000000001</v>
       </c>
-      <c r="H89" s="14">
+      <c r="I89" s="14">
         <v>4.41</v>
       </c>
-      <c r="I89" s="14">
+      <c r="J89" s="14">
         <v>5.34</v>
       </c>
-      <c r="J89" s="14">
+      <c r="K89" s="14">
         <v>7.37</v>
       </c>
-      <c r="K89" s="16">
+      <c r="L89" s="16">
         <v>24.3</v>
       </c>
-      <c r="L89" s="16">
+      <c r="M89" s="16">
         <v>40.700000000000003</v>
       </c>
-      <c r="M89" s="16">
+      <c r="N89" s="16">
         <v>30.3</v>
       </c>
-      <c r="N89" s="16">
+      <c r="O89" s="16">
         <v>91.9</v>
       </c>
-      <c r="O89" s="16">
+      <c r="P89" s="16">
         <v>3.1</v>
       </c>
-      <c r="P89" s="16">
+      <c r="Q89" s="16">
         <v>9.6999999999999993</v>
       </c>
-      <c r="Q89" s="16">
+      <c r="R89" s="16">
         <v>19.3</v>
       </c>
-      <c r="R89" s="16">
+      <c r="S89" s="16">
         <v>8.8000000000000007</v>
       </c>
-      <c r="S89" s="13">
+      <c r="T89" s="13">
         <v>21771</v>
       </c>
-      <c r="T89" s="13">
+      <c r="U89" s="13">
         <v>19</v>
       </c>
-      <c r="U89" s="13">
+      <c r="V89" s="13">
         <v>17</v>
       </c>
-      <c r="V89" s="13" t="s">
+      <c r="W89" s="13" t="s">
         <v>239</v>
       </c>
-      <c r="W89" s="13" t="s">
+      <c r="X89" s="13" t="s">
         <v>240</v>
       </c>
-      <c r="X89" s="13">
+      <c r="Y89" s="13">
         <v>74.2</v>
       </c>
     </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:X89">
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:Y89">
     <sortCondition ref="A2:A89"/>
   </sortState>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -7986,7 +8256,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2F192A0B-9170-4A1C-805B-F80BB4DF89A3}">
-  <dimension ref="A1:D29"/>
+  <dimension ref="A1:D30"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="13.85546875" style="2" customWidth="1"/>
@@ -8075,38 +8345,38 @@
     </row>
     <row r="7" spans="1:4" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="5" t="s">
-        <v>204</v>
+        <v>253</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>200</v>
+        <v>196</v>
       </c>
       <c r="C7" s="6" t="s">
-        <v>177</v>
-      </c>
-      <c r="D7" s="8">
-        <v>2021</v>
+        <v>254</v>
+      </c>
+      <c r="D7" s="6">
+        <v>2024</v>
       </c>
     </row>
     <row r="8" spans="1:4" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="5" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>199</v>
-      </c>
-      <c r="C8" s="6">
-        <v>2019</v>
-      </c>
-      <c r="D8" s="9">
-        <v>2022</v>
+        <v>200</v>
+      </c>
+      <c r="C8" s="6" t="s">
+        <v>177</v>
+      </c>
+      <c r="D8" s="8">
+        <v>2021</v>
       </c>
     </row>
     <row r="9" spans="1:4" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="5" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="C9" s="6">
         <v>2019</v>
@@ -8117,10 +8387,10 @@
     </row>
     <row r="10" spans="1:4" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="5" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="C10" s="6">
         <v>2019</v>
@@ -8131,27 +8401,27 @@
     </row>
     <row r="11" spans="1:4" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="5" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="C11" s="6">
         <v>2019</v>
       </c>
-      <c r="D11" s="8">
-        <v>2021</v>
+      <c r="D11" s="9">
+        <v>2022</v>
       </c>
     </row>
     <row r="12" spans="1:4" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="5" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>195</v>
-      </c>
-      <c r="C12" s="6" t="s">
-        <v>178</v>
+        <v>196</v>
+      </c>
+      <c r="C12" s="6">
+        <v>2019</v>
       </c>
       <c r="D12" s="8">
         <v>2021</v>
@@ -8159,24 +8429,24 @@
     </row>
     <row r="13" spans="1:4" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="5" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>194</v>
-      </c>
-      <c r="C13" s="6">
-        <v>2019</v>
-      </c>
-      <c r="D13" s="9">
-        <v>2022</v>
+        <v>195</v>
+      </c>
+      <c r="C13" s="6" t="s">
+        <v>178</v>
+      </c>
+      <c r="D13" s="8">
+        <v>2021</v>
       </c>
     </row>
     <row r="14" spans="1:4" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="5" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="C14" s="6">
         <v>2019</v>
@@ -8187,27 +8457,27 @@
     </row>
     <row r="15" spans="1:4" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="5" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>192</v>
-      </c>
-      <c r="C15" s="6" t="s">
-        <v>179</v>
-      </c>
-      <c r="D15" s="8">
-        <v>2021</v>
+        <v>193</v>
+      </c>
+      <c r="C15" s="6">
+        <v>2019</v>
+      </c>
+      <c r="D15" s="9">
+        <v>2022</v>
       </c>
     </row>
     <row r="16" spans="1:4" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="5" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>191</v>
-      </c>
-      <c r="C16" s="6">
-        <v>2019</v>
+        <v>192</v>
+      </c>
+      <c r="C16" s="6" t="s">
+        <v>179</v>
       </c>
       <c r="D16" s="8">
         <v>2021</v>
@@ -8215,10 +8485,10 @@
     </row>
     <row r="17" spans="1:4" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="5" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="B17" s="4" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="C17" s="6">
         <v>2019</v>
@@ -8229,66 +8499,66 @@
     </row>
     <row r="18" spans="1:4" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="5" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="B18" s="4" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="C18" s="6">
         <v>2019</v>
       </c>
-      <c r="D18" s="9">
-        <v>2022</v>
+      <c r="D18" s="8">
+        <v>2021</v>
       </c>
     </row>
     <row r="19" spans="1:4" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="5" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="B19" s="4" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="C19" s="6">
         <v>2019</v>
       </c>
-      <c r="D19" s="18">
-        <v>2023</v>
+      <c r="D19" s="9">
+        <v>2022</v>
       </c>
     </row>
     <row r="20" spans="1:4" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="5" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="B20" s="4" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="C20" s="6">
         <v>2019</v>
       </c>
-      <c r="D20" s="9">
-        <v>2022</v>
-      </c>
-    </row>
-    <row r="21" spans="1:4" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D20" s="18">
+        <v>2023</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="5" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="B21" s="4" t="s">
-        <v>223</v>
+        <v>187</v>
       </c>
       <c r="C21" s="6">
         <v>2019</v>
       </c>
-      <c r="D21" s="19">
-        <v>2019</v>
+      <c r="D21" s="9">
+        <v>2022</v>
       </c>
     </row>
     <row r="22" spans="1:4" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="5" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="B22" s="4" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="C22" s="6">
         <v>2019</v>
@@ -8297,60 +8567,74 @@
         <v>2019</v>
       </c>
     </row>
-    <row r="23" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:4" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="5" t="s">
-        <v>244</v>
+        <v>221</v>
       </c>
       <c r="B23" s="4" t="s">
-        <v>246</v>
+        <v>222</v>
       </c>
       <c r="C23" s="6">
-        <v>2024</v>
-      </c>
-      <c r="D23" s="20"/>
+        <v>2019</v>
+      </c>
+      <c r="D23" s="19">
+        <v>2019</v>
+      </c>
     </row>
     <row r="24" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A24" s="5" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="B24" s="4" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="C24" s="6">
         <v>2024</v>
       </c>
-      <c r="D24" s="20"/>
+      <c r="D24" s="6"/>
     </row>
     <row r="25" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A25" s="5" t="s">
-        <v>249</v>
+        <v>245</v>
       </c>
       <c r="B25" s="4" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="C25" s="6">
         <v>2024</v>
       </c>
-    </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A27" s="32" t="s">
+      <c r="D25" s="6"/>
+    </row>
+    <row r="26" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A26" s="5" t="s">
+        <v>249</v>
+      </c>
+      <c r="B26" s="4" t="s">
+        <v>248</v>
+      </c>
+      <c r="C26" s="6">
+        <v>2024</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A28" s="30" t="s">
         <v>250</v>
       </c>
-      <c r="B27" s="33" t="s">
+      <c r="B28" s="31" t="s">
         <v>251</v>
       </c>
-      <c r="C27" s="10"/>
-    </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A28" s="34"/>
-      <c r="B28" s="33" t="s">
+      <c r="C28" s="10"/>
+    </row>
+    <row r="29" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A29" s="32"/>
+      <c r="B29" s="31" t="s">
         <v>252</v>
       </c>
-      <c r="C28" s="10"/>
-    </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="B29" s="1"/>
       <c r="C29" s="10"/>
+    </row>
+    <row r="30" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="B30" s="1"/>
+      <c r="C30" s="10"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
